--- a/docs/xlsx/jobs-2026-10-01.xlsx
+++ b/docs/xlsx/jobs-2026-10-01.xlsx
@@ -14,7 +14,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="32" uniqueCount="8">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1026" uniqueCount="701">
   <si>
     <t>Title</t>
   </si>
@@ -38,13 +38,2092 @@
   </si>
   <si>
     <t>Link</t>
+  </si>
+  <si>
+    <t>Arborist 1 (Trainee Eligible)</t>
+  </si>
+  <si>
+    <t>City of Madison - Forestry</t>
+  </si>
+  <si>
+    <t>Madison, WI</t>
+  </si>
+  <si>
+    <t>Permanent</t>
+  </si>
+  <si>
+    <t>$58,405 - $63,871 per year</t>
+  </si>
+  <si>
+    <t>forestry</t>
+  </si>
+  <si>
+    <t>https://www.conservationjobboard.com/job-listing-arborist-1-trainee-eligible-madison-wisconsin/9398089689</t>
+  </si>
+  <si>
+    <t>ARD Helene Recovery Trail Crew Member</t>
+  </si>
+  <si>
+    <t>Conservation Corps North Carolina</t>
+  </si>
+  <si>
+    <t>Old Fort, NC</t>
+  </si>
+  <si>
+    <t>AmeriCorps</t>
+  </si>
+  <si>
+    <t>$600 per week</t>
+  </si>
+  <si>
+    <t>general-stewardship-outdoor-recreation</t>
+  </si>
+  <si>
+    <t>https://www.conservationjobboard.com/job-listing-ard-helene-recovery-trail-crew-member-old-fort-north-carolina/2051335621</t>
+  </si>
+  <si>
+    <t>Assistant Wildland Fire Management Officer</t>
+  </si>
+  <si>
+    <t>Washington State Department of Natural Resources</t>
+  </si>
+  <si>
+    <t>Chehalis or Menlo, WA</t>
+  </si>
+  <si>
+    <t>$54,204 - $72,900 per year</t>
+  </si>
+  <si>
+    <t>https://www.conservationjobboard.com/job-listing-assistant-wildland-fire-management-officer-chehalis-or-menlo-washington/8963108315</t>
+  </si>
+  <si>
+    <t>Avian Research Technician</t>
+  </si>
+  <si>
+    <t>Tall Timbers</t>
+  </si>
+  <si>
+    <t>Tallahassee, FL</t>
+  </si>
+  <si>
+    <t>Temporary</t>
+  </si>
+  <si>
+    <t>$19 per hour</t>
+  </si>
+  <si>
+    <t>ecology-wildlife</t>
+  </si>
+  <si>
+    <t>https://www.conservationjobboard.com/job-listing-avian-research-technician-tallahassee-florida/1930937581</t>
+  </si>
+  <si>
+    <t>Canada Goose Hazing Dog Team Handler</t>
+  </si>
+  <si>
+    <t>Wildlife Innovations</t>
+  </si>
+  <si>
+    <t>City and state parks across the San Francisco Bay Area, CA</t>
+  </si>
+  <si>
+    <t>$65,000 - $85,000 per year</t>
+  </si>
+  <si>
+    <t>wildlife</t>
+  </si>
+  <si>
+    <t>https://www.conservationjobboard.com/job-listing-canada-goose-hazing-dog-team-handler-city-and-state-parks-across-the-san-francisco-bay-area-california/2358515819</t>
+  </si>
+  <si>
+    <t>Conservation Specialist</t>
+  </si>
+  <si>
+    <t>Trempealeau County</t>
+  </si>
+  <si>
+    <t>Whitehall, WI</t>
+  </si>
+  <si>
+    <t>$26.38 - $30.14 per hour</t>
+  </si>
+  <si>
+    <t>general-stewardship</t>
+  </si>
+  <si>
+    <t>https://www.conservationjobboard.com/job-listing-conservation-specialist-whitehall-wisconsin/9735944649</t>
+  </si>
+  <si>
+    <t>Cumberland Trail Crew: Crew Member</t>
+  </si>
+  <si>
+    <t>Southeast Conservation Corps</t>
+  </si>
+  <si>
+    <t>Chattanooga, TN</t>
+  </si>
+  <si>
+    <t>$480 / week + Additional Benefits: $120 per week; Segal AmeriCorps Education Award: $1,956.35 upon successful completion of program</t>
+  </si>
+  <si>
+    <t>https://www.conservationjobboard.com/job-listing-cumberland-trail-crew-crew-member-chattanooga-tennessee/1133564895</t>
+  </si>
+  <si>
+    <t>Donor Engagement Senior Manager</t>
+  </si>
+  <si>
+    <t>The Marine Mammal Center</t>
+  </si>
+  <si>
+    <t>Sausalito, CA</t>
+  </si>
+  <si>
+    <t>$81,112 - $88,275 per year</t>
+  </si>
+  <si>
+    <t>admin-leadership</t>
+  </si>
+  <si>
+    <t>https://www.conservationjobboard.com/job-listing-donor-engagement-senior-manager-sausalito-california/1841459797</t>
+  </si>
+  <si>
+    <t>Engineer IV</t>
+  </si>
+  <si>
+    <t>Fairfax County Government</t>
+  </si>
+  <si>
+    <t>Fairfax, VA</t>
+  </si>
+  <si>
+    <t>$88,765 - $155,339 per year</t>
+  </si>
+  <si>
+    <t>hydrology</t>
+  </si>
+  <si>
+    <t>https://www.conservationjobboard.com/job-listing-engineer-iv-fairfax-virginia/9260221098</t>
+  </si>
+  <si>
+    <t>English as a Second Language Engagement Coordinator, Forestry Planner</t>
+  </si>
+  <si>
+    <t>Olympia, WA</t>
+  </si>
+  <si>
+    <t>$5,779 - $7,774 per month</t>
+  </si>
+  <si>
+    <t>forestry-general-stewardship</t>
+  </si>
+  <si>
+    <t>https://www.conservationjobboard.com/job-listing-english-as-a-second-language-engagement-coordinator-forestry-planner-olympia-washington/3567682457</t>
+  </si>
+  <si>
+    <t>Environmental Education Coordinator</t>
+  </si>
+  <si>
+    <t>Sawgrass Nature Center and Wildlife Hospital</t>
+  </si>
+  <si>
+    <t>Coral Springs, FL</t>
+  </si>
+  <si>
+    <t>$17 per hour</t>
+  </si>
+  <si>
+    <t>environmental-education-outdoor-recreation</t>
+  </si>
+  <si>
+    <t>https://www.conservationjobboard.com/job-listing-environmental-education-coordinator-coral-springs-florida/9935729184</t>
+  </si>
+  <si>
+    <t>Farm Bill Specialist</t>
+  </si>
+  <si>
+    <t>North Dakota Association of Soil Conservation Districts</t>
+  </si>
+  <si>
+    <t>Bowbells or Williston, ND</t>
+  </si>
+  <si>
+    <t>$24.04 per hour</t>
+  </si>
+  <si>
+    <t>general-stewardship-wildlife</t>
+  </si>
+  <si>
+    <t>https://www.conservationjobboard.com/job-listing-farm-bill-specialist-bowbells-or-williston-north-dakota/5105213583</t>
+  </si>
+  <si>
+    <t>Fish and Wildlife Biological Scientist III</t>
+  </si>
+  <si>
+    <t>Florida Fish and Wildlife Conservation Commission</t>
+  </si>
+  <si>
+    <t>$1,730.77 Biweekly + Benefits</t>
+  </si>
+  <si>
+    <t>ecology-marine-biology-wildlife</t>
+  </si>
+  <si>
+    <t>https://www.conservationjobboard.com/job-listing-fish-and-wildlife-biological-scientist-iii-tallahassee-florida/4036883486</t>
+  </si>
+  <si>
+    <t>Grants Manager</t>
+  </si>
+  <si>
+    <t>Restoring Lands: A Wisconsin Land Trust</t>
+  </si>
+  <si>
+    <t>West Bend, WI</t>
+  </si>
+  <si>
+    <t>$65,000 - $75,000 per year</t>
+  </si>
+  <si>
+    <t>admin-leadership-land-trust</t>
+  </si>
+  <si>
+    <t>https://www.conservationjobboard.com/job-listing-grants-manager-west-bend-wisconsin/2371947535</t>
+  </si>
+  <si>
+    <t>GRD Helene Recovery Trail Assistant Crew Leader</t>
+  </si>
+  <si>
+    <t>$650 per week</t>
+  </si>
+  <si>
+    <t>https://www.conservationjobboard.com/job-listing-grd-helene-recovery-trail-assistant-crew-leader-old-fort-north-carolina/2849432473</t>
+  </si>
+  <si>
+    <t>GRD Helene Recovery Trail Crew Member – AmeriCorps</t>
+  </si>
+  <si>
+    <t>https://www.conservationjobboard.com/job-listing-grd-helene-recovery-trail-crew-member--americorps-old-fort-north-carolina/4426285087</t>
+  </si>
+  <si>
+    <t>Intermediate Wetland Ecologist - (1998)</t>
+  </si>
+  <si>
+    <t>Western EcoSystems Technology ULC</t>
+  </si>
+  <si>
+    <t>Alberta, Canada</t>
+  </si>
+  <si>
+    <t>$70,000 - $95,000 per year</t>
+  </si>
+  <si>
+    <t>ecology</t>
+  </si>
+  <si>
+    <t>https://www.conservationjobboard.com/job-listing-intermediate-wetland-ecologist---1998-alberta-canada/2835634109</t>
+  </si>
+  <si>
+    <t>Land &amp; Wildlife Field Technician I (Entry Level) LCRA</t>
+  </si>
+  <si>
+    <t>Lower Colorado River Authority (LCRA)</t>
+  </si>
+  <si>
+    <t>Marble Falls, TX</t>
+  </si>
+  <si>
+    <t>$24.84 - $30.36 per hour</t>
+  </si>
+  <si>
+    <t>forestry-general-stewardship-restoration-wildlife</t>
+  </si>
+  <si>
+    <t>https://www.conservationjobboard.com/job-listing-land--wildlife-field-technician-i-entry-level-lcra-marble-falls-texas/9301783378</t>
+  </si>
+  <si>
+    <t>Natural Resources Forestry Fire Response Lead</t>
+  </si>
+  <si>
+    <t>Minnesota Department of Natural Resources, Division of Forestry</t>
+  </si>
+  <si>
+    <t>McGregor, MN</t>
+  </si>
+  <si>
+    <t>$21.33 - $26.62 / hourly; $44,537 - $55,582 / annually</t>
+  </si>
+  <si>
+    <t>https://www.conservationjobboard.com/job-listing-natural-resources-forestry-fire-response-lead-mcgregor-minnesota/6659765581</t>
+  </si>
+  <si>
+    <t>On-Call Avian Biologist</t>
+  </si>
+  <si>
+    <t>Coastal Southern California · San Diego, Orange &amp; Los Angeles Counties, CA</t>
+  </si>
+  <si>
+    <t>$32 - $75 per hour</t>
+  </si>
+  <si>
+    <t>https://www.conservationjobboard.com/job-listing-on-call-avian-biologist-coastal-southern-california--san-diego-orange--los-angeles-counties-california/7669887645</t>
+  </si>
+  <si>
+    <t>Outdoor Youth Education Facilitator</t>
+  </si>
+  <si>
+    <t>Sage Mountain Botanical Sanctuary</t>
+  </si>
+  <si>
+    <t>Orange, VT</t>
+  </si>
+  <si>
+    <t>$24 - $27 per hour</t>
+  </si>
+  <si>
+    <t>admin-leadership-environmental-education</t>
+  </si>
+  <si>
+    <t>https://www.conservationjobboard.com/job-listing-outdoor-youth-education-facilitator-orange-vermont/3834070181</t>
+  </si>
+  <si>
+    <t>Park Ranger/Naturalist</t>
+  </si>
+  <si>
+    <t>Franklin County Conservation</t>
+  </si>
+  <si>
+    <t>Hampton, IA</t>
+  </si>
+  <si>
+    <t>$22.52/hr-23.43/hr., will consider experience</t>
+  </si>
+  <si>
+    <t>https://www.conservationjobboard.com/job-listing-park-rangernaturalist-hampton-iowa/3080668349</t>
+  </si>
+  <si>
+    <t>Part-time Executive Director</t>
+  </si>
+  <si>
+    <t>Norwalk River Watershed Association</t>
+  </si>
+  <si>
+    <t>Norwalk, CT</t>
+  </si>
+  <si>
+    <t>$30 - $40 per hour</t>
+  </si>
+  <si>
+    <t>https://www.conservationjobboard.com/job-listing-part-time-executive-director-norwalk-connecticut/1055579245</t>
+  </si>
+  <si>
+    <t>Predator Biologist</t>
+  </si>
+  <si>
+    <t>Coastal San Diego, Orange, and/or Los Angeles Counties, CA</t>
+  </si>
+  <si>
+    <t>$70,000 - $110,000 per year</t>
+  </si>
+  <si>
+    <t>https://www.conservationjobboard.com/job-listing-predator-biologist-coastal-san-diego-orange-andor-los-angeles-counties-california/9625872236</t>
+  </si>
+  <si>
+    <t>President &amp; Chief Executive Officer</t>
+  </si>
+  <si>
+    <t>One Hundred Miles</t>
+  </si>
+  <si>
+    <t>Brunswick, GA</t>
+  </si>
+  <si>
+    <t>Compensation is expected to be in the mid-$100s, commensurate with experience and qualifications. One Hundred Miles offers a competitive benefits package.</t>
+  </si>
+  <si>
+    <t>admin-leadership-marine-biology-policy-and-law</t>
+  </si>
+  <si>
+    <t>https://www.conservationjobboard.com/job-listing-president--chief-executive-officer-brunswick-georgia/9436417515</t>
+  </si>
+  <si>
+    <t>Program Specialist V (Region IV/V Fire Management Coordinator)</t>
+  </si>
+  <si>
+    <t>Texas Parks and Wildlife Department</t>
+  </si>
+  <si>
+    <t>Region IV Post Oak Savannah and Coastal Prairie, TX</t>
+  </si>
+  <si>
+    <t>$6,776.85 per month</t>
+  </si>
+  <si>
+    <t>admin-leadership-forestry</t>
+  </si>
+  <si>
+    <t>https://www.conservationjobboard.com/job-listing-program-specialist-v-region-ivv-fire-management-coordinator-region-iv-post-oak-savannah-and-coastal-prairie-texas/8331341323</t>
+  </si>
+  <si>
+    <t>Research Supervisor Fellowship</t>
+  </si>
+  <si>
+    <t>The Canadian Organization for Tropical Education and Rainforest Conservation (COTERC)</t>
+  </si>
+  <si>
+    <t>Tortuguero, Costa Rica, Other</t>
+  </si>
+  <si>
+    <t>Full room and board at Caño Palma Biological Station. $600/month stipend. $200 bonus every three months. $1,000 bonus at the successful completion of 1 year contract.</t>
+  </si>
+  <si>
+    <t>ecology-forestry</t>
+  </si>
+  <si>
+    <t>https://www.conservationjobboard.com/job-listing-research-supervisor-fellowship-tortuguero-costa-rica-other/4020346567</t>
+  </si>
+  <si>
+    <t>Research Technician I–II</t>
+  </si>
+  <si>
+    <t>Texas A&amp;M University- Corpus Christi</t>
+  </si>
+  <si>
+    <t>Corpus Christi, TX</t>
+  </si>
+  <si>
+    <t>up to $20.67/hour</t>
+  </si>
+  <si>
+    <t>marine-biology-restoration</t>
+  </si>
+  <si>
+    <t>https://www.conservationjobboard.com/job-listing-research-technician-iii-corpus-christi-texas/3303429662</t>
+  </si>
+  <si>
+    <t>Restoration Site Operations Manager</t>
+  </si>
+  <si>
+    <t>GeoSystems Analysis</t>
+  </si>
+  <si>
+    <t>San Acacia, NM</t>
+  </si>
+  <si>
+    <t>$66,000 - $80,000 per year</t>
+  </si>
+  <si>
+    <t>restoration</t>
+  </si>
+  <si>
+    <t>https://www.conservationjobboard.com/job-listing-restoration-site-operations-manager-san-acacia-new-mexico/1794455081</t>
+  </si>
+  <si>
+    <t>Sanctuary Grounds Coordinator</t>
+  </si>
+  <si>
+    <t>American Bear Association</t>
+  </si>
+  <si>
+    <t>Orr, MN</t>
+  </si>
+  <si>
+    <t>$400 - $500 per week</t>
+  </si>
+  <si>
+    <t>https://www.conservationjobboard.com/job-listing-sanctuary-grounds-coordinator-orr-minnesota/6671991651</t>
+  </si>
+  <si>
+    <t>Senior Educator</t>
+  </si>
+  <si>
+    <t>Appalachian Mountain Club</t>
+  </si>
+  <si>
+    <t>Gorham, NH</t>
+  </si>
+  <si>
+    <t>$18 per hour</t>
+  </si>
+  <si>
+    <t>environmental-education</t>
+  </si>
+  <si>
+    <t>https://www.conservationjobboard.com/job-listing-senior-educator-gorham-new-hampshire/5076206852</t>
+  </si>
+  <si>
+    <t>Senior Environmental Scientist Specialist Inspector</t>
+  </si>
+  <si>
+    <t>Office of Energy Infrastructure Safety</t>
+  </si>
+  <si>
+    <t>Lakewood, CA</t>
+  </si>
+  <si>
+    <t>$7,820 - $10,732 per month</t>
+  </si>
+  <si>
+    <t>forestry-policy-and-law</t>
+  </si>
+  <si>
+    <t>https://www.conservationjobboard.com/job-listing-senior-environmental-scientist-specialist-inspector-lakewood-california/3626385816</t>
+  </si>
+  <si>
+    <t>Senior Information Manager - Vermont Department of Fish and Wildlife</t>
+  </si>
+  <si>
+    <t>Vermont Department of Fish and Wildlife</t>
+  </si>
+  <si>
+    <t>Montpelier, VT</t>
+  </si>
+  <si>
+    <t>$35.66 - $55.92 per hour</t>
+  </si>
+  <si>
+    <t>https://www.conservationjobboard.com/job-listing-senior-information-manager---vermont-department-of-fish-and-wildlife-montpelier-vermont/5826178067</t>
+  </si>
+  <si>
+    <t>SEPA and Environmental Regulation Specialist (Environmental Specialist 3)</t>
+  </si>
+  <si>
+    <t>WA State Department of Ecology</t>
+  </si>
+  <si>
+    <t>Richland, WA</t>
+  </si>
+  <si>
+    <t>$59,760 - $80,496 per year</t>
+  </si>
+  <si>
+    <t>general-stewardship-policy-and-law</t>
+  </si>
+  <si>
+    <t>https://www.conservationjobboard.com/job-listing-sepa-and-environmental-regulation-specialist-environmental-specialist-3-richland-washington/3004147398</t>
+  </si>
+  <si>
+    <t>Southern Appalachian Forest Recovery Program Manager</t>
+  </si>
+  <si>
+    <t>National Forest Foundation</t>
+  </si>
+  <si>
+    <t>Western, AR</t>
+  </si>
+  <si>
+    <t>$95,000 per year</t>
+  </si>
+  <si>
+    <t>admin-leadership-forestry-restoration</t>
+  </si>
+  <si>
+    <t>https://www.conservationjobboard.com/job-listing-southern-appalachian-forest-recovery-program-manager-western-arkansas/2900553067</t>
+  </si>
+  <si>
+    <t>Southern California Project Coordinator</t>
+  </si>
+  <si>
+    <t>Los Angeles, CA</t>
+  </si>
+  <si>
+    <t>$75,000 per year</t>
+  </si>
+  <si>
+    <t>admin-leadership-forestry-general-stewardship</t>
+  </si>
+  <si>
+    <t>https://www.conservationjobboard.com/job-listing-southern-california-project-coordinator-los-angeles-california/8898703238</t>
+  </si>
+  <si>
+    <t>Southwest Region Policy Manager</t>
+  </si>
+  <si>
+    <t>Florida Wildlife Federation</t>
+  </si>
+  <si>
+    <t>Remote, FL</t>
+  </si>
+  <si>
+    <t>$55,000 per year</t>
+  </si>
+  <si>
+    <t>policy-and-law-wildlife</t>
+  </si>
+  <si>
+    <t>https://www.conservationjobboard.com/job-listing-southwest-region-policy-manager-remote-florida/2282315707</t>
+  </si>
+  <si>
+    <t>Staff Attorney</t>
+  </si>
+  <si>
+    <t>Sage Steppe Wild</t>
+  </si>
+  <si>
+    <t>Pinedale, Remote</t>
+  </si>
+  <si>
+    <t>Based on Experience and Resources, to be discussed</t>
+  </si>
+  <si>
+    <t>policy-and-law</t>
+  </si>
+  <si>
+    <t>https://www.conservationjobboard.com/job-listing-staff-attorney-pinedale-remote/9366585405</t>
+  </si>
+  <si>
+    <t>State Parks Mountains Crew Member</t>
+  </si>
+  <si>
+    <t>https://www.conservationjobboard.com/job-listing-state-parks-mountains-crew-member-old-fort-north-carolina/3399877212</t>
+  </si>
+  <si>
+    <t>State Parks Piedmont Crew Member</t>
+  </si>
+  <si>
+    <t>Bahama, NC</t>
+  </si>
+  <si>
+    <t>https://www.conservationjobboard.com/job-listing-state-parks-piedmont-crew-member-bahama-north-carolina/6573790714</t>
+  </si>
+  <si>
+    <t>State Parks Piedmont Trail Assistant Crew Leader</t>
+  </si>
+  <si>
+    <t>https://www.conservationjobboard.com/job-listing-state-parks-piedmont-trail-assistant-crew-leader-bahama-north-carolina/5177540395</t>
+  </si>
+  <si>
+    <t>Technical Services Bureau Chief</t>
+  </si>
+  <si>
+    <t>Idaho Department of Fish and Game</t>
+  </si>
+  <si>
+    <t>Boise, ID</t>
+  </si>
+  <si>
+    <t>$47.90 - $59.87 per hour</t>
+  </si>
+  <si>
+    <t>admin-leadership-general-stewardship</t>
+  </si>
+  <si>
+    <t>https://www.conservationjobboard.com/job-listing-technical-services-bureau-chief-boise-idaho/1989753124</t>
+  </si>
+  <si>
+    <t>Visitor Center &amp; Retail Operations Manager</t>
+  </si>
+  <si>
+    <t>$500 - $575 per week</t>
+  </si>
+  <si>
+    <t>admin-leadership-outdoor-recreation</t>
+  </si>
+  <si>
+    <t>https://www.conservationjobboard.com/job-listing-visitor-center--retail-operations-manager-orr-minnesota/1392409179</t>
+  </si>
+  <si>
+    <t>Volunteer &amp; Training Coordinator</t>
+  </si>
+  <si>
+    <t>Washington Trails Association (WTA)</t>
+  </si>
+  <si>
+    <t>Seattle, WA</t>
+  </si>
+  <si>
+    <t>$25.50 - $27.50 per hour</t>
+  </si>
+  <si>
+    <t>https://www.conservationjobboard.com/job-listing-volunteer--training-coordinator-seattle-washington/7963000902</t>
+  </si>
+  <si>
+    <t>Wildlife Biologist / Management Specialist</t>
+  </si>
+  <si>
+    <t>San Francisco Bay Area (based in San Mateo County), CA</t>
+  </si>
+  <si>
+    <t>https://www.conservationjobboard.com/job-listing-wildlife-biologist--management-specialist-san-francisco-bay-area-based-in-san-mateo-county-california/1826782424</t>
+  </si>
+  <si>
+    <t>Wildlife Biologist II/III</t>
+  </si>
+  <si>
+    <t>Axon Environmental Management</t>
+  </si>
+  <si>
+    <t>Santa Barbara, CA</t>
+  </si>
+  <si>
+    <t>$28 - $38 per hour</t>
+  </si>
+  <si>
+    <t>https://www.conservationjobboard.com/job-listing-wildlife-biologist-iiiii-santa-barbara-california/8643057439</t>
+  </si>
+  <si>
+    <t>Ventura, CA</t>
+  </si>
+  <si>
+    <t>https://www.conservationjobboard.com/job-listing-wildlife-biologist-iiiii-ventura-california/9999221061</t>
+  </si>
+  <si>
+    <t>Riverside, CA</t>
+  </si>
+  <si>
+    <t>https://www.conservationjobboard.com/job-listing-wildlife-biologist-iiiii-riverside-california/7422704208</t>
+  </si>
+  <si>
+    <t>San Bernardino, CA</t>
+  </si>
+  <si>
+    <t>https://www.conservationjobboard.com/job-listing-wildlife-biologist-iiiii-san-bernardino-california/7182231511</t>
+  </si>
+  <si>
+    <t>Wildlife Habitat Biologist - South Dakota</t>
+  </si>
+  <si>
+    <t>Bird Conservancy of the Rockies</t>
+  </si>
+  <si>
+    <t>Philip or Kadoka, SD</t>
+  </si>
+  <si>
+    <t>$58,000 - $65,000 per year</t>
+  </si>
+  <si>
+    <t>restoration-wildlife</t>
+  </si>
+  <si>
+    <t>https://www.conservationjobboard.com/job-listing-wildlife-habitat-biologist---south-dakota-philip-or-kadoka-south-dakota/4251936345</t>
+  </si>
+  <si>
+    <t>Field Crewmember</t>
+  </si>
+  <si>
+    <t>EarthCorps</t>
+  </si>
+  <si>
+    <t>Seattle, Washington, United States</t>
+  </si>
+  <si>
+    <t>20,000 - 40,000</t>
+  </si>
+  <si>
+    <t>Environmental</t>
+  </si>
+  <si>
+    <t>https://greenjobs.greenjobsearch.org/jobs/field-crewmember/</t>
+  </si>
+  <si>
+    <t>Senior Planning Specialist (Zero Waste Programs), Grade 25</t>
+  </si>
+  <si>
+    <t>Montgomery County, MD Government</t>
+  </si>
+  <si>
+    <t>Wheaton-Glenmont, Maryland, United States</t>
+  </si>
+  <si>
+    <t>Full-Time</t>
+  </si>
+  <si>
+    <t/>
+  </si>
+  <si>
+    <t>Conservation</t>
+  </si>
+  <si>
+    <t>https://greenjobs.greenjobsearch.org/jobs/senior-planning-specialist-zero-waste-programs-grade-25/</t>
+  </si>
+  <si>
+    <t>Administrativo y atención a socios</t>
+  </si>
+  <si>
+    <t>Survival International- en español</t>
+  </si>
+  <si>
+    <t>Madrid, Madrid, ES</t>
+  </si>
+  <si>
+    <t>Full Time</t>
+  </si>
+  <si>
+    <t>EUR 25000.00 - 26000.00/year</t>
+  </si>
+  <si>
+    <t>Human Rights Civil Liberties, Environment</t>
+  </si>
+  <si>
+    <t>https://www.idealist.org/en/nonprofit-job/14dbd4a827594fa4832b53db538ac52d-administrativo-y-atencion-a-socios-survival-international-en-espanol-madrid</t>
+  </si>
+  <si>
+    <t>Africa Director</t>
+  </si>
+  <si>
+    <t>Re:wild</t>
+  </si>
+  <si>
+    <t>Remote</t>
+  </si>
+  <si>
+    <t>USD 115000.00 - 130000.00/year</t>
+  </si>
+  <si>
+    <t>Animals, Environment, Climate Change</t>
+  </si>
+  <si>
+    <t>https://www.idealist.org/en/nonprofit-job/e274a6116ba24779b01cce116fe3539e-africa-director-rewild-austin</t>
+  </si>
+  <si>
+    <t>After-School Director [IS 229]</t>
+  </si>
+  <si>
+    <t>Replications, Inc</t>
+  </si>
+  <si>
+    <t>Bronx, New York</t>
+  </si>
+  <si>
+    <t>USD 70000.00 - 80000.00/year</t>
+  </si>
+  <si>
+    <t>Children Youth, Community Development, Education</t>
+  </si>
+  <si>
+    <t>https://www.idealist.org/en/nonprofit-job/3527d18e35b145f5a7b63dafe9ea4dbc-after-school-director-is-229-replications-inc-bronx</t>
+  </si>
+  <si>
+    <t>Agency Relations Coordiantor</t>
+  </si>
+  <si>
+    <t>Food Lifeline</t>
+  </si>
+  <si>
+    <t>USD 25.00 - 30.00/hour</t>
+  </si>
+  <si>
+    <t>Hunger Food Security</t>
+  </si>
+  <si>
+    <t>https://www.idealist.org/en/nonprofit-job/5e65a875d09e417ea73866ead3feab3f-agency-relations-coordiantor-food-lifeline-seattle</t>
+  </si>
+  <si>
+    <t>Assistant Director of Programs</t>
+  </si>
+  <si>
+    <t>Minds Matter National, Inc.</t>
+  </si>
+  <si>
+    <t>USD 90000.00 - 90000.00/year</t>
+  </si>
+  <si>
+    <t>Children Youth, Education, Volunteering</t>
+  </si>
+  <si>
+    <t>https://www.idealist.org/en/nonprofit-job/9f923ac9c67b4acd87d9ad485075ee39-assistant-director-of-programs-minds-matter-national-inc-new-york</t>
+  </si>
+  <si>
+    <t>Assistant General Counsel</t>
+  </si>
+  <si>
+    <t>Hadassah, WZOA, Inc.</t>
+  </si>
+  <si>
+    <t>New York, New York</t>
+  </si>
+  <si>
+    <t>USD 146067.00 - 165000.00/year</t>
+  </si>
+  <si>
+    <t>Education, Health Medicine, Women</t>
+  </si>
+  <si>
+    <t>https://www.idealist.org/en/nonprofit-job/97ac0d5bacb248db82788aedaa389982-assistant-general-counsel-hadassah-wzoa-inc-new-york</t>
+  </si>
+  <si>
+    <t>Assistant Teacher</t>
+  </si>
+  <si>
+    <t>Freedom Side School</t>
+  </si>
+  <si>
+    <t>Philadelphia, Pennsylvania</t>
+  </si>
+  <si>
+    <t>USD 80000.00/year</t>
+  </si>
+  <si>
+    <t>Children Youth, Education, Prison Reform</t>
+  </si>
+  <si>
+    <t>https://www.idealist.org/en/nonprofit-job/96f180d599204818bb7073fc7bf10895-assistant-teacher-freedom-side-school-philadelphia</t>
+  </si>
+  <si>
+    <t>Assistant Teachers for Kindergarten, First or Second Grade</t>
+  </si>
+  <si>
+    <t>Wissahickon Charter School</t>
+  </si>
+  <si>
+    <t>USD 37000.00 - 37000.00/year</t>
+  </si>
+  <si>
+    <t>Education, Children Youth</t>
+  </si>
+  <si>
+    <t>https://www.idealist.org/en/nonprofit-job/52bad82e236249a78228e54983f4d2ae-assistant-teachers-for-kindergarten-first-or-second-grade-wissahickon-charter-school-philadelphia</t>
+  </si>
+  <si>
+    <t>Auxiliar de Cozinha e Limpeza (CLT)</t>
+  </si>
+  <si>
+    <t>Eco Caminhos</t>
+  </si>
+  <si>
+    <t>Nova Friburgo, Rio de Janeiro, BR</t>
+  </si>
+  <si>
+    <t>Agriculture, Education, Environment</t>
+  </si>
+  <si>
+    <t>https://www.idealist.org/en/nonprofit-job/3eddefbc326846c9a703fdc0d717f633-auxiliar-de-cozinha-e-limpeza-clt-eco-caminhos-nova-friburgo</t>
+  </si>
+  <si>
+    <t>Bilingual Therapist (Domestic and Sexual Violence)</t>
+  </si>
+  <si>
+    <t>Doorways</t>
+  </si>
+  <si>
+    <t>Arlington, Virginia</t>
+  </si>
+  <si>
+    <t>USD 65000.00 - 68000.00/year</t>
+  </si>
+  <si>
+    <t>Children Youth, Housing Homelessness, Mental Health</t>
+  </si>
+  <si>
+    <t>https://www.idealist.org/en/nonprofit-job/584520a7e9784c2f8466a7f62fee7371-bilingual-therapist-domestic-and-sexual-violence-doorways-arlington</t>
+  </si>
+  <si>
+    <t>Case Management Specialist</t>
+  </si>
+  <si>
+    <t>Bridge Over Troubled Water</t>
+  </si>
+  <si>
+    <t>Boston, Massachusetts</t>
+  </si>
+  <si>
+    <t>USD 60000.00 - 65000.00/year</t>
+  </si>
+  <si>
+    <t>https://www.idealist.org/en/job/9fb2e1db465844e89572a466bd4fc286-case-management-specialist-bridge-over-troubled-water-boston</t>
+  </si>
+  <si>
+    <t>Chief Operating Officer (COO)</t>
+  </si>
+  <si>
+    <t>National Domestic Workers Alliance / La Alianza Nacional de Trabajadores del Hogar</t>
+  </si>
+  <si>
+    <t>USD 175000.00 - 200000.00/year</t>
+  </si>
+  <si>
+    <t>Human Rights Civil Liberties, Immigrants Or Refugees, Job Workplace</t>
+  </si>
+  <si>
+    <t>https://www.idealist.org/en/nonprofit-job/7588fc61d7fe4377baab71c4e8dc6ccb-chief-operating-officer-coo-national-domestic-workers-alliance-la-alianza-nacional-de-trabajadores-del-hogar-new-york</t>
+  </si>
+  <si>
+    <t>Chief Program &amp; Strategy Officer</t>
+  </si>
+  <si>
+    <t>BoardSource</t>
+  </si>
+  <si>
+    <t>Washington, District of Columbia</t>
+  </si>
+  <si>
+    <t>USD 170000.00 - 210000.00/year</t>
+  </si>
+  <si>
+    <t>https://www.idealist.org/en/job/ee01929a11534ccaa4f424b81532105c-chief-program-strategy-officer-boardsource-washington</t>
+  </si>
+  <si>
+    <t>Co-Executive Directors</t>
+  </si>
+  <si>
+    <t>Farm School NYC</t>
+  </si>
+  <si>
+    <t>USD 100000.00 - 100000.00/year</t>
+  </si>
+  <si>
+    <t>Agriculture, Community Development, Education</t>
+  </si>
+  <si>
+    <t>https://www.idealist.org/en/nonprofit-job/f7c7dddd595d4d9295c950270546601b-co-executive-directors-farm-school-nyc-new-york</t>
+  </si>
+  <si>
+    <t>Communications &amp; Marketing Coordinator</t>
+  </si>
+  <si>
+    <t>Ivymount Organization</t>
+  </si>
+  <si>
+    <t>Potomac, Maryland</t>
+  </si>
+  <si>
+    <t>USD 62000.00/year</t>
+  </si>
+  <si>
+    <t>Disability, Education, Children Youth</t>
+  </si>
+  <si>
+    <t>https://www.idealist.org/en/nonprofit-job/64565abf6c20467dbf3e80521236a330-communications-marketing-coordinator-ivymount-organization-potomac</t>
+  </si>
+  <si>
+    <t>Community Engagement Manager</t>
+  </si>
+  <si>
+    <t>Project Citizenship</t>
+  </si>
+  <si>
+    <t>USD 55000.00 - 62000.00/year</t>
+  </si>
+  <si>
+    <t>Civic Engagement, Immigrants Or Refugees</t>
+  </si>
+  <si>
+    <t>https://www.idealist.org/en/nonprofit-job/fce45b1901b545b098041d3380bcb8d5-community-engagement-manager-project-citizenship-boston</t>
+  </si>
+  <si>
+    <t>Community Relations Director</t>
+  </si>
+  <si>
+    <t>Jewish Federation of Madison</t>
+  </si>
+  <si>
+    <t>Madison, Wisconsin</t>
+  </si>
+  <si>
+    <t>USD 75000.00 - 85000.00/year</t>
+  </si>
+  <si>
+    <t>Civic Engagement, Education, Conflict Resolution</t>
+  </si>
+  <si>
+    <t>https://www.idealist.org/en/nonprofit-job/cd6ca5f2039e48659f3159fe9cf6cfc8-community-relations-director-jewish-federation-of-madison-madison</t>
+  </si>
+  <si>
+    <t>Corporate &amp; Individual Gift Officer</t>
+  </si>
+  <si>
+    <t>Connectedly</t>
+  </si>
+  <si>
+    <t>Part Time</t>
+  </si>
+  <si>
+    <t>Children Youth, Education, Family</t>
+  </si>
+  <si>
+    <t>https://www.idealist.org/en/nonprofit-job/284113e0becb416d8d0f2cc36a8cc585-corporate-individual-gift-officer-connectedly-philadelphia</t>
+  </si>
+  <si>
+    <t>Development &amp; Communications Specialist</t>
+  </si>
+  <si>
+    <t>Washington Alliance for Better Schools</t>
+  </si>
+  <si>
+    <t>Shoreline, Washington</t>
+  </si>
+  <si>
+    <t>Education, Job Workplace, Science Technology</t>
+  </si>
+  <si>
+    <t>https://www.idealist.org/en/nonprofit-job/8f52be70fe024571876f2a10379568de-development-communications-specialist-washington-alliance-for-better-schools-shoreline</t>
+  </si>
+  <si>
+    <t>Development Associate</t>
+  </si>
+  <si>
+    <t>Asian Pacific Fund</t>
+  </si>
+  <si>
+    <t>San Francisco, California</t>
+  </si>
+  <si>
+    <t>USD 73000.00 - 90000.00/year</t>
+  </si>
+  <si>
+    <t>Philanthropy, Community Development</t>
+  </si>
+  <si>
+    <t>https://www.idealist.org/en/nonprofit-job/d386a79a793e43dba8cc0fe7be74a813-development-associate-asian-pacific-fund-san-francisco</t>
+  </si>
+  <si>
+    <t>Development Officer</t>
+  </si>
+  <si>
+    <t>ALL STARS PROJECT INC.</t>
+  </si>
+  <si>
+    <t>USD 60000.00 - 66000.00/year</t>
+  </si>
+  <si>
+    <t>https://www.idealist.org/en/job/7a0275774c344b8b89d606ed54bb4d2a-development-officer-all-stars-project-inc-new-york</t>
+  </si>
+  <si>
+    <t>Development, Fundraising and Grants Manager</t>
+  </si>
+  <si>
+    <t>Woman, Cradle of Abundance</t>
+  </si>
+  <si>
+    <t>Contract</t>
+  </si>
+  <si>
+    <t>USD 35.00/hour</t>
+  </si>
+  <si>
+    <t>Women, Children Youth, Education</t>
+  </si>
+  <si>
+    <t>https://www.idealist.org/en/nonprofit-job/1205b0516bd74e32bfd2fbf7da3af923-development-fundraising-and-grants-manager-woman-cradle-of-abundance-cherry-hill-township</t>
+  </si>
+  <si>
+    <t>Digital and Communications Manager</t>
+  </si>
+  <si>
+    <t>NY Renews</t>
+  </si>
+  <si>
+    <t>New York, NY</t>
+  </si>
+  <si>
+    <t>USD 70000.00 - 90000.00/year</t>
+  </si>
+  <si>
+    <t>Civic Engagement, Climate Change, Economic Development</t>
+  </si>
+  <si>
+    <t>https://www.idealist.org/en/nonprofit-job/3936fc166585477c844018ca9999ceb3-digital-and-communications-manager-ny-renews-new-york</t>
+  </si>
+  <si>
+    <t>Director of Development</t>
+  </si>
+  <si>
+    <t>Action in Africa</t>
+  </si>
+  <si>
+    <t>Denver, Colorado</t>
+  </si>
+  <si>
+    <t>USD 90000.00 - 115000.00/year</t>
+  </si>
+  <si>
+    <t>https://www.idealist.org/en/nonprofit-job/09e8de5859e8419f84d9275927787594-director-of-development-action-in-africa-denver</t>
+  </si>
+  <si>
+    <t>Director of Development and Communications</t>
+  </si>
+  <si>
+    <t>Court Appointed Special Advocates (CASA-NYC)</t>
+  </si>
+  <si>
+    <t>USD 140000.00 - 160000.00/year</t>
+  </si>
+  <si>
+    <t>Children Youth, Family, Volunteering</t>
+  </si>
+  <si>
+    <t>https://www.idealist.org/en/nonprofit-job/383c8a9377e34e2693c1d5046a205940-director-of-development-and-communications-court-appointed-special-advocates-casa-nyc-new-york</t>
+  </si>
+  <si>
+    <t>Atlas Performing Arts Center</t>
+  </si>
+  <si>
+    <t>Washington, DC</t>
+  </si>
+  <si>
+    <t>USD 80000.00 - 95000.00/year</t>
+  </si>
+  <si>
+    <t>Arts Music</t>
+  </si>
+  <si>
+    <t>https://www.idealist.org/en/nonprofit-job/f5cb2f4c3d71427ea1b622bd146cdd12-director-of-development-and-communications-atlas-performing-arts-center-washington</t>
+  </si>
+  <si>
+    <t>DC History Center</t>
+  </si>
+  <si>
+    <t>USD 95000.00 - 95000.00/year</t>
+  </si>
+  <si>
+    <t>https://www.idealist.org/en/job/1069753450d44dfc8766047230930593-director-of-development-and-communications-dc-history-center-washington</t>
+  </si>
+  <si>
+    <t>Director of Education &amp; Community Engagement</t>
+  </si>
+  <si>
+    <t>Santa Rosa Symphony</t>
+  </si>
+  <si>
+    <t>Santa Rosa, California</t>
+  </si>
+  <si>
+    <t>USD 80000.00 - 90000.00/year</t>
+  </si>
+  <si>
+    <t>Arts Music, Children Youth, Community Development</t>
+  </si>
+  <si>
+    <t>https://www.idealist.org/en/nonprofit-job/99970bde554c41339f5aae350d4851d9-director-of-education-community-engagement-santa-rosa-symphony-santa-rosa</t>
+  </si>
+  <si>
+    <t>Director of Philanthropy Operations</t>
+  </si>
+  <si>
+    <t>Children's Law Center</t>
+  </si>
+  <si>
+    <t>USD 80000.00 - 110000.00/year</t>
+  </si>
+  <si>
+    <t>Children Youth, Philanthropy</t>
+  </si>
+  <si>
+    <t>https://www.idealist.org/en/nonprofit-job/86d51dcdedc64840b9b8d2537a22fa8c-director-of-philanthropy-operations-childrens-law-center-washington</t>
+  </si>
+  <si>
+    <t>Director of Planned Giving</t>
+  </si>
+  <si>
+    <t>Jewish Federation of Greater Houston</t>
+  </si>
+  <si>
+    <t>Houston, Texas</t>
+  </si>
+  <si>
+    <t>USD 100000.00 - 120000.00/year</t>
+  </si>
+  <si>
+    <t>Community Development, Philanthropy, Religion Spirituality</t>
+  </si>
+  <si>
+    <t>https://www.idealist.org/en/nonprofit-job/dcdf3409284c4176a92d82c77c4d2338-director-of-planned-giving-jewish-federation-of-greater-houston-houston</t>
+  </si>
+  <si>
+    <t>Director, Major Gifts</t>
+  </si>
+  <si>
+    <t>Equality Now</t>
+  </si>
+  <si>
+    <t>USD 120000.00 - 140000.00/year</t>
+  </si>
+  <si>
+    <t>Women, Family, Human Rights Civil Liberties</t>
+  </si>
+  <si>
+    <t>https://www.idealist.org/en/nonprofit-job/78f9040a70e44c698e0143ed6666492d-director-major-gifts-equality-now-new-york</t>
+  </si>
+  <si>
+    <t>Donor Analyst Manager</t>
+  </si>
+  <si>
+    <t>Philanthropy, Religion Spirituality</t>
+  </si>
+  <si>
+    <t>https://www.idealist.org/en/nonprofit-job/cd6ec831f60246b4b01b5e3e6695dc5e-donor-analyst-manager-jewish-federation-of-greater-houston-houston</t>
+  </si>
+  <si>
+    <t>English as a Second Language Engagement Coordinator, Forestry Environmental Planner</t>
+  </si>
+  <si>
+    <t>WA State Department of Natural Resources</t>
+  </si>
+  <si>
+    <t>Full Time, Temporary</t>
+  </si>
+  <si>
+    <t>USD 5779.00 - 7774.00/month</t>
+  </si>
+  <si>
+    <t>Environment, Climate Change, Rural Areas</t>
+  </si>
+  <si>
+    <t>https://www.idealist.org/en/government-job/62a307af33c74853b046a7b65b25adef-english-as-a-second-language-engagement-coordinator-forestry-environmental-planner-wa-state-department-of-natural-resources-olympia</t>
+  </si>
+  <si>
+    <t>Executive Director</t>
+  </si>
+  <si>
+    <t>Washington Native Plant Society</t>
+  </si>
+  <si>
+    <t>Seattle, Washington</t>
+  </si>
+  <si>
+    <t>USD 110000.00 - 125000.00/year</t>
+  </si>
+  <si>
+    <t>Environment, Education, Volunteering</t>
+  </si>
+  <si>
+    <t>https://www.idealist.org/en/nonprofit-job/00ed3848b2f049d6b5cc62789800af2b-executive-director-washington-native-plant-society-seattle</t>
+  </si>
+  <si>
+    <t>Temple Beth El - Madison, WI</t>
+  </si>
+  <si>
+    <t>USD 125000.00 - 145000.00/year</t>
+  </si>
+  <si>
+    <t>Religion Spirituality</t>
+  </si>
+  <si>
+    <t>https://www.idealist.org/en/nonprofit-job/f9c186835123478d813afdb344ecc664-executive-director-temple-beth-el-madison-wi-madison</t>
+  </si>
+  <si>
+    <t>Edmonds Center for the Arts</t>
+  </si>
+  <si>
+    <t>Edmonds, Washington</t>
+  </si>
+  <si>
+    <t>USD 150000.00 - 180000.00/year</t>
+  </si>
+  <si>
+    <t>https://www.idealist.org/en/job/c49de7a171294a4781fda02bb361ae97-executive-director-edmonds-center-for-the-arts-edmonds</t>
+  </si>
+  <si>
+    <t>Executive Director / President</t>
+  </si>
+  <si>
+    <t>Code for Science &amp; Society (CS&amp;S)</t>
+  </si>
+  <si>
+    <t>USD 225000.00 - 250000.00/year</t>
+  </si>
+  <si>
+    <t>Science Technology</t>
+  </si>
+  <si>
+    <t>https://www.idealist.org/en/job/5fe0da323136401ab5e9d4b81b641c07-executive-director-president-code-for-science-society-css-portland</t>
+  </si>
+  <si>
+    <t>Executive Vice President</t>
+  </si>
+  <si>
+    <t>The Pacific Forest Trust</t>
+  </si>
+  <si>
+    <t>USD 160000.00 - 190000.00/year</t>
+  </si>
+  <si>
+    <t>Environment</t>
+  </si>
+  <si>
+    <t>https://www.idealist.org/en/nonprofit-job/db5dd06d2cf5404cb566411d09cc61e3-executive-vice-president-the-pacific-forest-trust-san-francisco</t>
+  </si>
+  <si>
+    <t>FARM PRODUCE DELIVERY DRIVER (NON-CDL)</t>
+  </si>
+  <si>
+    <t>Cityseed</t>
+  </si>
+  <si>
+    <t>New Haven, Connecticut</t>
+  </si>
+  <si>
+    <t>Agriculture, Entrepreneurship, Hunger Food Security</t>
+  </si>
+  <si>
+    <t>https://www.idealist.org/en/nonprofit-job/5f65205c9bbe434b902acdc1c8cb265f-farm-produce-delivery-driver-non-cdl-cityseed-new-haven</t>
+  </si>
+  <si>
+    <t>General Educational Development (GED) Instructor</t>
+  </si>
+  <si>
+    <t>Center for Work Education and Employment</t>
+  </si>
+  <si>
+    <t>USD 57749.00 - 75705.00/year</t>
+  </si>
+  <si>
+    <t>Job Workplace, Education, Economic Development</t>
+  </si>
+  <si>
+    <t>https://www.idealist.org/en/nonprofit-job/5546117e5cf54c409280fdbab2f37d0a-general-educational-development-ged-instructor-center-for-work-education-and-employment-denver</t>
+  </si>
+  <si>
+    <t>Housing Case Manager</t>
+  </si>
+  <si>
+    <t>USD 55000.00 - 57000.00/year</t>
+  </si>
+  <si>
+    <t>https://www.idealist.org/en/nonprofit-job/cac4552ef02e4eaa886a6e0597024754-housing-case-manager-doorways-arlington</t>
+  </si>
+  <si>
+    <t>HR/EPeC Generalist</t>
+  </si>
+  <si>
+    <t>Vermont Foodbank</t>
+  </si>
+  <si>
+    <t>Barre, Vermont</t>
+  </si>
+  <si>
+    <t>USD 54376.00 - 73568.00/year</t>
+  </si>
+  <si>
+    <t>Civic Engagement, Poverty, Volunteering</t>
+  </si>
+  <si>
+    <t>https://www.idealist.org/en/nonprofit-job/b818491867b340619bc27cc6ad8d1eda-hrepec-generalist-vermont-foodbank-barre</t>
+  </si>
+  <si>
+    <t>Immigrants’ Rights Staff Attorney or Senior Attorney Position</t>
+  </si>
+  <si>
+    <t>TakeRoot Justice</t>
+  </si>
+  <si>
+    <t>USD 83490.00 - 96550.00/year</t>
+  </si>
+  <si>
+    <t>Community Development, Housing Homelessness, Immigrants Or Refugees</t>
+  </si>
+  <si>
+    <t>https://www.idealist.org/en/nonprofit-job/7eb39fa95bee4a8dae172b1382bc5b51-immigrants-rights-staff-attorney-or-senior-attorney-position-takeroot-justice-new-york</t>
+  </si>
+  <si>
+    <t>Interim Director, Human Resources and Administration</t>
+  </si>
+  <si>
+    <t>Careers In Nonprofits, Inc.</t>
+  </si>
+  <si>
+    <t>Part Time, Temporary</t>
+  </si>
+  <si>
+    <t>USD 60.00 - 62.00/hour</t>
+  </si>
+  <si>
+    <t>https://www.idealist.org/en/job/c33f8963945c44958a4976bbda1522dd-interim-director-human-resources-and-administration-careers-in-nonprofits-inc-san-francisco</t>
+  </si>
+  <si>
+    <t>Manager, Philanthropy Reporting and Projects</t>
+  </si>
+  <si>
+    <t>USD 85000.00 - 90000.00/year</t>
+  </si>
+  <si>
+    <t>Health Medicine, Women, Philanthropy</t>
+  </si>
+  <si>
+    <t>https://www.idealist.org/en/nonprofit-job/0a9e741d182e4358b606b5e531b36194-manager-philanthropy-reporting-and-projects-hadassah-wzoa-inc-new-york</t>
+  </si>
+  <si>
+    <t>Managing Director - Movement Labs</t>
+  </si>
+  <si>
+    <t>Movement Labs</t>
+  </si>
+  <si>
+    <t>USD 200000.00 - 250000.00/year</t>
+  </si>
+  <si>
+    <t>Job Workplace, Civic Engagement, Policy</t>
+  </si>
+  <si>
+    <t>https://www.idealist.org/en/job/65663b8b92d949298145224fe638ca18-managing-director-movement-labs-movement-labs-new-york</t>
+  </si>
+  <si>
+    <t>Membership Coordinator (4 Month Temporary)</t>
+  </si>
+  <si>
+    <t>The Choice Inc</t>
+  </si>
+  <si>
+    <t>USD 30.00 - 30.00/hour</t>
+  </si>
+  <si>
+    <t>Economic Development, Job Workplace, Entrepreneurship</t>
+  </si>
+  <si>
+    <t>https://www.idealist.org/en/job/45a67aee2c1542b1860b33e6610af51c-membership-coordinator-4-month-temporary-the-choice-inc-washington</t>
+  </si>
+  <si>
+    <t>Mental Health Counselor</t>
+  </si>
+  <si>
+    <t>Wafa House, Inc.</t>
+  </si>
+  <si>
+    <t>Woodland Park, New Jersey</t>
+  </si>
+  <si>
+    <t>Family, Mental Health</t>
+  </si>
+  <si>
+    <t>https://www.idealist.org/en/nonprofit-job/2b1be6a33c9b4e4bb1112bdc913c59ec-mental-health-counselor-wafa-house-inc-woodland-park</t>
+  </si>
+  <si>
+    <t>National Advocacy Director</t>
+  </si>
+  <si>
+    <t>DC Vote</t>
+  </si>
+  <si>
+    <t>USD 100000.00 - 130000.00/year</t>
+  </si>
+  <si>
+    <t>Civic Engagement, Community Development, Education</t>
+  </si>
+  <si>
+    <t>https://www.idealist.org/en/nonprofit-job/2f0f7f0133cb45cc9ed77160f4629d1d-national-advocacy-director-dc-vote-washington</t>
+  </si>
+  <si>
+    <t>NexGen Philanthropy Manager</t>
+  </si>
+  <si>
+    <t>USD 70000.00 - 85000.00/year</t>
+  </si>
+  <si>
+    <t>https://www.idealist.org/en/nonprofit-job/029aa00a7a854e9b949b9eeca4d52f44-nexgen-philanthropy-manager-jewish-federation-of-greater-houston-houston</t>
+  </si>
+  <si>
+    <t>Office Manager</t>
+  </si>
+  <si>
+    <t>Council of New Jersey Grantmakers</t>
+  </si>
+  <si>
+    <t>Remote (New Jersey)</t>
+  </si>
+  <si>
+    <t>USD 25.65 - 28.20/hour</t>
+  </si>
+  <si>
+    <t>Philanthropy</t>
+  </si>
+  <si>
+    <t>https://www.idealist.org/en/nonprofit-job/cb29ac1f8cba438597430a3828ed08cb-office-manager-council-of-new-jersey-grantmakers-ewing</t>
+  </si>
+  <si>
+    <t>Paralegal</t>
+  </si>
+  <si>
+    <t>USD 70000.00 - 75000.00/year</t>
+  </si>
+  <si>
+    <t>https://www.idealist.org/en/nonprofit-job/5b125c82b25c49c494fbe131c6131bfb-paralegal-hadassah-wzoa-inc-new-york</t>
+  </si>
+  <si>
+    <t>Paralegal (full-time) at Law Firm Exclusively Serving Nonprofit/Tax-Exempt Organizations</t>
+  </si>
+  <si>
+    <t>Cheshire Law Group</t>
+  </si>
+  <si>
+    <t>Legal Assistance</t>
+  </si>
+  <si>
+    <t>https://www.idealist.org/en/consultant-job/26897cef5e54417cb8c5ad5840fb8dde-paralegal-full-time-at-law-firm-exclusively-serving-nonprofittax-exempt-organizations-cheshire-law-group-philadelphia</t>
+  </si>
+  <si>
+    <t>Payroll and Benefits Manager</t>
+  </si>
+  <si>
+    <t>Hispanic Federation</t>
+  </si>
+  <si>
+    <t>USD 55000.00 - 65000.00/year</t>
+  </si>
+  <si>
+    <t>https://www.idealist.org/en/nonprofit-job/def19effe3a24a64aa5b1815b8132fd2-payroll-and-benefits-manager-hispanic-federation-new-york</t>
+  </si>
+  <si>
+    <t>Philanthropy Administrator</t>
+  </si>
+  <si>
+    <t>USD 60000.00 - 75000.00/year</t>
+  </si>
+  <si>
+    <t>https://www.idealist.org/en/nonprofit-job/82add784e945475dbf2a6691008b4042-philanthropy-administrator-jewish-federation-of-greater-houston-houston</t>
+  </si>
+  <si>
+    <t>Philanthropy Officer</t>
+  </si>
+  <si>
+    <t>USD 85000.00 - 95000.00/year</t>
+  </si>
+  <si>
+    <t>https://www.idealist.org/en/nonprofit-job/5fa7315ac87d40e7b3440c475a144034-philanthropy-officer-jewish-federation-of-greater-houston-houston</t>
+  </si>
+  <si>
+    <t>President</t>
+  </si>
+  <si>
+    <t>Endowment for Health</t>
+  </si>
+  <si>
+    <t>Concord, New Hampshire</t>
+  </si>
+  <si>
+    <t>USD 275000.00 - 300000.00/year</t>
+  </si>
+  <si>
+    <t>https://www.idealist.org/en/job/eca1662bdb084451bc977c942899d5bf-president-endowment-for-health-concord</t>
+  </si>
+  <si>
+    <t>Press Officer</t>
+  </si>
+  <si>
+    <t>If/When/How: Lawyering for Reproductive Justice</t>
+  </si>
+  <si>
+    <t>USD 72000.00 - 77000.00/year</t>
+  </si>
+  <si>
+    <t>Reproductive Health Rights, Family, Legal Assistance</t>
+  </si>
+  <si>
+    <t>https://www.idealist.org/en/nonprofit-job/de2864b7133642589f1814223243a085-press-officer-ifwhenhow-lawyering-for-reproductive-justice-chicago</t>
+  </si>
+  <si>
+    <t>Principal Campus Counsel</t>
+  </si>
+  <si>
+    <t>University of California, Los Angeles</t>
+  </si>
+  <si>
+    <t>Los Angeles, California</t>
+  </si>
+  <si>
+    <t>USD 181400.00 - 366600.00/year</t>
+  </si>
+  <si>
+    <t>Education</t>
+  </si>
+  <si>
+    <t>https://www.idealist.org/en/job/4985397a84a24abe98bee0f65790677d-principal-campus-counsel-university-of-california-los-angeles-los-angeles</t>
+  </si>
+  <si>
+    <t>Profesional para Trabajo Comunitario con Familias | Filial Mar del Plata</t>
+  </si>
+  <si>
+    <t>Aldeas Infantiles SOS Argentina</t>
+  </si>
+  <si>
+    <t>Mar del Plata, Provincia de Buenos Aires, AR</t>
+  </si>
+  <si>
+    <t>Children Youth, Family, Community Development</t>
+  </si>
+  <si>
+    <t>https://www.idealist.org/en/nonprofit-job/f791e9d540ef427aa2da00b73a53e720-profesional-para-trabajo-comunitario-con-familias-filial-mar-del-plata-aldeas-infantiles-sos-argentina-mar-del-plata</t>
+  </si>
+  <si>
+    <t>Program Coordinator</t>
+  </si>
+  <si>
+    <t>Baby2Baby</t>
+  </si>
+  <si>
+    <t>Culver City, California</t>
+  </si>
+  <si>
+    <t>USD 24.00 - 26.00/hour</t>
+  </si>
+  <si>
+    <t>Children Youth</t>
+  </si>
+  <si>
+    <t>https://www.idealist.org/en/nonprofit-job/1b2ed7928df0453e967166f9da87e6b7-program-coordinator-baby2baby-culver-city</t>
+  </si>
+  <si>
+    <t>Program Manager - Mental Health Education &amp; Growth</t>
+  </si>
+  <si>
+    <t>Mental Health Collaborative, Inc.</t>
+  </si>
+  <si>
+    <t>USD 65000.00 - 75000.00/year</t>
+  </si>
+  <si>
+    <t>Education, Family, Mental Health</t>
+  </si>
+  <si>
+    <t>https://www.idealist.org/en/nonprofit-job/c455c9ac89b94111b9c6ac866a274dc3-program-manager-mental-health-education-growth-mental-health-collaborative-inc-hopkinton</t>
+  </si>
+  <si>
+    <t>Project Manager</t>
+  </si>
+  <si>
+    <t>Northbrook, Illinois</t>
+  </si>
+  <si>
+    <t>USD 63000.00 - 67000.00/year</t>
+  </si>
+  <si>
+    <t>https://www.idealist.org/en/nonprofit-job/de76d8d61b734b14b7e7a475f348fe41-project-manager-hadassah-wzoa-inc-northbrook</t>
+  </si>
+  <si>
+    <t>Public Policy and Advocacy Associate</t>
+  </si>
+  <si>
+    <t>CT Community Nonprofit Alliance, Inc.</t>
+  </si>
+  <si>
+    <t>Rocky Hill, Connecticut</t>
+  </si>
+  <si>
+    <t>Disability, Arts Music, Housing Homelessness</t>
+  </si>
+  <si>
+    <t>https://www.idealist.org/en/nonprofit-job/e56d9f7595ae4879a2fdbc1946c4147c-public-policy-and-advocacy-associate-ct-community-nonprofit-alliance-inc-rocky-hill</t>
+  </si>
+  <si>
+    <t>Salt Watch Coordinator</t>
+  </si>
+  <si>
+    <t>Izaak Walton League of America</t>
+  </si>
+  <si>
+    <t>Gaithersburg, Maryland</t>
+  </si>
+  <si>
+    <t>USD 46000.00 - 50000.00/year</t>
+  </si>
+  <si>
+    <t>Environment, Volunteering, Water Sanitation</t>
+  </si>
+  <si>
+    <t>https://www.idealist.org/en/nonprofit-job/3f681eba0fec455eb244f9fefb0cab52-salt-watch-coordinator-izaak-walton-league-of-america-gaithersburg</t>
+  </si>
+  <si>
+    <t>Senior Communications Manager</t>
+  </si>
+  <si>
+    <t>Ten Strands</t>
+  </si>
+  <si>
+    <t>Remote (California)</t>
+  </si>
+  <si>
+    <t>Environment, Children Youth, Education</t>
+  </si>
+  <si>
+    <t>https://www.idealist.org/en/nonprofit-job/b792deed69b24e2ba16bac108848475f-senior-communications-manager-ten-strands-san-francisco</t>
+  </si>
+  <si>
+    <t>Senior Grants &amp; Contracts Analyst</t>
+  </si>
+  <si>
+    <t>Rural Community Assistance Partnership,Inc</t>
+  </si>
+  <si>
+    <t>USD 89546.00 - 109329.00/year</t>
+  </si>
+  <si>
+    <t>Community Development, Disaster Relief, Environment</t>
+  </si>
+  <si>
+    <t>https://www.idealist.org/en/nonprofit-job/89231fa18c9f429d893460a3a81247d6-senior-grants-contracts-analyst-rural-community-assistance-partnershipinc-washington</t>
+  </si>
+  <si>
+    <t>Senior Manager, Corporate Partnerships &amp; Communications</t>
+  </si>
+  <si>
+    <t>Bonneville Environmental Foundation (BEF)</t>
+  </si>
+  <si>
+    <t>Remote (Oregon)</t>
+  </si>
+  <si>
+    <t>USD 80000.00 - 92000.00/year</t>
+  </si>
+  <si>
+    <t>Climate Change, Environment, Media</t>
+  </si>
+  <si>
+    <t>https://www.idealist.org/en/nonprofit-job/c7c42f6b07a84d1682cbec5e523fc084-senior-manager-corporate-partnerships-communications-bonneville-environmental-foundation-bef-portland</t>
+  </si>
+  <si>
+    <t>Senior Manager, Insights and Analytics</t>
+  </si>
+  <si>
+    <t>StriveTogether, Inc.</t>
+  </si>
+  <si>
+    <t>USD 83000.00 - 93000.00/year</t>
+  </si>
+  <si>
+    <t>Civic Engagement, Education, Poverty</t>
+  </si>
+  <si>
+    <t>https://www.idealist.org/en/nonprofit-job/4417d14f4ddb48a6affa6402210955f8-senior-manager-insights-and-analytics-strivetogether-inc-cincinnati</t>
+  </si>
+  <si>
+    <t>Senior Program Officer, TCU Computer Science Programs</t>
+  </si>
+  <si>
+    <t>American Indian College Fund</t>
+  </si>
+  <si>
+    <t>USD 86540.00 - 96276.00/year</t>
+  </si>
+  <si>
+    <t>Education, Philanthropy</t>
+  </si>
+  <si>
+    <t>https://www.idealist.org/en/nonprofit-job/e26398e0b2384348b6ee1e8e53efb16b-senior-program-officer-tcu-computer-science-programs-american-indian-college-fund-denver</t>
+  </si>
+  <si>
+    <t>Senior Staff Attorney</t>
+  </si>
+  <si>
+    <t>Texas Defender Service</t>
+  </si>
+  <si>
+    <t>Austin, Texas</t>
+  </si>
+  <si>
+    <t>USD 95000.00 - 110000.00/year</t>
+  </si>
+  <si>
+    <t>https://www.idealist.org/en/nonprofit-job/4881e273a0fa4bccaa1a9b7c930f11c1-senior-staff-attorney-texas-defender-service-austin</t>
+  </si>
+  <si>
+    <t>Senior Vice President</t>
+  </si>
+  <si>
+    <t>617MediaGroup</t>
+  </si>
+  <si>
+    <t>USD 117448.00 - 129301.00/year</t>
+  </si>
+  <si>
+    <t>https://www.idealist.org/en/consultant-job/29d7fdf747d64bbf903c8f727cb7583c-senior-vice-president-617mediagroup-boston</t>
+  </si>
+  <si>
+    <t>Staff Accountant</t>
+  </si>
+  <si>
+    <t>Fair Labor Association</t>
+  </si>
+  <si>
+    <t>USD 59000.00 - 63000.00/year</t>
+  </si>
+  <si>
+    <t>Human Rights Civil Liberties</t>
+  </si>
+  <si>
+    <t>https://www.idealist.org/en/nonprofit-job/1252cea818134bb59aaaba6b56d3e186-staff-accountant-fair-labor-association-washington</t>
+  </si>
+  <si>
+    <t>Family, Legal Assistance</t>
+  </si>
+  <si>
+    <t>https://www.idealist.org/en/nonprofit-job/fe60e60144554603aadc728f6b25d003-staff-attorney-wafa-house-inc-woodland-park</t>
+  </si>
+  <si>
+    <t>Staff Attorney – Housing and Disability Advocacy Program (HDAP)</t>
+  </si>
+  <si>
+    <t>LEGAL AID SOCIETY OF SAN BERNARDINO</t>
+  </si>
+  <si>
+    <t>San Bernadino, CA</t>
+  </si>
+  <si>
+    <t>USD 75000.00 - 90000.00/year</t>
+  </si>
+  <si>
+    <t>https://www.idealist.org/en/job/b3b1eaf287804535b070f8bf5627c63d-staff-attorney-housing-and-disability-advocacy-program-hdap-legal-aid-society-of-san-bernardino-san-bernadino</t>
+  </si>
+  <si>
+    <t>Staff Attorney – Housing or Family (Hybrid)</t>
+  </si>
+  <si>
+    <t>USD 75000.00 - 95000.00/year</t>
+  </si>
+  <si>
+    <t>https://www.idealist.org/en/job/0fd17fa61d484b28a3397c5cdf1b6025-staff-attorney-housing-or-family-hybrid-legal-aid-society-of-san-bernardino-san-bernadino</t>
+  </si>
+  <si>
+    <t>Staff Attorney (Maryland)</t>
+  </si>
+  <si>
+    <t>Council on American-Islamic Relations - National Headquarters</t>
+  </si>
+  <si>
+    <t>Remote (Maryland)</t>
+  </si>
+  <si>
+    <t>USD 75000.00 - 83100.00/year</t>
+  </si>
+  <si>
+    <t>Civic Engagement, Education, Human Rights Civil Liberties</t>
+  </si>
+  <si>
+    <t>https://www.idealist.org/en/nonprofit-job/cba0978d07544708832580566f654a06-staff-attorney-maryland-council-on-american-islamic-relations-national-headquarters-washington</t>
+  </si>
+  <si>
+    <t>Staff Attorney, Bronx</t>
+  </si>
+  <si>
+    <t>The Children's Law Center NY</t>
+  </si>
+  <si>
+    <t>Bronx County, New York</t>
+  </si>
+  <si>
+    <t>USD 86700.00 - 140472.21/year</t>
+  </si>
+  <si>
+    <t>https://www.idealist.org/en/nonprofit-job/4c9fc6cc1be3445b9bab99fd1381e937-staff-attorney-bronx-the-childrens-law-center-ny-bronx-county</t>
+  </si>
+  <si>
+    <t>Staff Attorney, Brooklyn</t>
+  </si>
+  <si>
+    <t>Kings County, New York</t>
+  </si>
+  <si>
+    <t>https://www.idealist.org/en/nonprofit-job/94ffa68f630246e9bb5c16e5838ecb02-staff-attorney-brooklyn-the-childrens-law-center-ny-kings-county</t>
+  </si>
+  <si>
+    <t>Statehood Field Director/ Lead Organizer</t>
+  </si>
+  <si>
+    <t>Civic Engagement, Community Development, Human Rights Civil Liberties</t>
+  </si>
+  <si>
+    <t>https://www.idealist.org/en/nonprofit-job/cb03091e68ba4f1da342290c0a616d08-statehood-field-director-lead-organizer-dc-vote-washington</t>
+  </si>
+  <si>
+    <t>Substance Use Disorder (SUD) Senior Community Outreach Specialist/Case Manager</t>
+  </si>
+  <si>
+    <t>Identity, Inc.</t>
+  </si>
+  <si>
+    <t>Derwood, Maryland</t>
+  </si>
+  <si>
+    <t>USD 26.44 - 26.44/hour</t>
+  </si>
+  <si>
+    <t>Children Youth, Substance Abuse Addiction</t>
+  </si>
+  <si>
+    <t>https://www.idealist.org/en/nonprofit-job/f15f9d737ffe4a8ea56d2a68925a492b-substance-use-disorder-sud-senior-community-outreach-specialistcase-manager-identity-inc-derwood</t>
+  </si>
+  <si>
+    <t>Substitute Teacher</t>
+  </si>
+  <si>
+    <t>https://www.idealist.org/en/nonprofit-job/c08dbdca552d444bb4f761bf5b3497b2-substitute-teacher-freedom-side-school-philadelphia</t>
+  </si>
+  <si>
+    <t>Supervisory Youth Development Representative</t>
+  </si>
+  <si>
+    <t>District of Columbia Department of Youth Rehabilitation Services</t>
+  </si>
+  <si>
+    <t>Laurel, Maryland</t>
+  </si>
+  <si>
+    <t>USD 73334.00 - 102667.00/year</t>
+  </si>
+  <si>
+    <t>Children Youth, Community Development, Crime Safety</t>
+  </si>
+  <si>
+    <t>https://www.idealist.org/en/government-job/7f4bfc93351e48de9529b11f60a0f435-supervisory-youth-development-representative-district-of-columbia-department-of-youth-rehabilitation-services-laurel</t>
+  </si>
+  <si>
+    <t>Systems and Data Integrity Specialist</t>
+  </si>
+  <si>
+    <t>Jack Kent Cooke Foundation</t>
+  </si>
+  <si>
+    <t>Leesburg, Virginia</t>
+  </si>
+  <si>
+    <t>https://www.idealist.org/en/nonprofit-job/84b5e6d7471246ac998951043f45833b-systems-and-data-integrity-specialist-jack-kent-cooke-foundation-leesburg</t>
+  </si>
+  <si>
+    <t>Teaching Fellow/Teacher</t>
+  </si>
+  <si>
+    <t>City Teaching Alliance</t>
+  </si>
+  <si>
+    <t>USD 40000.00 - 60000.00/year</t>
+  </si>
+  <si>
+    <t>https://www.idealist.org/en/nonprofit-job/c37cec38f9234fee99494075b487e0a6-teaching-fellowteacher-city-teaching-alliance-philadelphia</t>
+  </si>
+  <si>
+    <t>Baltimore County, Maryland</t>
+  </si>
+  <si>
+    <t>https://www.idealist.org/en/nonprofit-job/b505f3e6a6d24c78b0008b02576250c7-teaching-fellowteacher-city-teaching-alliance-baltimore-county</t>
+  </si>
+  <si>
+    <t>Dallas County, Texas</t>
+  </si>
+  <si>
+    <t>https://www.idealist.org/en/nonprofit-job/6389b26988da4cea84b0b71eac32585d-teaching-fellowteacher-city-teaching-alliance-dallas-county</t>
+  </si>
+  <si>
+    <t>https://www.idealist.org/en/nonprofit-job/1178265cc3484f97896a29e7558858b5-teaching-fellowteacher-city-teaching-alliance-washington</t>
+  </si>
+  <si>
+    <t>Vice President</t>
+  </si>
+  <si>
+    <t>USD 98090.00 - 110944.00/year</t>
+  </si>
+  <si>
+    <t>https://www.idealist.org/en/consultant-job/6cf6edb7238c403e9702c5f657686935-vice-president-617mediagroup-boston</t>
+  </si>
+  <si>
+    <t>Vice President, Programs</t>
+  </si>
+  <si>
+    <t>The Housing Collective</t>
+  </si>
+  <si>
+    <t>Bridgeport, Connecticut</t>
+  </si>
+  <si>
+    <t>USD 135000.00 - 155000.00/year</t>
+  </si>
+  <si>
+    <t>Job Workplace, Housing Homelessness</t>
+  </si>
+  <si>
+    <t>https://www.idealist.org/en/job/112ed6d73ce24517a980f5c246919e0c-vice-president-programs-the-housing-collective-bridgeport</t>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" mc:Ignorable="x14ac x16r2">
-  <fonts count="2" x14ac:knownFonts="1">
+  <fonts count="3" x14ac:knownFonts="1">
     <font>
       <color theme="1"/>
       <family val="2"/>
@@ -54,6 +2133,10 @@
     </font>
     <font>
       <b/>
+    </font>
+    <font>
+      <u/>
+      <color rgb="FF1155CC"/>
     </font>
   </fonts>
   <fills count="2">
@@ -76,9 +2159,10 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="2">
+  <cellXfs count="3">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -418,7 +2502,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <dimension ref="A1:H1"/>
+  <dimension ref="A1:H51"/>
   <sheetFormatPr defaultRowHeight="15" outlineLevelRow="0" outlineLevelCol="0" x14ac:dyDescent="55"/>
   <cols>
     <col min="1" max="1" width="48" customWidth="1"/>
@@ -457,8 +2541,1210 @@
         <v>7</v>
       </c>
     </row>
+    <row r="2" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A2" t="s">
+        <v>8</v>
+      </c>
+      <c r="B2" t="s">
+        <v>9</v>
+      </c>
+      <c r="C2" t="s">
+        <v>10</v>
+      </c>
+      <c r="D2" t="s">
+        <v>11</v>
+      </c>
+      <c r="E2" t="s">
+        <v>12</v>
+      </c>
+      <c r="F2" t="s">
+        <v>13</v>
+      </c>
+      <c r="H2" s="2" t="s">
+        <v>14</v>
+      </c>
+    </row>
+    <row r="3" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A3" t="s">
+        <v>15</v>
+      </c>
+      <c r="B3" t="s">
+        <v>16</v>
+      </c>
+      <c r="C3" t="s">
+        <v>17</v>
+      </c>
+      <c r="D3" t="s">
+        <v>18</v>
+      </c>
+      <c r="E3" t="s">
+        <v>19</v>
+      </c>
+      <c r="F3" t="s">
+        <v>20</v>
+      </c>
+      <c r="H3" s="2" t="s">
+        <v>21</v>
+      </c>
+    </row>
+    <row r="4" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A4" t="s">
+        <v>22</v>
+      </c>
+      <c r="B4" t="s">
+        <v>23</v>
+      </c>
+      <c r="C4" t="s">
+        <v>24</v>
+      </c>
+      <c r="D4" t="s">
+        <v>11</v>
+      </c>
+      <c r="E4" t="s">
+        <v>25</v>
+      </c>
+      <c r="F4" t="s">
+        <v>13</v>
+      </c>
+      <c r="H4" s="2" t="s">
+        <v>26</v>
+      </c>
+    </row>
+    <row r="5" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A5" t="s">
+        <v>27</v>
+      </c>
+      <c r="B5" t="s">
+        <v>28</v>
+      </c>
+      <c r="C5" t="s">
+        <v>29</v>
+      </c>
+      <c r="D5" t="s">
+        <v>30</v>
+      </c>
+      <c r="E5" t="s">
+        <v>31</v>
+      </c>
+      <c r="F5" t="s">
+        <v>32</v>
+      </c>
+      <c r="H5" s="2" t="s">
+        <v>33</v>
+      </c>
+    </row>
+    <row r="6" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A6" t="s">
+        <v>34</v>
+      </c>
+      <c r="B6" t="s">
+        <v>35</v>
+      </c>
+      <c r="C6" t="s">
+        <v>36</v>
+      </c>
+      <c r="D6" t="s">
+        <v>11</v>
+      </c>
+      <c r="E6" t="s">
+        <v>37</v>
+      </c>
+      <c r="F6" t="s">
+        <v>38</v>
+      </c>
+      <c r="H6" s="2" t="s">
+        <v>39</v>
+      </c>
+    </row>
+    <row r="7" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A7" t="s">
+        <v>40</v>
+      </c>
+      <c r="B7" t="s">
+        <v>41</v>
+      </c>
+      <c r="C7" t="s">
+        <v>42</v>
+      </c>
+      <c r="D7" t="s">
+        <v>11</v>
+      </c>
+      <c r="E7" t="s">
+        <v>43</v>
+      </c>
+      <c r="F7" t="s">
+        <v>44</v>
+      </c>
+      <c r="H7" s="2" t="s">
+        <v>45</v>
+      </c>
+    </row>
+    <row r="8" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A8" t="s">
+        <v>46</v>
+      </c>
+      <c r="B8" t="s">
+        <v>47</v>
+      </c>
+      <c r="C8" t="s">
+        <v>48</v>
+      </c>
+      <c r="D8" t="s">
+        <v>18</v>
+      </c>
+      <c r="E8" t="s">
+        <v>49</v>
+      </c>
+      <c r="F8" t="s">
+        <v>20</v>
+      </c>
+      <c r="H8" s="2" t="s">
+        <v>50</v>
+      </c>
+    </row>
+    <row r="9" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A9" t="s">
+        <v>51</v>
+      </c>
+      <c r="B9" t="s">
+        <v>52</v>
+      </c>
+      <c r="C9" t="s">
+        <v>53</v>
+      </c>
+      <c r="D9" t="s">
+        <v>11</v>
+      </c>
+      <c r="E9" t="s">
+        <v>54</v>
+      </c>
+      <c r="F9" t="s">
+        <v>55</v>
+      </c>
+      <c r="H9" s="2" t="s">
+        <v>56</v>
+      </c>
+    </row>
+    <row r="10" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A10" t="s">
+        <v>57</v>
+      </c>
+      <c r="B10" t="s">
+        <v>58</v>
+      </c>
+      <c r="C10" t="s">
+        <v>59</v>
+      </c>
+      <c r="D10" t="s">
+        <v>11</v>
+      </c>
+      <c r="E10" t="s">
+        <v>60</v>
+      </c>
+      <c r="F10" t="s">
+        <v>61</v>
+      </c>
+      <c r="H10" s="2" t="s">
+        <v>62</v>
+      </c>
+    </row>
+    <row r="11" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A11" t="s">
+        <v>63</v>
+      </c>
+      <c r="B11" t="s">
+        <v>23</v>
+      </c>
+      <c r="C11" t="s">
+        <v>64</v>
+      </c>
+      <c r="D11" t="s">
+        <v>11</v>
+      </c>
+      <c r="E11" t="s">
+        <v>65</v>
+      </c>
+      <c r="F11" t="s">
+        <v>66</v>
+      </c>
+      <c r="H11" s="2" t="s">
+        <v>67</v>
+      </c>
+    </row>
+    <row r="12" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A12" t="s">
+        <v>68</v>
+      </c>
+      <c r="B12" t="s">
+        <v>69</v>
+      </c>
+      <c r="C12" t="s">
+        <v>70</v>
+      </c>
+      <c r="D12" t="s">
+        <v>11</v>
+      </c>
+      <c r="E12" t="s">
+        <v>71</v>
+      </c>
+      <c r="F12" t="s">
+        <v>72</v>
+      </c>
+      <c r="H12" s="2" t="s">
+        <v>73</v>
+      </c>
+    </row>
+    <row r="13" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A13" t="s">
+        <v>74</v>
+      </c>
+      <c r="B13" t="s">
+        <v>75</v>
+      </c>
+      <c r="C13" t="s">
+        <v>76</v>
+      </c>
+      <c r="D13" t="s">
+        <v>11</v>
+      </c>
+      <c r="E13" t="s">
+        <v>77</v>
+      </c>
+      <c r="F13" t="s">
+        <v>78</v>
+      </c>
+      <c r="H13" s="2" t="s">
+        <v>79</v>
+      </c>
+    </row>
+    <row r="14" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A14" t="s">
+        <v>80</v>
+      </c>
+      <c r="B14" t="s">
+        <v>81</v>
+      </c>
+      <c r="C14" t="s">
+        <v>29</v>
+      </c>
+      <c r="D14" t="s">
+        <v>11</v>
+      </c>
+      <c r="E14" t="s">
+        <v>82</v>
+      </c>
+      <c r="F14" t="s">
+        <v>83</v>
+      </c>
+      <c r="H14" s="2" t="s">
+        <v>84</v>
+      </c>
+    </row>
+    <row r="15" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A15" t="s">
+        <v>85</v>
+      </c>
+      <c r="B15" t="s">
+        <v>86</v>
+      </c>
+      <c r="C15" t="s">
+        <v>87</v>
+      </c>
+      <c r="D15" t="s">
+        <v>11</v>
+      </c>
+      <c r="E15" t="s">
+        <v>88</v>
+      </c>
+      <c r="F15" t="s">
+        <v>89</v>
+      </c>
+      <c r="H15" s="2" t="s">
+        <v>90</v>
+      </c>
+    </row>
+    <row r="16" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A16" t="s">
+        <v>91</v>
+      </c>
+      <c r="B16" t="s">
+        <v>16</v>
+      </c>
+      <c r="C16" t="s">
+        <v>17</v>
+      </c>
+      <c r="D16" t="s">
+        <v>18</v>
+      </c>
+      <c r="E16" t="s">
+        <v>92</v>
+      </c>
+      <c r="F16" t="s">
+        <v>20</v>
+      </c>
+      <c r="H16" s="2" t="s">
+        <v>93</v>
+      </c>
+    </row>
+    <row r="17" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A17" t="s">
+        <v>94</v>
+      </c>
+      <c r="B17" t="s">
+        <v>16</v>
+      </c>
+      <c r="C17" t="s">
+        <v>17</v>
+      </c>
+      <c r="D17" t="s">
+        <v>18</v>
+      </c>
+      <c r="E17" t="s">
+        <v>19</v>
+      </c>
+      <c r="F17" t="s">
+        <v>20</v>
+      </c>
+      <c r="H17" s="2" t="s">
+        <v>95</v>
+      </c>
+    </row>
+    <row r="18" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A18" t="s">
+        <v>96</v>
+      </c>
+      <c r="B18" t="s">
+        <v>97</v>
+      </c>
+      <c r="C18" t="s">
+        <v>98</v>
+      </c>
+      <c r="D18" t="s">
+        <v>11</v>
+      </c>
+      <c r="E18" t="s">
+        <v>99</v>
+      </c>
+      <c r="F18" t="s">
+        <v>100</v>
+      </c>
+      <c r="H18" s="2" t="s">
+        <v>101</v>
+      </c>
+    </row>
+    <row r="19" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A19" t="s">
+        <v>102</v>
+      </c>
+      <c r="B19" t="s">
+        <v>103</v>
+      </c>
+      <c r="C19" t="s">
+        <v>104</v>
+      </c>
+      <c r="D19" t="s">
+        <v>11</v>
+      </c>
+      <c r="E19" t="s">
+        <v>105</v>
+      </c>
+      <c r="F19" t="s">
+        <v>106</v>
+      </c>
+      <c r="H19" s="2" t="s">
+        <v>107</v>
+      </c>
+    </row>
+    <row r="20" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A20" t="s">
+        <v>108</v>
+      </c>
+      <c r="B20" t="s">
+        <v>109</v>
+      </c>
+      <c r="C20" t="s">
+        <v>110</v>
+      </c>
+      <c r="D20" t="s">
+        <v>11</v>
+      </c>
+      <c r="E20" t="s">
+        <v>111</v>
+      </c>
+      <c r="F20" t="s">
+        <v>13</v>
+      </c>
+      <c r="H20" s="2" t="s">
+        <v>112</v>
+      </c>
+    </row>
+    <row r="21" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A21" t="s">
+        <v>113</v>
+      </c>
+      <c r="B21" t="s">
+        <v>35</v>
+      </c>
+      <c r="C21" t="s">
+        <v>114</v>
+      </c>
+      <c r="D21" t="s">
+        <v>11</v>
+      </c>
+      <c r="E21" t="s">
+        <v>115</v>
+      </c>
+      <c r="F21" t="s">
+        <v>38</v>
+      </c>
+      <c r="H21" s="2" t="s">
+        <v>116</v>
+      </c>
+    </row>
+    <row r="22" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A22" t="s">
+        <v>117</v>
+      </c>
+      <c r="B22" t="s">
+        <v>118</v>
+      </c>
+      <c r="C22" t="s">
+        <v>119</v>
+      </c>
+      <c r="D22" t="s">
+        <v>11</v>
+      </c>
+      <c r="E22" t="s">
+        <v>120</v>
+      </c>
+      <c r="F22" t="s">
+        <v>121</v>
+      </c>
+      <c r="H22" s="2" t="s">
+        <v>122</v>
+      </c>
+    </row>
+    <row r="23" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A23" t="s">
+        <v>123</v>
+      </c>
+      <c r="B23" t="s">
+        <v>124</v>
+      </c>
+      <c r="C23" t="s">
+        <v>125</v>
+      </c>
+      <c r="D23" t="s">
+        <v>11</v>
+      </c>
+      <c r="E23" t="s">
+        <v>126</v>
+      </c>
+      <c r="F23" t="s">
+        <v>72</v>
+      </c>
+      <c r="H23" s="2" t="s">
+        <v>127</v>
+      </c>
+    </row>
+    <row r="24" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A24" t="s">
+        <v>128</v>
+      </c>
+      <c r="B24" t="s">
+        <v>129</v>
+      </c>
+      <c r="C24" t="s">
+        <v>130</v>
+      </c>
+      <c r="D24" t="s">
+        <v>11</v>
+      </c>
+      <c r="E24" t="s">
+        <v>131</v>
+      </c>
+      <c r="F24" t="s">
+        <v>55</v>
+      </c>
+      <c r="H24" s="2" t="s">
+        <v>132</v>
+      </c>
+    </row>
+    <row r="25" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A25" t="s">
+        <v>133</v>
+      </c>
+      <c r="B25" t="s">
+        <v>35</v>
+      </c>
+      <c r="C25" t="s">
+        <v>134</v>
+      </c>
+      <c r="D25" t="s">
+        <v>11</v>
+      </c>
+      <c r="E25" t="s">
+        <v>135</v>
+      </c>
+      <c r="F25" t="s">
+        <v>38</v>
+      </c>
+      <c r="H25" s="2" t="s">
+        <v>136</v>
+      </c>
+    </row>
+    <row r="26" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A26" t="s">
+        <v>137</v>
+      </c>
+      <c r="B26" t="s">
+        <v>138</v>
+      </c>
+      <c r="C26" t="s">
+        <v>139</v>
+      </c>
+      <c r="D26" t="s">
+        <v>11</v>
+      </c>
+      <c r="E26" t="s">
+        <v>140</v>
+      </c>
+      <c r="F26" t="s">
+        <v>141</v>
+      </c>
+      <c r="H26" s="2" t="s">
+        <v>142</v>
+      </c>
+    </row>
+    <row r="27" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A27" t="s">
+        <v>143</v>
+      </c>
+      <c r="B27" t="s">
+        <v>144</v>
+      </c>
+      <c r="C27" t="s">
+        <v>145</v>
+      </c>
+      <c r="D27" t="s">
+        <v>11</v>
+      </c>
+      <c r="E27" t="s">
+        <v>146</v>
+      </c>
+      <c r="F27" t="s">
+        <v>147</v>
+      </c>
+      <c r="H27" s="2" t="s">
+        <v>148</v>
+      </c>
+    </row>
+    <row r="28" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A28" t="s">
+        <v>149</v>
+      </c>
+      <c r="B28" t="s">
+        <v>150</v>
+      </c>
+      <c r="C28" t="s">
+        <v>151</v>
+      </c>
+      <c r="D28" t="s">
+        <v>30</v>
+      </c>
+      <c r="E28" t="s">
+        <v>152</v>
+      </c>
+      <c r="F28" t="s">
+        <v>153</v>
+      </c>
+      <c r="H28" s="2" t="s">
+        <v>154</v>
+      </c>
+    </row>
+    <row r="29" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A29" t="s">
+        <v>155</v>
+      </c>
+      <c r="B29" t="s">
+        <v>156</v>
+      </c>
+      <c r="C29" t="s">
+        <v>157</v>
+      </c>
+      <c r="D29" t="s">
+        <v>11</v>
+      </c>
+      <c r="E29" t="s">
+        <v>158</v>
+      </c>
+      <c r="F29" t="s">
+        <v>159</v>
+      </c>
+      <c r="H29" s="2" t="s">
+        <v>160</v>
+      </c>
+    </row>
+    <row r="30" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A30" t="s">
+        <v>161</v>
+      </c>
+      <c r="B30" t="s">
+        <v>162</v>
+      </c>
+      <c r="C30" t="s">
+        <v>163</v>
+      </c>
+      <c r="D30" t="s">
+        <v>11</v>
+      </c>
+      <c r="E30" t="s">
+        <v>164</v>
+      </c>
+      <c r="F30" t="s">
+        <v>165</v>
+      </c>
+      <c r="H30" s="2" t="s">
+        <v>166</v>
+      </c>
+    </row>
+    <row r="31" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A31" t="s">
+        <v>167</v>
+      </c>
+      <c r="B31" t="s">
+        <v>168</v>
+      </c>
+      <c r="C31" t="s">
+        <v>169</v>
+      </c>
+      <c r="D31" t="s">
+        <v>30</v>
+      </c>
+      <c r="E31" t="s">
+        <v>170</v>
+      </c>
+      <c r="F31" t="s">
+        <v>78</v>
+      </c>
+      <c r="H31" s="2" t="s">
+        <v>171</v>
+      </c>
+    </row>
+    <row r="32" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A32" t="s">
+        <v>172</v>
+      </c>
+      <c r="B32" t="s">
+        <v>173</v>
+      </c>
+      <c r="C32" t="s">
+        <v>174</v>
+      </c>
+      <c r="D32" t="s">
+        <v>30</v>
+      </c>
+      <c r="E32" t="s">
+        <v>175</v>
+      </c>
+      <c r="F32" t="s">
+        <v>176</v>
+      </c>
+      <c r="H32" s="2" t="s">
+        <v>177</v>
+      </c>
+    </row>
+    <row r="33" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A33" t="s">
+        <v>178</v>
+      </c>
+      <c r="B33" t="s">
+        <v>179</v>
+      </c>
+      <c r="C33" t="s">
+        <v>180</v>
+      </c>
+      <c r="D33" t="s">
+        <v>11</v>
+      </c>
+      <c r="E33" t="s">
+        <v>181</v>
+      </c>
+      <c r="F33" t="s">
+        <v>182</v>
+      </c>
+      <c r="H33" s="2" t="s">
+        <v>183</v>
+      </c>
+    </row>
+    <row r="34" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A34" t="s">
+        <v>184</v>
+      </c>
+      <c r="B34" t="s">
+        <v>185</v>
+      </c>
+      <c r="C34" t="s">
+        <v>186</v>
+      </c>
+      <c r="D34" t="s">
+        <v>11</v>
+      </c>
+      <c r="E34" t="s">
+        <v>187</v>
+      </c>
+      <c r="F34" t="s">
+        <v>32</v>
+      </c>
+      <c r="H34" s="2" t="s">
+        <v>188</v>
+      </c>
+    </row>
+    <row r="35" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A35" t="s">
+        <v>189</v>
+      </c>
+      <c r="B35" t="s">
+        <v>190</v>
+      </c>
+      <c r="C35" t="s">
+        <v>191</v>
+      </c>
+      <c r="D35" t="s">
+        <v>11</v>
+      </c>
+      <c r="E35" t="s">
+        <v>192</v>
+      </c>
+      <c r="F35" t="s">
+        <v>193</v>
+      </c>
+      <c r="H35" s="2" t="s">
+        <v>194</v>
+      </c>
+    </row>
+    <row r="36" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A36" t="s">
+        <v>195</v>
+      </c>
+      <c r="B36" t="s">
+        <v>196</v>
+      </c>
+      <c r="C36" t="s">
+        <v>197</v>
+      </c>
+      <c r="D36" t="s">
+        <v>11</v>
+      </c>
+      <c r="E36" t="s">
+        <v>198</v>
+      </c>
+      <c r="F36" t="s">
+        <v>199</v>
+      </c>
+      <c r="H36" s="2" t="s">
+        <v>200</v>
+      </c>
+    </row>
+    <row r="37" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A37" t="s">
+        <v>201</v>
+      </c>
+      <c r="B37" t="s">
+        <v>196</v>
+      </c>
+      <c r="C37" t="s">
+        <v>202</v>
+      </c>
+      <c r="D37" t="s">
+        <v>30</v>
+      </c>
+      <c r="E37" t="s">
+        <v>203</v>
+      </c>
+      <c r="F37" t="s">
+        <v>204</v>
+      </c>
+      <c r="H37" s="2" t="s">
+        <v>205</v>
+      </c>
+    </row>
+    <row r="38" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A38" t="s">
+        <v>206</v>
+      </c>
+      <c r="B38" t="s">
+        <v>207</v>
+      </c>
+      <c r="C38" t="s">
+        <v>208</v>
+      </c>
+      <c r="D38" t="s">
+        <v>11</v>
+      </c>
+      <c r="E38" t="s">
+        <v>209</v>
+      </c>
+      <c r="F38" t="s">
+        <v>210</v>
+      </c>
+      <c r="H38" s="2" t="s">
+        <v>211</v>
+      </c>
+    </row>
+    <row r="39" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A39" t="s">
+        <v>212</v>
+      </c>
+      <c r="B39" t="s">
+        <v>213</v>
+      </c>
+      <c r="C39" t="s">
+        <v>214</v>
+      </c>
+      <c r="D39" t="s">
+        <v>11</v>
+      </c>
+      <c r="E39" t="s">
+        <v>215</v>
+      </c>
+      <c r="F39" t="s">
+        <v>216</v>
+      </c>
+      <c r="H39" s="2" t="s">
+        <v>217</v>
+      </c>
+    </row>
+    <row r="40" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A40" t="s">
+        <v>218</v>
+      </c>
+      <c r="B40" t="s">
+        <v>16</v>
+      </c>
+      <c r="C40" t="s">
+        <v>17</v>
+      </c>
+      <c r="D40" t="s">
+        <v>18</v>
+      </c>
+      <c r="E40" t="s">
+        <v>19</v>
+      </c>
+      <c r="F40" t="s">
+        <v>20</v>
+      </c>
+      <c r="H40" s="2" t="s">
+        <v>219</v>
+      </c>
+    </row>
+    <row r="41" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A41" t="s">
+        <v>220</v>
+      </c>
+      <c r="B41" t="s">
+        <v>16</v>
+      </c>
+      <c r="C41" t="s">
+        <v>221</v>
+      </c>
+      <c r="D41" t="s">
+        <v>18</v>
+      </c>
+      <c r="E41" t="s">
+        <v>19</v>
+      </c>
+      <c r="F41" t="s">
+        <v>20</v>
+      </c>
+      <c r="H41" s="2" t="s">
+        <v>222</v>
+      </c>
+    </row>
+    <row r="42" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A42" t="s">
+        <v>223</v>
+      </c>
+      <c r="B42" t="s">
+        <v>16</v>
+      </c>
+      <c r="C42" t="s">
+        <v>221</v>
+      </c>
+      <c r="D42" t="s">
+        <v>18</v>
+      </c>
+      <c r="E42" t="s">
+        <v>92</v>
+      </c>
+      <c r="F42" t="s">
+        <v>20</v>
+      </c>
+      <c r="H42" s="2" t="s">
+        <v>224</v>
+      </c>
+    </row>
+    <row r="43" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A43" t="s">
+        <v>225</v>
+      </c>
+      <c r="B43" t="s">
+        <v>226</v>
+      </c>
+      <c r="C43" t="s">
+        <v>227</v>
+      </c>
+      <c r="D43" t="s">
+        <v>11</v>
+      </c>
+      <c r="E43" t="s">
+        <v>228</v>
+      </c>
+      <c r="F43" t="s">
+        <v>229</v>
+      </c>
+      <c r="H43" s="2" t="s">
+        <v>230</v>
+      </c>
+    </row>
+    <row r="44" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A44" t="s">
+        <v>231</v>
+      </c>
+      <c r="B44" t="s">
+        <v>168</v>
+      </c>
+      <c r="C44" t="s">
+        <v>169</v>
+      </c>
+      <c r="D44" t="s">
+        <v>30</v>
+      </c>
+      <c r="E44" t="s">
+        <v>232</v>
+      </c>
+      <c r="F44" t="s">
+        <v>233</v>
+      </c>
+      <c r="H44" s="2" t="s">
+        <v>234</v>
+      </c>
+    </row>
+    <row r="45" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A45" t="s">
+        <v>235</v>
+      </c>
+      <c r="B45" t="s">
+        <v>236</v>
+      </c>
+      <c r="C45" t="s">
+        <v>237</v>
+      </c>
+      <c r="D45" t="s">
+        <v>11</v>
+      </c>
+      <c r="E45" t="s">
+        <v>238</v>
+      </c>
+      <c r="F45" t="s">
+        <v>233</v>
+      </c>
+      <c r="H45" s="2" t="s">
+        <v>239</v>
+      </c>
+    </row>
+    <row r="46" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A46" t="s">
+        <v>240</v>
+      </c>
+      <c r="B46" t="s">
+        <v>35</v>
+      </c>
+      <c r="C46" t="s">
+        <v>241</v>
+      </c>
+      <c r="D46" t="s">
+        <v>11</v>
+      </c>
+      <c r="E46" t="s">
+        <v>37</v>
+      </c>
+      <c r="F46" t="s">
+        <v>32</v>
+      </c>
+      <c r="H46" s="2" t="s">
+        <v>242</v>
+      </c>
+    </row>
+    <row r="47" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A47" t="s">
+        <v>243</v>
+      </c>
+      <c r="B47" t="s">
+        <v>244</v>
+      </c>
+      <c r="C47" t="s">
+        <v>245</v>
+      </c>
+      <c r="D47" t="s">
+        <v>11</v>
+      </c>
+      <c r="E47" t="s">
+        <v>246</v>
+      </c>
+      <c r="F47" t="s">
+        <v>32</v>
+      </c>
+      <c r="H47" s="2" t="s">
+        <v>247</v>
+      </c>
+    </row>
+    <row r="48" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A48" t="s">
+        <v>243</v>
+      </c>
+      <c r="B48" t="s">
+        <v>244</v>
+      </c>
+      <c r="C48" t="s">
+        <v>248</v>
+      </c>
+      <c r="D48" t="s">
+        <v>11</v>
+      </c>
+      <c r="E48" t="s">
+        <v>246</v>
+      </c>
+      <c r="F48" t="s">
+        <v>32</v>
+      </c>
+      <c r="H48" s="2" t="s">
+        <v>249</v>
+      </c>
+    </row>
+    <row r="49" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A49" t="s">
+        <v>243</v>
+      </c>
+      <c r="B49" t="s">
+        <v>244</v>
+      </c>
+      <c r="C49" t="s">
+        <v>250</v>
+      </c>
+      <c r="D49" t="s">
+        <v>11</v>
+      </c>
+      <c r="E49" t="s">
+        <v>246</v>
+      </c>
+      <c r="F49" t="s">
+        <v>32</v>
+      </c>
+      <c r="H49" s="2" t="s">
+        <v>251</v>
+      </c>
+    </row>
+    <row r="50" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A50" t="s">
+        <v>243</v>
+      </c>
+      <c r="B50" t="s">
+        <v>244</v>
+      </c>
+      <c r="C50" t="s">
+        <v>252</v>
+      </c>
+      <c r="D50" t="s">
+        <v>11</v>
+      </c>
+      <c r="E50" t="s">
+        <v>246</v>
+      </c>
+      <c r="F50" t="s">
+        <v>32</v>
+      </c>
+      <c r="H50" s="2" t="s">
+        <v>253</v>
+      </c>
+    </row>
+    <row r="51" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A51" t="s">
+        <v>254</v>
+      </c>
+      <c r="B51" t="s">
+        <v>255</v>
+      </c>
+      <c r="C51" t="s">
+        <v>256</v>
+      </c>
+      <c r="D51" t="s">
+        <v>11</v>
+      </c>
+      <c r="E51" t="s">
+        <v>257</v>
+      </c>
+      <c r="F51" t="s">
+        <v>258</v>
+      </c>
+      <c r="H51" s="2" t="s">
+        <v>259</v>
+      </c>
+    </row>
   </sheetData>
   <autoFilter ref="A1:H1"/>
+  <hyperlinks>
+    <hyperlink ref="H2" r:id="rId1"/>
+    <hyperlink ref="H3" r:id="rId2"/>
+    <hyperlink ref="H4" r:id="rId3"/>
+    <hyperlink ref="H5" r:id="rId4"/>
+    <hyperlink ref="H6" r:id="rId5"/>
+    <hyperlink ref="H7" r:id="rId6"/>
+    <hyperlink ref="H8" r:id="rId7"/>
+    <hyperlink ref="H9" r:id="rId8"/>
+    <hyperlink ref="H10" r:id="rId9"/>
+    <hyperlink ref="H11" r:id="rId10"/>
+    <hyperlink ref="H12" r:id="rId11"/>
+    <hyperlink ref="H13" r:id="rId12"/>
+    <hyperlink ref="H14" r:id="rId13"/>
+    <hyperlink ref="H15" r:id="rId14"/>
+    <hyperlink ref="H16" r:id="rId15"/>
+    <hyperlink ref="H17" r:id="rId16"/>
+    <hyperlink ref="H18" r:id="rId17"/>
+    <hyperlink ref="H19" r:id="rId18"/>
+    <hyperlink ref="H20" r:id="rId19"/>
+    <hyperlink ref="H21" r:id="rId20"/>
+    <hyperlink ref="H22" r:id="rId21"/>
+    <hyperlink ref="H23" r:id="rId22"/>
+    <hyperlink ref="H24" r:id="rId23"/>
+    <hyperlink ref="H25" r:id="rId24"/>
+    <hyperlink ref="H26" r:id="rId25"/>
+    <hyperlink ref="H27" r:id="rId26"/>
+    <hyperlink ref="H28" r:id="rId27"/>
+    <hyperlink ref="H29" r:id="rId28"/>
+    <hyperlink ref="H30" r:id="rId29"/>
+    <hyperlink ref="H31" r:id="rId30"/>
+    <hyperlink ref="H32" r:id="rId31"/>
+    <hyperlink ref="H33" r:id="rId32"/>
+    <hyperlink ref="H34" r:id="rId33"/>
+    <hyperlink ref="H35" r:id="rId34"/>
+    <hyperlink ref="H36" r:id="rId35"/>
+    <hyperlink ref="H37" r:id="rId36"/>
+    <hyperlink ref="H38" r:id="rId37"/>
+    <hyperlink ref="H39" r:id="rId38"/>
+    <hyperlink ref="H40" r:id="rId39"/>
+    <hyperlink ref="H41" r:id="rId40"/>
+    <hyperlink ref="H42" r:id="rId41"/>
+    <hyperlink ref="H43" r:id="rId42"/>
+    <hyperlink ref="H44" r:id="rId43"/>
+    <hyperlink ref="H45" r:id="rId44"/>
+    <hyperlink ref="H46" r:id="rId45"/>
+    <hyperlink ref="H47" r:id="rId46"/>
+    <hyperlink ref="H48" r:id="rId47"/>
+    <hyperlink ref="H49" r:id="rId48"/>
+    <hyperlink ref="H50" r:id="rId49"/>
+    <hyperlink ref="H51" r:id="rId50"/>
+  </hyperlinks>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup orientation="portrait" horizontalDpi="4294967295" verticalDpi="4294967295" scale="100" fitToWidth="1" fitToHeight="1"/>
 </worksheet>
@@ -466,7 +3752,7 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <dimension ref="A1:H1"/>
+  <dimension ref="A1:H3"/>
   <sheetFormatPr defaultRowHeight="15" outlineLevelRow="0" outlineLevelCol="0" x14ac:dyDescent="55"/>
   <cols>
     <col min="1" max="1" width="48" customWidth="1"/>
@@ -505,8 +3791,58 @@
         <v>7</v>
       </c>
     </row>
+    <row r="2" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A2" t="s">
+        <v>260</v>
+      </c>
+      <c r="B2" t="s">
+        <v>261</v>
+      </c>
+      <c r="C2" t="s">
+        <v>262</v>
+      </c>
+      <c r="D2" t="s">
+        <v>30</v>
+      </c>
+      <c r="E2" t="s">
+        <v>263</v>
+      </c>
+      <c r="F2" t="s">
+        <v>264</v>
+      </c>
+      <c r="H2" s="2" t="s">
+        <v>265</v>
+      </c>
+    </row>
+    <row r="3" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A3" t="s">
+        <v>266</v>
+      </c>
+      <c r="B3" t="s">
+        <v>267</v>
+      </c>
+      <c r="C3" t="s">
+        <v>268</v>
+      </c>
+      <c r="D3" t="s">
+        <v>269</v>
+      </c>
+      <c r="E3" t="s">
+        <v>270</v>
+      </c>
+      <c r="F3" t="s">
+        <v>271</v>
+      </c>
+      <c r="H3" s="2" t="s">
+        <v>272</v>
+      </c>
+    </row>
   </sheetData>
   <autoFilter ref="A1:H1"/>
+  <hyperlinks>
+    <hyperlink ref="H2" r:id="rId1"/>
+    <hyperlink ref="H3" r:id="rId2"/>
+  </hyperlinks>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup orientation="portrait" horizontalDpi="4294967295" verticalDpi="4294967295" scale="100" fitToWidth="1" fitToHeight="1"/>
 </worksheet>
@@ -514,7 +3850,7 @@
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <dimension ref="A1:H1"/>
+  <dimension ref="A1:H91"/>
   <sheetFormatPr defaultRowHeight="15" outlineLevelRow="0" outlineLevelCol="0" x14ac:dyDescent="55"/>
   <cols>
     <col min="1" max="1" width="48" customWidth="1"/>
@@ -553,8 +3889,2170 @@
         <v>7</v>
       </c>
     </row>
+    <row r="2" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A2" t="s">
+        <v>273</v>
+      </c>
+      <c r="B2" t="s">
+        <v>274</v>
+      </c>
+      <c r="C2" t="s">
+        <v>275</v>
+      </c>
+      <c r="D2" t="s">
+        <v>276</v>
+      </c>
+      <c r="E2" t="s">
+        <v>277</v>
+      </c>
+      <c r="F2" t="s">
+        <v>278</v>
+      </c>
+      <c r="H2" s="2" t="s">
+        <v>279</v>
+      </c>
+    </row>
+    <row r="3" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A3" t="s">
+        <v>280</v>
+      </c>
+      <c r="B3" t="s">
+        <v>281</v>
+      </c>
+      <c r="C3" t="s">
+        <v>282</v>
+      </c>
+      <c r="D3" t="s">
+        <v>276</v>
+      </c>
+      <c r="E3" t="s">
+        <v>283</v>
+      </c>
+      <c r="F3" t="s">
+        <v>284</v>
+      </c>
+      <c r="H3" s="2" t="s">
+        <v>285</v>
+      </c>
+    </row>
+    <row r="4" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A4" t="s">
+        <v>286</v>
+      </c>
+      <c r="B4" t="s">
+        <v>287</v>
+      </c>
+      <c r="C4" t="s">
+        <v>288</v>
+      </c>
+      <c r="D4" t="s">
+        <v>276</v>
+      </c>
+      <c r="E4" t="s">
+        <v>289</v>
+      </c>
+      <c r="F4" t="s">
+        <v>290</v>
+      </c>
+      <c r="H4" s="2" t="s">
+        <v>291</v>
+      </c>
+    </row>
+    <row r="5" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A5" t="s">
+        <v>292</v>
+      </c>
+      <c r="B5" t="s">
+        <v>293</v>
+      </c>
+      <c r="C5" t="s">
+        <v>237</v>
+      </c>
+      <c r="D5" t="s">
+        <v>276</v>
+      </c>
+      <c r="E5" t="s">
+        <v>294</v>
+      </c>
+      <c r="F5" t="s">
+        <v>295</v>
+      </c>
+      <c r="H5" s="2" t="s">
+        <v>296</v>
+      </c>
+    </row>
+    <row r="6" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A6" t="s">
+        <v>297</v>
+      </c>
+      <c r="B6" t="s">
+        <v>298</v>
+      </c>
+      <c r="C6" t="s">
+        <v>282</v>
+      </c>
+      <c r="D6" t="s">
+        <v>276</v>
+      </c>
+      <c r="E6" t="s">
+        <v>299</v>
+      </c>
+      <c r="F6" t="s">
+        <v>300</v>
+      </c>
+      <c r="H6" s="2" t="s">
+        <v>301</v>
+      </c>
+    </row>
+    <row r="7" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A7" t="s">
+        <v>302</v>
+      </c>
+      <c r="B7" t="s">
+        <v>303</v>
+      </c>
+      <c r="C7" t="s">
+        <v>304</v>
+      </c>
+      <c r="D7" t="s">
+        <v>276</v>
+      </c>
+      <c r="E7" t="s">
+        <v>305</v>
+      </c>
+      <c r="F7" t="s">
+        <v>306</v>
+      </c>
+      <c r="H7" s="2" t="s">
+        <v>307</v>
+      </c>
+    </row>
+    <row r="8" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A8" t="s">
+        <v>308</v>
+      </c>
+      <c r="B8" t="s">
+        <v>309</v>
+      </c>
+      <c r="C8" t="s">
+        <v>310</v>
+      </c>
+      <c r="D8" t="s">
+        <v>276</v>
+      </c>
+      <c r="E8" t="s">
+        <v>311</v>
+      </c>
+      <c r="F8" t="s">
+        <v>312</v>
+      </c>
+      <c r="H8" s="2" t="s">
+        <v>313</v>
+      </c>
+    </row>
+    <row r="9" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A9" t="s">
+        <v>314</v>
+      </c>
+      <c r="B9" t="s">
+        <v>315</v>
+      </c>
+      <c r="C9" t="s">
+        <v>310</v>
+      </c>
+      <c r="D9" t="s">
+        <v>276</v>
+      </c>
+      <c r="E9" t="s">
+        <v>316</v>
+      </c>
+      <c r="F9" t="s">
+        <v>317</v>
+      </c>
+      <c r="H9" s="2" t="s">
+        <v>318</v>
+      </c>
+    </row>
+    <row r="10" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A10" t="s">
+        <v>319</v>
+      </c>
+      <c r="B10" t="s">
+        <v>320</v>
+      </c>
+      <c r="C10" t="s">
+        <v>321</v>
+      </c>
+      <c r="D10" t="s">
+        <v>276</v>
+      </c>
+      <c r="E10" t="s">
+        <v>270</v>
+      </c>
+      <c r="F10" t="s">
+        <v>322</v>
+      </c>
+      <c r="H10" s="2" t="s">
+        <v>323</v>
+      </c>
+    </row>
+    <row r="11" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A11" t="s">
+        <v>324</v>
+      </c>
+      <c r="B11" t="s">
+        <v>325</v>
+      </c>
+      <c r="C11" t="s">
+        <v>326</v>
+      </c>
+      <c r="D11" t="s">
+        <v>276</v>
+      </c>
+      <c r="E11" t="s">
+        <v>327</v>
+      </c>
+      <c r="F11" t="s">
+        <v>328</v>
+      </c>
+      <c r="H11" s="2" t="s">
+        <v>329</v>
+      </c>
+    </row>
+    <row r="12" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A12" t="s">
+        <v>330</v>
+      </c>
+      <c r="B12" t="s">
+        <v>331</v>
+      </c>
+      <c r="C12" t="s">
+        <v>332</v>
+      </c>
+      <c r="D12" t="s">
+        <v>276</v>
+      </c>
+      <c r="E12" t="s">
+        <v>333</v>
+      </c>
+      <c r="F12" t="s">
+        <v>270</v>
+      </c>
+      <c r="H12" s="2" t="s">
+        <v>334</v>
+      </c>
+    </row>
+    <row r="13" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A13" t="s">
+        <v>335</v>
+      </c>
+      <c r="B13" t="s">
+        <v>336</v>
+      </c>
+      <c r="C13" t="s">
+        <v>282</v>
+      </c>
+      <c r="D13" t="s">
+        <v>276</v>
+      </c>
+      <c r="E13" t="s">
+        <v>337</v>
+      </c>
+      <c r="F13" t="s">
+        <v>338</v>
+      </c>
+      <c r="H13" s="2" t="s">
+        <v>339</v>
+      </c>
+    </row>
+    <row r="14" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A14" t="s">
+        <v>340</v>
+      </c>
+      <c r="B14" t="s">
+        <v>341</v>
+      </c>
+      <c r="C14" t="s">
+        <v>342</v>
+      </c>
+      <c r="D14" t="s">
+        <v>276</v>
+      </c>
+      <c r="E14" t="s">
+        <v>343</v>
+      </c>
+      <c r="F14" t="s">
+        <v>270</v>
+      </c>
+      <c r="H14" s="2" t="s">
+        <v>344</v>
+      </c>
+    </row>
+    <row r="15" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A15" t="s">
+        <v>345</v>
+      </c>
+      <c r="B15" t="s">
+        <v>346</v>
+      </c>
+      <c r="C15" t="s">
+        <v>304</v>
+      </c>
+      <c r="D15" t="s">
+        <v>276</v>
+      </c>
+      <c r="E15" t="s">
+        <v>347</v>
+      </c>
+      <c r="F15" t="s">
+        <v>348</v>
+      </c>
+      <c r="H15" s="2" t="s">
+        <v>349</v>
+      </c>
+    </row>
+    <row r="16" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A16" t="s">
+        <v>350</v>
+      </c>
+      <c r="B16" t="s">
+        <v>351</v>
+      </c>
+      <c r="C16" t="s">
+        <v>352</v>
+      </c>
+      <c r="D16" t="s">
+        <v>276</v>
+      </c>
+      <c r="E16" t="s">
+        <v>353</v>
+      </c>
+      <c r="F16" t="s">
+        <v>354</v>
+      </c>
+      <c r="H16" s="2" t="s">
+        <v>355</v>
+      </c>
+    </row>
+    <row r="17" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A17" t="s">
+        <v>356</v>
+      </c>
+      <c r="B17" t="s">
+        <v>357</v>
+      </c>
+      <c r="C17" t="s">
+        <v>332</v>
+      </c>
+      <c r="D17" t="s">
+        <v>276</v>
+      </c>
+      <c r="E17" t="s">
+        <v>358</v>
+      </c>
+      <c r="F17" t="s">
+        <v>359</v>
+      </c>
+      <c r="H17" s="2" t="s">
+        <v>360</v>
+      </c>
+    </row>
+    <row r="18" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A18" t="s">
+        <v>361</v>
+      </c>
+      <c r="B18" t="s">
+        <v>362</v>
+      </c>
+      <c r="C18" t="s">
+        <v>363</v>
+      </c>
+      <c r="D18" t="s">
+        <v>276</v>
+      </c>
+      <c r="E18" t="s">
+        <v>364</v>
+      </c>
+      <c r="F18" t="s">
+        <v>365</v>
+      </c>
+      <c r="H18" s="2" t="s">
+        <v>366</v>
+      </c>
+    </row>
+    <row r="19" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A19" t="s">
+        <v>367</v>
+      </c>
+      <c r="B19" t="s">
+        <v>368</v>
+      </c>
+      <c r="C19" t="s">
+        <v>310</v>
+      </c>
+      <c r="D19" t="s">
+        <v>369</v>
+      </c>
+      <c r="E19" t="s">
+        <v>270</v>
+      </c>
+      <c r="F19" t="s">
+        <v>370</v>
+      </c>
+      <c r="H19" s="2" t="s">
+        <v>371</v>
+      </c>
+    </row>
+    <row r="20" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A20" t="s">
+        <v>372</v>
+      </c>
+      <c r="B20" t="s">
+        <v>373</v>
+      </c>
+      <c r="C20" t="s">
+        <v>374</v>
+      </c>
+      <c r="D20" t="s">
+        <v>276</v>
+      </c>
+      <c r="E20" t="s">
+        <v>289</v>
+      </c>
+      <c r="F20" t="s">
+        <v>375</v>
+      </c>
+      <c r="H20" s="2" t="s">
+        <v>376</v>
+      </c>
+    </row>
+    <row r="21" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A21" t="s">
+        <v>377</v>
+      </c>
+      <c r="B21" t="s">
+        <v>378</v>
+      </c>
+      <c r="C21" t="s">
+        <v>379</v>
+      </c>
+      <c r="D21" t="s">
+        <v>276</v>
+      </c>
+      <c r="E21" t="s">
+        <v>380</v>
+      </c>
+      <c r="F21" t="s">
+        <v>381</v>
+      </c>
+      <c r="H21" s="2" t="s">
+        <v>382</v>
+      </c>
+    </row>
+    <row r="22" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A22" t="s">
+        <v>383</v>
+      </c>
+      <c r="B22" t="s">
+        <v>384</v>
+      </c>
+      <c r="C22" t="s">
+        <v>304</v>
+      </c>
+      <c r="D22" t="s">
+        <v>276</v>
+      </c>
+      <c r="E22" t="s">
+        <v>385</v>
+      </c>
+      <c r="F22" t="s">
+        <v>270</v>
+      </c>
+      <c r="H22" s="2" t="s">
+        <v>386</v>
+      </c>
+    </row>
+    <row r="23" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A23" t="s">
+        <v>387</v>
+      </c>
+      <c r="B23" t="s">
+        <v>388</v>
+      </c>
+      <c r="C23" t="s">
+        <v>282</v>
+      </c>
+      <c r="D23" t="s">
+        <v>389</v>
+      </c>
+      <c r="E23" t="s">
+        <v>390</v>
+      </c>
+      <c r="F23" t="s">
+        <v>391</v>
+      </c>
+      <c r="H23" s="2" t="s">
+        <v>392</v>
+      </c>
+    </row>
+    <row r="24" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A24" t="s">
+        <v>393</v>
+      </c>
+      <c r="B24" t="s">
+        <v>394</v>
+      </c>
+      <c r="C24" t="s">
+        <v>395</v>
+      </c>
+      <c r="D24" t="s">
+        <v>276</v>
+      </c>
+      <c r="E24" t="s">
+        <v>396</v>
+      </c>
+      <c r="F24" t="s">
+        <v>397</v>
+      </c>
+      <c r="H24" s="2" t="s">
+        <v>398</v>
+      </c>
+    </row>
+    <row r="25" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A25" t="s">
+        <v>399</v>
+      </c>
+      <c r="B25" t="s">
+        <v>400</v>
+      </c>
+      <c r="C25" t="s">
+        <v>401</v>
+      </c>
+      <c r="D25" t="s">
+        <v>276</v>
+      </c>
+      <c r="E25" t="s">
+        <v>402</v>
+      </c>
+      <c r="F25" t="s">
+        <v>290</v>
+      </c>
+      <c r="H25" s="2" t="s">
+        <v>403</v>
+      </c>
+    </row>
+    <row r="26" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A26" t="s">
+        <v>404</v>
+      </c>
+      <c r="B26" t="s">
+        <v>405</v>
+      </c>
+      <c r="C26" t="s">
+        <v>304</v>
+      </c>
+      <c r="D26" t="s">
+        <v>276</v>
+      </c>
+      <c r="E26" t="s">
+        <v>406</v>
+      </c>
+      <c r="F26" t="s">
+        <v>407</v>
+      </c>
+      <c r="H26" s="2" t="s">
+        <v>408</v>
+      </c>
+    </row>
+    <row r="27" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A27" t="s">
+        <v>404</v>
+      </c>
+      <c r="B27" t="s">
+        <v>409</v>
+      </c>
+      <c r="C27" t="s">
+        <v>410</v>
+      </c>
+      <c r="D27" t="s">
+        <v>276</v>
+      </c>
+      <c r="E27" t="s">
+        <v>411</v>
+      </c>
+      <c r="F27" t="s">
+        <v>412</v>
+      </c>
+      <c r="H27" s="2" t="s">
+        <v>413</v>
+      </c>
+    </row>
+    <row r="28" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A28" t="s">
+        <v>404</v>
+      </c>
+      <c r="B28" t="s">
+        <v>414</v>
+      </c>
+      <c r="C28" t="s">
+        <v>342</v>
+      </c>
+      <c r="D28" t="s">
+        <v>276</v>
+      </c>
+      <c r="E28" t="s">
+        <v>415</v>
+      </c>
+      <c r="F28" t="s">
+        <v>270</v>
+      </c>
+      <c r="H28" s="2" t="s">
+        <v>416</v>
+      </c>
+    </row>
+    <row r="29" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A29" t="s">
+        <v>417</v>
+      </c>
+      <c r="B29" t="s">
+        <v>418</v>
+      </c>
+      <c r="C29" t="s">
+        <v>419</v>
+      </c>
+      <c r="D29" t="s">
+        <v>276</v>
+      </c>
+      <c r="E29" t="s">
+        <v>420</v>
+      </c>
+      <c r="F29" t="s">
+        <v>421</v>
+      </c>
+      <c r="H29" s="2" t="s">
+        <v>422</v>
+      </c>
+    </row>
+    <row r="30" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A30" t="s">
+        <v>423</v>
+      </c>
+      <c r="B30" t="s">
+        <v>424</v>
+      </c>
+      <c r="C30" t="s">
+        <v>342</v>
+      </c>
+      <c r="D30" t="s">
+        <v>276</v>
+      </c>
+      <c r="E30" t="s">
+        <v>425</v>
+      </c>
+      <c r="F30" t="s">
+        <v>426</v>
+      </c>
+      <c r="H30" s="2" t="s">
+        <v>427</v>
+      </c>
+    </row>
+    <row r="31" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A31" t="s">
+        <v>428</v>
+      </c>
+      <c r="B31" t="s">
+        <v>429</v>
+      </c>
+      <c r="C31" t="s">
+        <v>430</v>
+      </c>
+      <c r="D31" t="s">
+        <v>276</v>
+      </c>
+      <c r="E31" t="s">
+        <v>431</v>
+      </c>
+      <c r="F31" t="s">
+        <v>432</v>
+      </c>
+      <c r="H31" s="2" t="s">
+        <v>433</v>
+      </c>
+    </row>
+    <row r="32" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A32" t="s">
+        <v>434</v>
+      </c>
+      <c r="B32" t="s">
+        <v>435</v>
+      </c>
+      <c r="C32" t="s">
+        <v>282</v>
+      </c>
+      <c r="D32" t="s">
+        <v>276</v>
+      </c>
+      <c r="E32" t="s">
+        <v>436</v>
+      </c>
+      <c r="F32" t="s">
+        <v>437</v>
+      </c>
+      <c r="H32" s="2" t="s">
+        <v>438</v>
+      </c>
+    </row>
+    <row r="33" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A33" t="s">
+        <v>439</v>
+      </c>
+      <c r="B33" t="s">
+        <v>429</v>
+      </c>
+      <c r="C33" t="s">
+        <v>430</v>
+      </c>
+      <c r="D33" t="s">
+        <v>276</v>
+      </c>
+      <c r="E33" t="s">
+        <v>270</v>
+      </c>
+      <c r="F33" t="s">
+        <v>440</v>
+      </c>
+      <c r="H33" s="2" t="s">
+        <v>441</v>
+      </c>
+    </row>
+    <row r="34" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A34" t="s">
+        <v>442</v>
+      </c>
+      <c r="B34" t="s">
+        <v>443</v>
+      </c>
+      <c r="C34" t="s">
+        <v>64</v>
+      </c>
+      <c r="D34" t="s">
+        <v>444</v>
+      </c>
+      <c r="E34" t="s">
+        <v>445</v>
+      </c>
+      <c r="F34" t="s">
+        <v>446</v>
+      </c>
+      <c r="H34" s="2" t="s">
+        <v>447</v>
+      </c>
+    </row>
+    <row r="35" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A35" t="s">
+        <v>448</v>
+      </c>
+      <c r="B35" t="s">
+        <v>449</v>
+      </c>
+      <c r="C35" t="s">
+        <v>450</v>
+      </c>
+      <c r="D35" t="s">
+        <v>276</v>
+      </c>
+      <c r="E35" t="s">
+        <v>451</v>
+      </c>
+      <c r="F35" t="s">
+        <v>452</v>
+      </c>
+      <c r="H35" s="2" t="s">
+        <v>453</v>
+      </c>
+    </row>
+    <row r="36" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A36" t="s">
+        <v>448</v>
+      </c>
+      <c r="B36" t="s">
+        <v>454</v>
+      </c>
+      <c r="C36" t="s">
+        <v>363</v>
+      </c>
+      <c r="D36" t="s">
+        <v>276</v>
+      </c>
+      <c r="E36" t="s">
+        <v>455</v>
+      </c>
+      <c r="F36" t="s">
+        <v>456</v>
+      </c>
+      <c r="H36" s="2" t="s">
+        <v>457</v>
+      </c>
+    </row>
+    <row r="37" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A37" t="s">
+        <v>448</v>
+      </c>
+      <c r="B37" t="s">
+        <v>458</v>
+      </c>
+      <c r="C37" t="s">
+        <v>459</v>
+      </c>
+      <c r="D37" t="s">
+        <v>276</v>
+      </c>
+      <c r="E37" t="s">
+        <v>460</v>
+      </c>
+      <c r="F37" t="s">
+        <v>270</v>
+      </c>
+      <c r="H37" s="2" t="s">
+        <v>461</v>
+      </c>
+    </row>
+    <row r="38" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A38" t="s">
+        <v>462</v>
+      </c>
+      <c r="B38" t="s">
+        <v>463</v>
+      </c>
+      <c r="C38" t="s">
+        <v>282</v>
+      </c>
+      <c r="D38" t="s">
+        <v>276</v>
+      </c>
+      <c r="E38" t="s">
+        <v>464</v>
+      </c>
+      <c r="F38" t="s">
+        <v>465</v>
+      </c>
+      <c r="H38" s="2" t="s">
+        <v>466</v>
+      </c>
+    </row>
+    <row r="39" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A39" t="s">
+        <v>467</v>
+      </c>
+      <c r="B39" t="s">
+        <v>468</v>
+      </c>
+      <c r="C39" t="s">
+        <v>379</v>
+      </c>
+      <c r="D39" t="s">
+        <v>276</v>
+      </c>
+      <c r="E39" t="s">
+        <v>469</v>
+      </c>
+      <c r="F39" t="s">
+        <v>470</v>
+      </c>
+      <c r="H39" s="2" t="s">
+        <v>471</v>
+      </c>
+    </row>
+    <row r="40" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A40" t="s">
+        <v>472</v>
+      </c>
+      <c r="B40" t="s">
+        <v>473</v>
+      </c>
+      <c r="C40" t="s">
+        <v>474</v>
+      </c>
+      <c r="D40" t="s">
+        <v>369</v>
+      </c>
+      <c r="E40" t="s">
+        <v>270</v>
+      </c>
+      <c r="F40" t="s">
+        <v>475</v>
+      </c>
+      <c r="H40" s="2" t="s">
+        <v>476</v>
+      </c>
+    </row>
+    <row r="41" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A41" t="s">
+        <v>477</v>
+      </c>
+      <c r="B41" t="s">
+        <v>478</v>
+      </c>
+      <c r="C41" t="s">
+        <v>401</v>
+      </c>
+      <c r="D41" t="s">
+        <v>276</v>
+      </c>
+      <c r="E41" t="s">
+        <v>479</v>
+      </c>
+      <c r="F41" t="s">
+        <v>480</v>
+      </c>
+      <c r="H41" s="2" t="s">
+        <v>481</v>
+      </c>
+    </row>
+    <row r="42" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A42" t="s">
+        <v>482</v>
+      </c>
+      <c r="B42" t="s">
+        <v>325</v>
+      </c>
+      <c r="C42" t="s">
+        <v>326</v>
+      </c>
+      <c r="D42" t="s">
+        <v>276</v>
+      </c>
+      <c r="E42" t="s">
+        <v>483</v>
+      </c>
+      <c r="F42" t="s">
+        <v>328</v>
+      </c>
+      <c r="H42" s="2" t="s">
+        <v>484</v>
+      </c>
+    </row>
+    <row r="43" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A43" t="s">
+        <v>485</v>
+      </c>
+      <c r="B43" t="s">
+        <v>486</v>
+      </c>
+      <c r="C43" t="s">
+        <v>487</v>
+      </c>
+      <c r="D43" t="s">
+        <v>276</v>
+      </c>
+      <c r="E43" t="s">
+        <v>488</v>
+      </c>
+      <c r="F43" t="s">
+        <v>489</v>
+      </c>
+      <c r="H43" s="2" t="s">
+        <v>490</v>
+      </c>
+    </row>
+    <row r="44" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A44" t="s">
+        <v>491</v>
+      </c>
+      <c r="B44" t="s">
+        <v>492</v>
+      </c>
+      <c r="C44" t="s">
+        <v>304</v>
+      </c>
+      <c r="D44" t="s">
+        <v>276</v>
+      </c>
+      <c r="E44" t="s">
+        <v>493</v>
+      </c>
+      <c r="F44" t="s">
+        <v>494</v>
+      </c>
+      <c r="H44" s="2" t="s">
+        <v>495</v>
+      </c>
+    </row>
+    <row r="45" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A45" t="s">
+        <v>496</v>
+      </c>
+      <c r="B45" t="s">
+        <v>497</v>
+      </c>
+      <c r="C45" t="s">
+        <v>379</v>
+      </c>
+      <c r="D45" t="s">
+        <v>498</v>
+      </c>
+      <c r="E45" t="s">
+        <v>499</v>
+      </c>
+      <c r="F45" t="s">
+        <v>270</v>
+      </c>
+      <c r="H45" s="2" t="s">
+        <v>500</v>
+      </c>
+    </row>
+    <row r="46" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A46" t="s">
+        <v>501</v>
+      </c>
+      <c r="B46" t="s">
+        <v>303</v>
+      </c>
+      <c r="C46" t="s">
+        <v>304</v>
+      </c>
+      <c r="D46" t="s">
+        <v>276</v>
+      </c>
+      <c r="E46" t="s">
+        <v>502</v>
+      </c>
+      <c r="F46" t="s">
+        <v>503</v>
+      </c>
+      <c r="H46" s="2" t="s">
+        <v>504</v>
+      </c>
+    </row>
+    <row r="47" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A47" t="s">
+        <v>505</v>
+      </c>
+      <c r="B47" t="s">
+        <v>506</v>
+      </c>
+      <c r="C47" t="s">
+        <v>282</v>
+      </c>
+      <c r="D47" t="s">
+        <v>276</v>
+      </c>
+      <c r="E47" t="s">
+        <v>507</v>
+      </c>
+      <c r="F47" t="s">
+        <v>508</v>
+      </c>
+      <c r="H47" s="2" t="s">
+        <v>509</v>
+      </c>
+    </row>
+    <row r="48" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A48" t="s">
+        <v>510</v>
+      </c>
+      <c r="B48" t="s">
+        <v>511</v>
+      </c>
+      <c r="C48" t="s">
+        <v>342</v>
+      </c>
+      <c r="D48" t="s">
+        <v>444</v>
+      </c>
+      <c r="E48" t="s">
+        <v>512</v>
+      </c>
+      <c r="F48" t="s">
+        <v>513</v>
+      </c>
+      <c r="H48" s="2" t="s">
+        <v>514</v>
+      </c>
+    </row>
+    <row r="49" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A49" t="s">
+        <v>515</v>
+      </c>
+      <c r="B49" t="s">
+        <v>516</v>
+      </c>
+      <c r="C49" t="s">
+        <v>517</v>
+      </c>
+      <c r="D49" t="s">
+        <v>276</v>
+      </c>
+      <c r="E49" t="s">
+        <v>299</v>
+      </c>
+      <c r="F49" t="s">
+        <v>518</v>
+      </c>
+      <c r="H49" s="2" t="s">
+        <v>519</v>
+      </c>
+    </row>
+    <row r="50" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A50" t="s">
+        <v>520</v>
+      </c>
+      <c r="B50" t="s">
+        <v>521</v>
+      </c>
+      <c r="C50" t="s">
+        <v>282</v>
+      </c>
+      <c r="D50" t="s">
+        <v>276</v>
+      </c>
+      <c r="E50" t="s">
+        <v>522</v>
+      </c>
+      <c r="F50" t="s">
+        <v>523</v>
+      </c>
+      <c r="H50" s="2" t="s">
+        <v>524</v>
+      </c>
+    </row>
+    <row r="51" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A51" t="s">
+        <v>525</v>
+      </c>
+      <c r="B51" t="s">
+        <v>429</v>
+      </c>
+      <c r="C51" t="s">
+        <v>430</v>
+      </c>
+      <c r="D51" t="s">
+        <v>276</v>
+      </c>
+      <c r="E51" t="s">
+        <v>526</v>
+      </c>
+      <c r="F51" t="s">
+        <v>440</v>
+      </c>
+      <c r="H51" s="2" t="s">
+        <v>527</v>
+      </c>
+    </row>
+    <row r="52" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A52" t="s">
+        <v>528</v>
+      </c>
+      <c r="B52" t="s">
+        <v>529</v>
+      </c>
+      <c r="C52" t="s">
+        <v>530</v>
+      </c>
+      <c r="D52" t="s">
+        <v>276</v>
+      </c>
+      <c r="E52" t="s">
+        <v>531</v>
+      </c>
+      <c r="F52" t="s">
+        <v>532</v>
+      </c>
+      <c r="H52" s="2" t="s">
+        <v>533</v>
+      </c>
+    </row>
+    <row r="53" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A53" t="s">
+        <v>534</v>
+      </c>
+      <c r="B53" t="s">
+        <v>303</v>
+      </c>
+      <c r="C53" t="s">
+        <v>304</v>
+      </c>
+      <c r="D53" t="s">
+        <v>276</v>
+      </c>
+      <c r="E53" t="s">
+        <v>535</v>
+      </c>
+      <c r="F53" t="s">
+        <v>306</v>
+      </c>
+      <c r="H53" s="2" t="s">
+        <v>536</v>
+      </c>
+    </row>
+    <row r="54" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A54" t="s">
+        <v>537</v>
+      </c>
+      <c r="B54" t="s">
+        <v>538</v>
+      </c>
+      <c r="C54" t="s">
+        <v>310</v>
+      </c>
+      <c r="D54" t="s">
+        <v>276</v>
+      </c>
+      <c r="E54" t="s">
+        <v>396</v>
+      </c>
+      <c r="F54" t="s">
+        <v>539</v>
+      </c>
+      <c r="H54" s="2" t="s">
+        <v>540</v>
+      </c>
+    </row>
+    <row r="55" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A55" t="s">
+        <v>541</v>
+      </c>
+      <c r="B55" t="s">
+        <v>542</v>
+      </c>
+      <c r="C55" t="s">
+        <v>304</v>
+      </c>
+      <c r="D55" t="s">
+        <v>276</v>
+      </c>
+      <c r="E55" t="s">
+        <v>543</v>
+      </c>
+      <c r="F55" t="s">
+        <v>270</v>
+      </c>
+      <c r="H55" s="2" t="s">
+        <v>544</v>
+      </c>
+    </row>
+    <row r="56" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A56" t="s">
+        <v>545</v>
+      </c>
+      <c r="B56" t="s">
+        <v>429</v>
+      </c>
+      <c r="C56" t="s">
+        <v>430</v>
+      </c>
+      <c r="D56" t="s">
+        <v>276</v>
+      </c>
+      <c r="E56" t="s">
+        <v>546</v>
+      </c>
+      <c r="F56" t="s">
+        <v>440</v>
+      </c>
+      <c r="H56" s="2" t="s">
+        <v>547</v>
+      </c>
+    </row>
+    <row r="57" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A57" t="s">
+        <v>548</v>
+      </c>
+      <c r="B57" t="s">
+        <v>429</v>
+      </c>
+      <c r="C57" t="s">
+        <v>430</v>
+      </c>
+      <c r="D57" t="s">
+        <v>276</v>
+      </c>
+      <c r="E57" t="s">
+        <v>549</v>
+      </c>
+      <c r="F57" t="s">
+        <v>440</v>
+      </c>
+      <c r="H57" s="2" t="s">
+        <v>550</v>
+      </c>
+    </row>
+    <row r="58" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A58" t="s">
+        <v>551</v>
+      </c>
+      <c r="B58" t="s">
+        <v>552</v>
+      </c>
+      <c r="C58" t="s">
+        <v>553</v>
+      </c>
+      <c r="D58" t="s">
+        <v>276</v>
+      </c>
+      <c r="E58" t="s">
+        <v>554</v>
+      </c>
+      <c r="F58" t="s">
+        <v>270</v>
+      </c>
+      <c r="H58" s="2" t="s">
+        <v>555</v>
+      </c>
+    </row>
+    <row r="59" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A59" t="s">
+        <v>556</v>
+      </c>
+      <c r="B59" t="s">
+        <v>557</v>
+      </c>
+      <c r="C59" t="s">
+        <v>282</v>
+      </c>
+      <c r="D59" t="s">
+        <v>276</v>
+      </c>
+      <c r="E59" t="s">
+        <v>558</v>
+      </c>
+      <c r="F59" t="s">
+        <v>559</v>
+      </c>
+      <c r="H59" s="2" t="s">
+        <v>560</v>
+      </c>
+    </row>
+    <row r="60" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A60" t="s">
+        <v>561</v>
+      </c>
+      <c r="B60" t="s">
+        <v>562</v>
+      </c>
+      <c r="C60" t="s">
+        <v>563</v>
+      </c>
+      <c r="D60" t="s">
+        <v>276</v>
+      </c>
+      <c r="E60" t="s">
+        <v>564</v>
+      </c>
+      <c r="F60" t="s">
+        <v>565</v>
+      </c>
+      <c r="H60" s="2" t="s">
+        <v>566</v>
+      </c>
+    </row>
+    <row r="61" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A61" t="s">
+        <v>567</v>
+      </c>
+      <c r="B61" t="s">
+        <v>568</v>
+      </c>
+      <c r="C61" t="s">
+        <v>569</v>
+      </c>
+      <c r="D61" t="s">
+        <v>389</v>
+      </c>
+      <c r="E61" t="s">
+        <v>270</v>
+      </c>
+      <c r="F61" t="s">
+        <v>570</v>
+      </c>
+      <c r="H61" s="2" t="s">
+        <v>571</v>
+      </c>
+    </row>
+    <row r="62" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A62" t="s">
+        <v>572</v>
+      </c>
+      <c r="B62" t="s">
+        <v>573</v>
+      </c>
+      <c r="C62" t="s">
+        <v>574</v>
+      </c>
+      <c r="D62" t="s">
+        <v>276</v>
+      </c>
+      <c r="E62" t="s">
+        <v>575</v>
+      </c>
+      <c r="F62" t="s">
+        <v>576</v>
+      </c>
+      <c r="H62" s="2" t="s">
+        <v>577</v>
+      </c>
+    </row>
+    <row r="63" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A63" t="s">
+        <v>578</v>
+      </c>
+      <c r="B63" t="s">
+        <v>579</v>
+      </c>
+      <c r="C63" t="s">
+        <v>282</v>
+      </c>
+      <c r="D63" t="s">
+        <v>276</v>
+      </c>
+      <c r="E63" t="s">
+        <v>580</v>
+      </c>
+      <c r="F63" t="s">
+        <v>581</v>
+      </c>
+      <c r="H63" s="2" t="s">
+        <v>582</v>
+      </c>
+    </row>
+    <row r="64" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A64" t="s">
+        <v>583</v>
+      </c>
+      <c r="B64" t="s">
+        <v>303</v>
+      </c>
+      <c r="C64" t="s">
+        <v>584</v>
+      </c>
+      <c r="D64" t="s">
+        <v>276</v>
+      </c>
+      <c r="E64" t="s">
+        <v>585</v>
+      </c>
+      <c r="F64" t="s">
+        <v>306</v>
+      </c>
+      <c r="H64" s="2" t="s">
+        <v>586</v>
+      </c>
+    </row>
+    <row r="65" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A65" t="s">
+        <v>587</v>
+      </c>
+      <c r="B65" t="s">
+        <v>588</v>
+      </c>
+      <c r="C65" t="s">
+        <v>589</v>
+      </c>
+      <c r="D65" t="s">
+        <v>276</v>
+      </c>
+      <c r="E65" t="s">
+        <v>289</v>
+      </c>
+      <c r="F65" t="s">
+        <v>590</v>
+      </c>
+      <c r="H65" s="2" t="s">
+        <v>591</v>
+      </c>
+    </row>
+    <row r="66" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A66" t="s">
+        <v>592</v>
+      </c>
+      <c r="B66" t="s">
+        <v>593</v>
+      </c>
+      <c r="C66" t="s">
+        <v>594</v>
+      </c>
+      <c r="D66" t="s">
+        <v>276</v>
+      </c>
+      <c r="E66" t="s">
+        <v>595</v>
+      </c>
+      <c r="F66" t="s">
+        <v>596</v>
+      </c>
+      <c r="H66" s="2" t="s">
+        <v>597</v>
+      </c>
+    </row>
+    <row r="67" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A67" t="s">
+        <v>598</v>
+      </c>
+      <c r="B67" t="s">
+        <v>599</v>
+      </c>
+      <c r="C67" t="s">
+        <v>600</v>
+      </c>
+      <c r="D67" t="s">
+        <v>276</v>
+      </c>
+      <c r="E67" t="s">
+        <v>411</v>
+      </c>
+      <c r="F67" t="s">
+        <v>601</v>
+      </c>
+      <c r="H67" s="2" t="s">
+        <v>602</v>
+      </c>
+    </row>
+    <row r="68" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A68" t="s">
+        <v>603</v>
+      </c>
+      <c r="B68" t="s">
+        <v>604</v>
+      </c>
+      <c r="C68" t="s">
+        <v>282</v>
+      </c>
+      <c r="D68" t="s">
+        <v>276</v>
+      </c>
+      <c r="E68" t="s">
+        <v>605</v>
+      </c>
+      <c r="F68" t="s">
+        <v>606</v>
+      </c>
+      <c r="H68" s="2" t="s">
+        <v>607</v>
+      </c>
+    </row>
+    <row r="69" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A69" t="s">
+        <v>608</v>
+      </c>
+      <c r="B69" t="s">
+        <v>609</v>
+      </c>
+      <c r="C69" t="s">
+        <v>610</v>
+      </c>
+      <c r="D69" t="s">
+        <v>276</v>
+      </c>
+      <c r="E69" t="s">
+        <v>611</v>
+      </c>
+      <c r="F69" t="s">
+        <v>612</v>
+      </c>
+      <c r="H69" s="2" t="s">
+        <v>613</v>
+      </c>
+    </row>
+    <row r="70" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A70" t="s">
+        <v>614</v>
+      </c>
+      <c r="B70" t="s">
+        <v>615</v>
+      </c>
+      <c r="C70" t="s">
+        <v>282</v>
+      </c>
+      <c r="D70" t="s">
+        <v>276</v>
+      </c>
+      <c r="E70" t="s">
+        <v>616</v>
+      </c>
+      <c r="F70" t="s">
+        <v>617</v>
+      </c>
+      <c r="H70" s="2" t="s">
+        <v>618</v>
+      </c>
+    </row>
+    <row r="71" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A71" t="s">
+        <v>619</v>
+      </c>
+      <c r="B71" t="s">
+        <v>620</v>
+      </c>
+      <c r="C71" t="s">
+        <v>401</v>
+      </c>
+      <c r="D71" t="s">
+        <v>276</v>
+      </c>
+      <c r="E71" t="s">
+        <v>621</v>
+      </c>
+      <c r="F71" t="s">
+        <v>622</v>
+      </c>
+      <c r="H71" s="2" t="s">
+        <v>623</v>
+      </c>
+    </row>
+    <row r="72" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A72" t="s">
+        <v>624</v>
+      </c>
+      <c r="B72" t="s">
+        <v>625</v>
+      </c>
+      <c r="C72" t="s">
+        <v>626</v>
+      </c>
+      <c r="D72" t="s">
+        <v>276</v>
+      </c>
+      <c r="E72" t="s">
+        <v>627</v>
+      </c>
+      <c r="F72" t="s">
+        <v>539</v>
+      </c>
+      <c r="H72" s="2" t="s">
+        <v>628</v>
+      </c>
+    </row>
+    <row r="73" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A73" t="s">
+        <v>629</v>
+      </c>
+      <c r="B73" t="s">
+        <v>630</v>
+      </c>
+      <c r="C73" t="s">
+        <v>282</v>
+      </c>
+      <c r="D73" t="s">
+        <v>276</v>
+      </c>
+      <c r="E73" t="s">
+        <v>631</v>
+      </c>
+      <c r="F73" t="s">
+        <v>270</v>
+      </c>
+      <c r="H73" s="2" t="s">
+        <v>632</v>
+      </c>
+    </row>
+    <row r="74" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A74" t="s">
+        <v>633</v>
+      </c>
+      <c r="B74" t="s">
+        <v>634</v>
+      </c>
+      <c r="C74" t="s">
+        <v>282</v>
+      </c>
+      <c r="D74" t="s">
+        <v>276</v>
+      </c>
+      <c r="E74" t="s">
+        <v>635</v>
+      </c>
+      <c r="F74" t="s">
+        <v>636</v>
+      </c>
+      <c r="H74" s="2" t="s">
+        <v>637</v>
+      </c>
+    </row>
+    <row r="75" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A75" t="s">
+        <v>212</v>
+      </c>
+      <c r="B75" t="s">
+        <v>516</v>
+      </c>
+      <c r="C75" t="s">
+        <v>517</v>
+      </c>
+      <c r="D75" t="s">
+        <v>276</v>
+      </c>
+      <c r="E75" t="s">
+        <v>347</v>
+      </c>
+      <c r="F75" t="s">
+        <v>638</v>
+      </c>
+      <c r="H75" s="2" t="s">
+        <v>639</v>
+      </c>
+    </row>
+    <row r="76" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A76" t="s">
+        <v>640</v>
+      </c>
+      <c r="B76" t="s">
+        <v>641</v>
+      </c>
+      <c r="C76" t="s">
+        <v>642</v>
+      </c>
+      <c r="D76" t="s">
+        <v>276</v>
+      </c>
+      <c r="E76" t="s">
+        <v>643</v>
+      </c>
+      <c r="F76" t="s">
+        <v>270</v>
+      </c>
+      <c r="H76" s="2" t="s">
+        <v>644</v>
+      </c>
+    </row>
+    <row r="77" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A77" t="s">
+        <v>645</v>
+      </c>
+      <c r="B77" t="s">
+        <v>641</v>
+      </c>
+      <c r="C77" t="s">
+        <v>642</v>
+      </c>
+      <c r="D77" t="s">
+        <v>276</v>
+      </c>
+      <c r="E77" t="s">
+        <v>646</v>
+      </c>
+      <c r="F77" t="s">
+        <v>270</v>
+      </c>
+      <c r="H77" s="2" t="s">
+        <v>647</v>
+      </c>
+    </row>
+    <row r="78" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A78" t="s">
+        <v>648</v>
+      </c>
+      <c r="B78" t="s">
+        <v>649</v>
+      </c>
+      <c r="C78" t="s">
+        <v>650</v>
+      </c>
+      <c r="D78" t="s">
+        <v>276</v>
+      </c>
+      <c r="E78" t="s">
+        <v>651</v>
+      </c>
+      <c r="F78" t="s">
+        <v>652</v>
+      </c>
+      <c r="H78" s="2" t="s">
+        <v>653</v>
+      </c>
+    </row>
+    <row r="79" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A79" t="s">
+        <v>654</v>
+      </c>
+      <c r="B79" t="s">
+        <v>655</v>
+      </c>
+      <c r="C79" t="s">
+        <v>656</v>
+      </c>
+      <c r="D79" t="s">
+        <v>276</v>
+      </c>
+      <c r="E79" t="s">
+        <v>657</v>
+      </c>
+      <c r="F79" t="s">
+        <v>539</v>
+      </c>
+      <c r="H79" s="2" t="s">
+        <v>658</v>
+      </c>
+    </row>
+    <row r="80" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A80" t="s">
+        <v>659</v>
+      </c>
+      <c r="B80" t="s">
+        <v>655</v>
+      </c>
+      <c r="C80" t="s">
+        <v>660</v>
+      </c>
+      <c r="D80" t="s">
+        <v>276</v>
+      </c>
+      <c r="E80" t="s">
+        <v>657</v>
+      </c>
+      <c r="F80" t="s">
+        <v>539</v>
+      </c>
+      <c r="H80" s="2" t="s">
+        <v>661</v>
+      </c>
+    </row>
+    <row r="81" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A81" t="s">
+        <v>662</v>
+      </c>
+      <c r="B81" t="s">
+        <v>521</v>
+      </c>
+      <c r="C81" t="s">
+        <v>282</v>
+      </c>
+      <c r="D81" t="s">
+        <v>276</v>
+      </c>
+      <c r="E81" t="s">
+        <v>522</v>
+      </c>
+      <c r="F81" t="s">
+        <v>663</v>
+      </c>
+      <c r="H81" s="2" t="s">
+        <v>664</v>
+      </c>
+    </row>
+    <row r="82" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A82" t="s">
+        <v>665</v>
+      </c>
+      <c r="B82" t="s">
+        <v>666</v>
+      </c>
+      <c r="C82" t="s">
+        <v>667</v>
+      </c>
+      <c r="D82" t="s">
+        <v>276</v>
+      </c>
+      <c r="E82" t="s">
+        <v>668</v>
+      </c>
+      <c r="F82" t="s">
+        <v>669</v>
+      </c>
+      <c r="H82" s="2" t="s">
+        <v>670</v>
+      </c>
+    </row>
+    <row r="83" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A83" t="s">
+        <v>671</v>
+      </c>
+      <c r="B83" t="s">
+        <v>309</v>
+      </c>
+      <c r="C83" t="s">
+        <v>310</v>
+      </c>
+      <c r="D83" t="s">
+        <v>389</v>
+      </c>
+      <c r="E83" t="s">
+        <v>270</v>
+      </c>
+      <c r="F83" t="s">
+        <v>312</v>
+      </c>
+      <c r="H83" s="2" t="s">
+        <v>672</v>
+      </c>
+    </row>
+    <row r="84" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A84" t="s">
+        <v>673</v>
+      </c>
+      <c r="B84" t="s">
+        <v>674</v>
+      </c>
+      <c r="C84" t="s">
+        <v>675</v>
+      </c>
+      <c r="D84" t="s">
+        <v>276</v>
+      </c>
+      <c r="E84" t="s">
+        <v>676</v>
+      </c>
+      <c r="F84" t="s">
+        <v>677</v>
+      </c>
+      <c r="H84" s="2" t="s">
+        <v>678</v>
+      </c>
+    </row>
+    <row r="85" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A85" t="s">
+        <v>679</v>
+      </c>
+      <c r="B85" t="s">
+        <v>680</v>
+      </c>
+      <c r="C85" t="s">
+        <v>681</v>
+      </c>
+      <c r="D85" t="s">
+        <v>276</v>
+      </c>
+      <c r="E85" t="s">
+        <v>643</v>
+      </c>
+      <c r="F85" t="s">
+        <v>565</v>
+      </c>
+      <c r="H85" s="2" t="s">
+        <v>682</v>
+      </c>
+    </row>
+    <row r="86" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A86" t="s">
+        <v>683</v>
+      </c>
+      <c r="B86" t="s">
+        <v>684</v>
+      </c>
+      <c r="C86" t="s">
+        <v>310</v>
+      </c>
+      <c r="D86" t="s">
+        <v>276</v>
+      </c>
+      <c r="E86" t="s">
+        <v>685</v>
+      </c>
+      <c r="F86" t="s">
+        <v>290</v>
+      </c>
+      <c r="H86" s="2" t="s">
+        <v>686</v>
+      </c>
+    </row>
+    <row r="87" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A87" t="s">
+        <v>683</v>
+      </c>
+      <c r="B87" t="s">
+        <v>684</v>
+      </c>
+      <c r="C87" t="s">
+        <v>687</v>
+      </c>
+      <c r="D87" t="s">
+        <v>276</v>
+      </c>
+      <c r="E87" t="s">
+        <v>685</v>
+      </c>
+      <c r="F87" t="s">
+        <v>290</v>
+      </c>
+      <c r="H87" s="2" t="s">
+        <v>688</v>
+      </c>
+    </row>
+    <row r="88" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A88" t="s">
+        <v>683</v>
+      </c>
+      <c r="B88" t="s">
+        <v>684</v>
+      </c>
+      <c r="C88" t="s">
+        <v>689</v>
+      </c>
+      <c r="D88" t="s">
+        <v>276</v>
+      </c>
+      <c r="E88" t="s">
+        <v>685</v>
+      </c>
+      <c r="F88" t="s">
+        <v>290</v>
+      </c>
+      <c r="H88" s="2" t="s">
+        <v>690</v>
+      </c>
+    </row>
+    <row r="89" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A89" t="s">
+        <v>683</v>
+      </c>
+      <c r="B89" t="s">
+        <v>684</v>
+      </c>
+      <c r="C89" t="s">
+        <v>342</v>
+      </c>
+      <c r="D89" t="s">
+        <v>276</v>
+      </c>
+      <c r="E89" t="s">
+        <v>685</v>
+      </c>
+      <c r="F89" t="s">
+        <v>290</v>
+      </c>
+      <c r="H89" s="2" t="s">
+        <v>691</v>
+      </c>
+    </row>
+    <row r="90" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A90" t="s">
+        <v>692</v>
+      </c>
+      <c r="B90" t="s">
+        <v>630</v>
+      </c>
+      <c r="C90" t="s">
+        <v>282</v>
+      </c>
+      <c r="D90" t="s">
+        <v>276</v>
+      </c>
+      <c r="E90" t="s">
+        <v>693</v>
+      </c>
+      <c r="F90" t="s">
+        <v>270</v>
+      </c>
+      <c r="H90" s="2" t="s">
+        <v>694</v>
+      </c>
+    </row>
+    <row r="91" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A91" t="s">
+        <v>695</v>
+      </c>
+      <c r="B91" t="s">
+        <v>696</v>
+      </c>
+      <c r="C91" t="s">
+        <v>697</v>
+      </c>
+      <c r="D91" t="s">
+        <v>276</v>
+      </c>
+      <c r="E91" t="s">
+        <v>698</v>
+      </c>
+      <c r="F91" t="s">
+        <v>699</v>
+      </c>
+      <c r="H91" s="2" t="s">
+        <v>700</v>
+      </c>
+    </row>
   </sheetData>
   <autoFilter ref="A1:H1"/>
+  <hyperlinks>
+    <hyperlink ref="H2" r:id="rId1"/>
+    <hyperlink ref="H3" r:id="rId2"/>
+    <hyperlink ref="H4" r:id="rId3"/>
+    <hyperlink ref="H5" r:id="rId4"/>
+    <hyperlink ref="H6" r:id="rId5"/>
+    <hyperlink ref="H7" r:id="rId6"/>
+    <hyperlink ref="H8" r:id="rId7"/>
+    <hyperlink ref="H9" r:id="rId8"/>
+    <hyperlink ref="H10" r:id="rId9"/>
+    <hyperlink ref="H11" r:id="rId10"/>
+    <hyperlink ref="H12" r:id="rId11"/>
+    <hyperlink ref="H13" r:id="rId12"/>
+    <hyperlink ref="H14" r:id="rId13"/>
+    <hyperlink ref="H15" r:id="rId14"/>
+    <hyperlink ref="H16" r:id="rId15"/>
+    <hyperlink ref="H17" r:id="rId16"/>
+    <hyperlink ref="H18" r:id="rId17"/>
+    <hyperlink ref="H19" r:id="rId18"/>
+    <hyperlink ref="H20" r:id="rId19"/>
+    <hyperlink ref="H21" r:id="rId20"/>
+    <hyperlink ref="H22" r:id="rId21"/>
+    <hyperlink ref="H23" r:id="rId22"/>
+    <hyperlink ref="H24" r:id="rId23"/>
+    <hyperlink ref="H25" r:id="rId24"/>
+    <hyperlink ref="H26" r:id="rId25"/>
+    <hyperlink ref="H27" r:id="rId26"/>
+    <hyperlink ref="H28" r:id="rId27"/>
+    <hyperlink ref="H29" r:id="rId28"/>
+    <hyperlink ref="H30" r:id="rId29"/>
+    <hyperlink ref="H31" r:id="rId30"/>
+    <hyperlink ref="H32" r:id="rId31"/>
+    <hyperlink ref="H33" r:id="rId32"/>
+    <hyperlink ref="H34" r:id="rId33"/>
+    <hyperlink ref="H35" r:id="rId34"/>
+    <hyperlink ref="H36" r:id="rId35"/>
+    <hyperlink ref="H37" r:id="rId36"/>
+    <hyperlink ref="H38" r:id="rId37"/>
+    <hyperlink ref="H39" r:id="rId38"/>
+    <hyperlink ref="H40" r:id="rId39"/>
+    <hyperlink ref="H41" r:id="rId40"/>
+    <hyperlink ref="H42" r:id="rId41"/>
+    <hyperlink ref="H43" r:id="rId42"/>
+    <hyperlink ref="H44" r:id="rId43"/>
+    <hyperlink ref="H45" r:id="rId44"/>
+    <hyperlink ref="H46" r:id="rId45"/>
+    <hyperlink ref="H47" r:id="rId46"/>
+    <hyperlink ref="H48" r:id="rId47"/>
+    <hyperlink ref="H49" r:id="rId48"/>
+    <hyperlink ref="H50" r:id="rId49"/>
+    <hyperlink ref="H51" r:id="rId50"/>
+    <hyperlink ref="H52" r:id="rId51"/>
+    <hyperlink ref="H53" r:id="rId52"/>
+    <hyperlink ref="H54" r:id="rId53"/>
+    <hyperlink ref="H55" r:id="rId54"/>
+    <hyperlink ref="H56" r:id="rId55"/>
+    <hyperlink ref="H57" r:id="rId56"/>
+    <hyperlink ref="H58" r:id="rId57"/>
+    <hyperlink ref="H59" r:id="rId58"/>
+    <hyperlink ref="H60" r:id="rId59"/>
+    <hyperlink ref="H61" r:id="rId60"/>
+    <hyperlink ref="H62" r:id="rId61"/>
+    <hyperlink ref="H63" r:id="rId62"/>
+    <hyperlink ref="H64" r:id="rId63"/>
+    <hyperlink ref="H65" r:id="rId64"/>
+    <hyperlink ref="H66" r:id="rId65"/>
+    <hyperlink ref="H67" r:id="rId66"/>
+    <hyperlink ref="H68" r:id="rId67"/>
+    <hyperlink ref="H69" r:id="rId68"/>
+    <hyperlink ref="H70" r:id="rId69"/>
+    <hyperlink ref="H71" r:id="rId70"/>
+    <hyperlink ref="H72" r:id="rId71"/>
+    <hyperlink ref="H73" r:id="rId72"/>
+    <hyperlink ref="H74" r:id="rId73"/>
+    <hyperlink ref="H75" r:id="rId74"/>
+    <hyperlink ref="H76" r:id="rId75"/>
+    <hyperlink ref="H77" r:id="rId76"/>
+    <hyperlink ref="H78" r:id="rId77"/>
+    <hyperlink ref="H79" r:id="rId78"/>
+    <hyperlink ref="H80" r:id="rId79"/>
+    <hyperlink ref="H81" r:id="rId80"/>
+    <hyperlink ref="H82" r:id="rId81"/>
+    <hyperlink ref="H83" r:id="rId82"/>
+    <hyperlink ref="H84" r:id="rId83"/>
+    <hyperlink ref="H85" r:id="rId84"/>
+    <hyperlink ref="H86" r:id="rId85"/>
+    <hyperlink ref="H87" r:id="rId86"/>
+    <hyperlink ref="H88" r:id="rId87"/>
+    <hyperlink ref="H89" r:id="rId88"/>
+    <hyperlink ref="H90" r:id="rId89"/>
+    <hyperlink ref="H91" r:id="rId90"/>
+  </hyperlinks>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup orientation="portrait" horizontalDpi="4294967295" verticalDpi="4294967295" scale="100" fitToWidth="1" fitToHeight="1"/>
 </worksheet>

--- a/docs/xlsx/jobs-2026-10-01.xlsx
+++ b/docs/xlsx/jobs-2026-10-01.xlsx
@@ -14,7 +14,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1026" uniqueCount="701">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1247" uniqueCount="834">
   <si>
     <t>Title</t>
   </si>
@@ -796,6 +796,30 @@
     <t>https://www.conservationjobboard.com/job-listing-wildlife-habitat-biologist---south-dakota-philip-or-kadoka-south-dakota/4251936345</t>
   </si>
   <si>
+    <t>Environmental Engineer</t>
+  </si>
+  <si>
+    <t>Environmental Integrity Project</t>
+  </si>
+  <si>
+    <t>Remote</t>
+  </si>
+  <si>
+    <t>Full-Time</t>
+  </si>
+  <si>
+    <t>100,000 and above</t>
+  </si>
+  <si>
+    <t>Environmental</t>
+  </si>
+  <si>
+    <t>Idealist</t>
+  </si>
+  <si>
+    <t>https://greenjobs.greenjobsearch.org/jobs/environmental-engineer-2/</t>
+  </si>
+  <si>
     <t>Field Crewmember</t>
   </si>
   <si>
@@ -808,9 +832,6 @@
     <t>20,000 - 40,000</t>
   </si>
   <si>
-    <t>Environmental</t>
-  </si>
-  <si>
     <t>https://greenjobs.greenjobsearch.org/jobs/field-crewmember/</t>
   </si>
   <si>
@@ -823,9 +844,6 @@
     <t>Wheaton-Glenmont, Maryland, United States</t>
   </si>
   <si>
-    <t>Full-Time</t>
-  </si>
-  <si>
     <t/>
   </si>
   <si>
@@ -835,6 +853,24 @@
     <t>https://greenjobs.greenjobsearch.org/jobs/senior-planning-specialist-zero-waste-programs-grade-25/</t>
   </si>
   <si>
+    <t>Trail and Watershed Outreach Coordinator</t>
+  </si>
+  <si>
+    <t>Clean Air Council</t>
+  </si>
+  <si>
+    <t>Philadelphia, Pennsylvania, United States</t>
+  </si>
+  <si>
+    <t>40,000 - 60,000</t>
+  </si>
+  <si>
+    <t>Land Use</t>
+  </si>
+  <si>
+    <t>https://greenjobs.greenjobsearch.org/jobs/trail-and-watershed-outreach-coordinator/</t>
+  </si>
+  <si>
     <t>Administrativo y atención a socios</t>
   </si>
   <si>
@@ -856,15 +892,30 @@
     <t>https://www.idealist.org/en/nonprofit-job/14dbd4a827594fa4832b53db538ac52d-administrativo-y-atencion-a-socios-survival-international-en-espanol-madrid</t>
   </si>
   <si>
+    <t>Advancement Director, Great Lakes Chapter</t>
+  </si>
+  <si>
+    <t>Parkinson's Foundation</t>
+  </si>
+  <si>
+    <t>Remote (Ohio)</t>
+  </si>
+  <si>
+    <t>USD 75000.00 - 85000.00/year</t>
+  </si>
+  <si>
+    <t>Health Medicine</t>
+  </si>
+  <si>
+    <t>https://www.idealist.org/en/nonprofit-job/f33c3924aeeb4f91b2dbbbdbdf2c759c-advancement-director-great-lakes-chapter-parkinsons-foundation-miami</t>
+  </si>
+  <si>
     <t>Africa Director</t>
   </si>
   <si>
     <t>Re:wild</t>
   </si>
   <si>
-    <t>Remote</t>
-  </si>
-  <si>
     <t>USD 115000.00 - 130000.00/year</t>
   </si>
   <si>
@@ -1006,6 +1057,24 @@
     <t>https://www.idealist.org/en/nonprofit-job/584520a7e9784c2f8466a7f62fee7371-bilingual-therapist-domestic-and-sexual-violence-doorways-arlington</t>
   </si>
   <si>
+    <t>Board Member - Innovative Education Management (IEM) Board of Directors</t>
+  </si>
+  <si>
+    <t>Innovative Education Management</t>
+  </si>
+  <si>
+    <t>Placerville, California</t>
+  </si>
+  <si>
+    <t>Part Time</t>
+  </si>
+  <si>
+    <t>Children Youth, Education</t>
+  </si>
+  <si>
+    <t>https://www.idealist.org/en/nonprofit-job/9a81977ff9214578949eb7191c7c4785-board-member-innovative-education-management-iem-board-of-directors-innovative-education-management-placerville</t>
+  </si>
+  <si>
     <t>Case Management Specialist</t>
   </si>
   <si>
@@ -1021,6 +1090,18 @@
     <t>https://www.idealist.org/en/job/9fb2e1db465844e89572a466bd4fc286-case-management-specialist-bridge-over-troubled-water-boston</t>
   </si>
   <si>
+    <t>Chief of Institutional Advancement</t>
+  </si>
+  <si>
+    <t>The Centers</t>
+  </si>
+  <si>
+    <t>Cleveland, Ohio</t>
+  </si>
+  <si>
+    <t>https://www.idealist.org/en/job/f7962f3834f64024b4c3f48ddde3b743-chief-of-institutional-advancement-the-centers-cleveland</t>
+  </si>
+  <si>
     <t>Chief Operating Officer (COO)</t>
   </si>
   <si>
@@ -1099,6 +1180,18 @@
     <t>https://www.idealist.org/en/nonprofit-job/fce45b1901b545b098041d3380bcb8d5-community-engagement-manager-project-citizenship-boston</t>
   </si>
   <si>
+    <t>Community Partners Trainer (RN)</t>
+  </si>
+  <si>
+    <t>Contract</t>
+  </si>
+  <si>
+    <t>USD 50.00 - 50.00/hour</t>
+  </si>
+  <si>
+    <t>https://www.idealist.org/en/nonprofit-job/0b45179e006c4c7f9f0c831ce50d109e-community-partners-trainer-rn-parkinsons-foundation-miami</t>
+  </si>
+  <si>
     <t>Community Relations Director</t>
   </si>
   <si>
@@ -1108,9 +1201,6 @@
     <t>Madison, Wisconsin</t>
   </si>
   <si>
-    <t>USD 75000.00 - 85000.00/year</t>
-  </si>
-  <si>
     <t>Civic Engagement, Education, Conflict Resolution</t>
   </si>
   <si>
@@ -1123,15 +1213,45 @@
     <t>Connectedly</t>
   </si>
   <si>
-    <t>Part Time</t>
-  </si>
-  <si>
     <t>Children Youth, Education, Family</t>
   </si>
   <si>
     <t>https://www.idealist.org/en/nonprofit-job/284113e0becb416d8d0f2cc36a8cc585-corporate-individual-gift-officer-connectedly-philadelphia</t>
   </si>
   <si>
+    <t>Corporate Partnerships Manager</t>
+  </si>
+  <si>
+    <t>SONRISAS DENTAL HEALTH INC</t>
+  </si>
+  <si>
+    <t>San Mateo, California</t>
+  </si>
+  <si>
+    <t>USD 85000.00 - 95000.00/year</t>
+  </si>
+  <si>
+    <t>Health Medicine, Seniors Retirement, Volunteering</t>
+  </si>
+  <si>
+    <t>https://www.idealist.org/en/nonprofit-job/09bc6c9cd8c54003b1246cc5b7d38fd7-corporate-partnerships-manager-sonrisas-dental-health-inc-san-mateo</t>
+  </si>
+  <si>
+    <t>Customer (Member) Success Manager</t>
+  </si>
+  <si>
+    <t>Hello Insight</t>
+  </si>
+  <si>
+    <t>USD 60000.00 - 60000.00/year</t>
+  </si>
+  <si>
+    <t>Children Youth</t>
+  </si>
+  <si>
+    <t>https://www.idealist.org/en/consultant-job/264231fb46c6494ebed7afceaa449498-customer-member-success-manager-hello-insight-baltimore</t>
+  </si>
+  <si>
     <t>Development &amp; Communications Specialist</t>
   </si>
   <si>
@@ -1165,6 +1285,18 @@
     <t>https://www.idealist.org/en/nonprofit-job/d386a79a793e43dba8cc0fe7be74a813-development-associate-asian-pacific-fund-san-francisco</t>
   </si>
   <si>
+    <t>Development Manager</t>
+  </si>
+  <si>
+    <t>exalt youth</t>
+  </si>
+  <si>
+    <t>USD 80000.00 - 90000.00/year</t>
+  </si>
+  <si>
+    <t>https://www.idealist.org/en/nonprofit-job/52d9aee788e9439aa29ee64fda4fdb74-development-manager-exalt-youth-new-york</t>
+  </si>
+  <si>
     <t>Development Officer</t>
   </si>
   <si>
@@ -1177,15 +1309,24 @@
     <t>https://www.idealist.org/en/job/7a0275774c344b8b89d606ed54bb4d2a-development-officer-all-stars-project-inc-new-york</t>
   </si>
   <si>
+    <t>Development Operations Senior Coordinator</t>
+  </si>
+  <si>
+    <t>Shalom Hartman Institute of North America</t>
+  </si>
+  <si>
+    <t>USD 68000.00 - 71000.00/year</t>
+  </si>
+  <si>
+    <t>https://www.idealist.org/en/nonprofit-job/74e97befae3a4da893c744bdfbcf70d2-development-operations-senior-coordinator-shalom-hartman-institute-of-north-america-new-york</t>
+  </si>
+  <si>
     <t>Development, Fundraising and Grants Manager</t>
   </si>
   <si>
     <t>Woman, Cradle of Abundance</t>
   </si>
   <si>
-    <t>Contract</t>
-  </si>
-  <si>
     <t>USD 35.00/hour</t>
   </si>
   <si>
@@ -1267,6 +1408,33 @@
     <t>https://www.idealist.org/en/job/1069753450d44dfc8766047230930593-director-of-development-and-communications-dc-history-center-washington</t>
   </si>
   <si>
+    <t>Director of Development, Grateful Patient &amp; Family, HSC/UNMH</t>
+  </si>
+  <si>
+    <t>University of New Mexico Foundation, Inc.</t>
+  </si>
+  <si>
+    <t>Albuquerque, New Mexico</t>
+  </si>
+  <si>
+    <t>USD 80000.00 - 105000.00/year</t>
+  </si>
+  <si>
+    <t>Education, Health Medicine, Philanthropy</t>
+  </si>
+  <si>
+    <t>https://www.idealist.org/en/nonprofit-job/d5bb34fa21f54c60b40c87797fb312d8-director-of-development-grateful-patient-family-hscunmh-university-of-new-mexico-foundation-inc-albuquerque</t>
+  </si>
+  <si>
+    <t>Director of Development, UNM Hospitals &amp; UNM Children's Hospital</t>
+  </si>
+  <si>
+    <t>USD 80000.00 - 93000.00/year</t>
+  </si>
+  <si>
+    <t>https://www.idealist.org/en/nonprofit-job/953b3bda6c5d43899978e7edd41cc0d9-director-of-development-unm-hospitals-unm-childrens-hospital-university-of-new-mexico-foundation-inc-albuquerque</t>
+  </si>
+  <si>
     <t>Director of Education &amp; Community Engagement</t>
   </si>
   <si>
@@ -1276,15 +1444,30 @@
     <t>Santa Rosa, California</t>
   </si>
   <si>
-    <t>USD 80000.00 - 90000.00/year</t>
-  </si>
-  <si>
     <t>Arts Music, Children Youth, Community Development</t>
   </si>
   <si>
     <t>https://www.idealist.org/en/nonprofit-job/99970bde554c41339f5aae350d4851d9-director-of-education-community-engagement-santa-rosa-symphony-santa-rosa</t>
   </si>
   <si>
+    <t>Director of Philanthropy - Minnesota Northwoods</t>
+  </si>
+  <si>
+    <t>Trust for Public Land</t>
+  </si>
+  <si>
+    <t>Saint Paul, Minnesota</t>
+  </si>
+  <si>
+    <t>USD 130000.00 - 140000.00/year</t>
+  </si>
+  <si>
+    <t>Environment, Climate Change</t>
+  </si>
+  <si>
+    <t>https://www.idealist.org/en/nonprofit-job/c26eb55383614ff5b2d75652582a2f9c-director-of-philanthropy-minnesota-northwoods-trust-for-public-land-saint-paul</t>
+  </si>
+  <si>
     <t>Director of Philanthropy Operations</t>
   </si>
   <si>
@@ -1318,6 +1501,21 @@
     <t>https://www.idealist.org/en/nonprofit-job/dcdf3409284c4176a92d82c77c4d2338-director-of-planned-giving-jewish-federation-of-greater-houston-houston</t>
   </si>
   <si>
+    <t>Director, Learning Strategy</t>
+  </si>
+  <si>
+    <t>National Association of Community Health Centers</t>
+  </si>
+  <si>
+    <t>USD 137000.00 - 178000.00/year</t>
+  </si>
+  <si>
+    <t>Health Medicine, Policy</t>
+  </si>
+  <si>
+    <t>https://www.idealist.org/en/nonprofit-job/2e8bda4d4a0948948e745a67f565a86e-director-learning-strategy-national-association-of-community-health-centers-bethesda</t>
+  </si>
+  <si>
     <t>Director, Major Gifts</t>
   </si>
   <si>
@@ -1360,6 +1558,36 @@
     <t>https://www.idealist.org/en/government-job/62a307af33c74853b046a7b65b25adef-english-as-a-second-language-engagement-coordinator-forestry-environmental-planner-wa-state-department-of-natural-resources-olympia</t>
   </si>
   <si>
+    <t>USD 105000.00 - 132000.00/year</t>
+  </si>
+  <si>
+    <t>Environment</t>
+  </si>
+  <si>
+    <t>Green Jobs</t>
+  </si>
+  <si>
+    <t>https://www.idealist.org/en/nonprofit-job/24e541b302f445cbaeffe7701fb4274d-environmental-engineer-environmental-integrity-project-washington</t>
+  </si>
+  <si>
+    <t>Executive Assistant &amp; Outreach Coordinator</t>
+  </si>
+  <si>
+    <t>C-Change Conversations</t>
+  </si>
+  <si>
+    <t>Princeton, NJ</t>
+  </si>
+  <si>
+    <t>USD 25.00 - 35.00/hour</t>
+  </si>
+  <si>
+    <t>Climate Change, Environment, Education</t>
+  </si>
+  <si>
+    <t>https://www.idealist.org/en/nonprofit-job/9f94c1696cd747d8bbd89d34fe7d2808-executive-assistant-outreach-coordinator-c-change-conversations-princeton</t>
+  </si>
+  <si>
     <t>Executive Director</t>
   </si>
   <si>
@@ -1426,9 +1654,6 @@
     <t>USD 160000.00 - 190000.00/year</t>
   </si>
   <si>
-    <t>Environment</t>
-  </si>
-  <si>
     <t>https://www.idealist.org/en/nonprofit-job/db5dd06d2cf5404cb566411d09cc61e3-executive-vice-president-the-pacific-forest-trust-san-francisco</t>
   </si>
   <si>
@@ -1504,6 +1729,21 @@
     <t>https://www.idealist.org/en/nonprofit-job/7eb39fa95bee4a8dae172b1382bc5b51-immigrants-rights-staff-attorney-or-senior-attorney-position-takeroot-justice-new-york</t>
   </si>
   <si>
+    <t>Innovation Associate</t>
+  </si>
+  <si>
+    <t>Legal Services Corporation</t>
+  </si>
+  <si>
+    <t>USD 93250.00 - 97017.00/year</t>
+  </si>
+  <si>
+    <t>Legal Assistance, Education, Human Rights Civil Liberties</t>
+  </si>
+  <si>
+    <t>https://www.idealist.org/en/nonprofit-job/6759b0d5a36445a1a83e4a1dcccf47dc-innovation-associate-legal-services-corporation-washington</t>
+  </si>
+  <si>
     <t>Interim Director, Human Resources and Administration</t>
   </si>
   <si>
@@ -1519,6 +1759,36 @@
     <t>https://www.idealist.org/en/job/c33f8963945c44958a4976bbda1522dd-interim-director-human-resources-and-administration-careers-in-nonprofits-inc-san-francisco</t>
   </si>
   <si>
+    <t>Investigator</t>
+  </si>
+  <si>
+    <t>Federal Public Defender - Western District of Washington</t>
+  </si>
+  <si>
+    <t>USD 83935.00 - 141367.00/year</t>
+  </si>
+  <si>
+    <t>Legal Assistance</t>
+  </si>
+  <si>
+    <t>https://www.idealist.org/en/government-job/c003ae72617346d3b57ffed5e49dd4cf-investigator-federal-public-defender-western-district-of-washington-seattle</t>
+  </si>
+  <si>
+    <t>League Associate, Teacher (San Francisco, Palo Alto, Hillsborough)</t>
+  </si>
+  <si>
+    <t>League of Creative Minds, Academy of Debate and Diplomacy</t>
+  </si>
+  <si>
+    <t>USD 300.00 - 3000.00/week</t>
+  </si>
+  <si>
+    <t>Civic Engagement, Children Youth, Conflict Resolution</t>
+  </si>
+  <si>
+    <t>https://www.idealist.org/en/business-job/37016f051f014cf8973969eb4b6a2644-league-associate-teacher-san-francisco-palo-alto-hillsborough-league-of-creative-minds-academy-of-debate-and-diplomacy-san-francisco</t>
+  </si>
+  <si>
     <t>Manager, Philanthropy Reporting and Projects</t>
   </si>
   <si>
@@ -1546,6 +1816,21 @@
     <t>https://www.idealist.org/en/job/65663b8b92d949298145224fe638ca18-managing-director-movement-labs-movement-labs-new-york</t>
   </si>
   <si>
+    <t>Membership &amp; Visitor Services Assistant</t>
+  </si>
+  <si>
+    <t>Bay Area Discovery Museum</t>
+  </si>
+  <si>
+    <t>Sausalito, California</t>
+  </si>
+  <si>
+    <t>USD 22.05 - 23.05/hour</t>
+  </si>
+  <si>
+    <t>https://www.idealist.org/en/nonprofit-job/658aae3844dd405d94a813147f3560f2-membership-visitor-services-assistant-bay-area-discovery-museum-sausalito</t>
+  </si>
+  <si>
     <t>Membership Coordinator (4 Month Temporary)</t>
   </si>
   <si>
@@ -1627,15 +1912,27 @@
     <t>https://www.idealist.org/en/nonprofit-job/5b125c82b25c49c494fbe131c6131bfb-paralegal-hadassah-wzoa-inc-new-york</t>
   </si>
   <si>
+    <t>Americans for Immigrant Justice</t>
+  </si>
+  <si>
+    <t>Miami, Florida</t>
+  </si>
+  <si>
+    <t>USD 46000.00 - 71000.00/year</t>
+  </si>
+  <si>
+    <t>Children Youth, Family, Immigrants Or Refugees</t>
+  </si>
+  <si>
+    <t>https://www.idealist.org/en/nonprofit-job/cbaed116bcf841989005addec830d88a-paralegal-americans-for-immigrant-justice-miami</t>
+  </si>
+  <si>
     <t>Paralegal (full-time) at Law Firm Exclusively Serving Nonprofit/Tax-Exempt Organizations</t>
   </si>
   <si>
     <t>Cheshire Law Group</t>
   </si>
   <si>
-    <t>Legal Assistance</t>
-  </si>
-  <si>
     <t>https://www.idealist.org/en/consultant-job/26897cef5e54417cb8c5ad5840fb8dde-paralegal-full-time-at-law-firm-exclusively-serving-nonprofittax-exempt-organizations-cheshire-law-group-philadelphia</t>
   </si>
   <si>
@@ -1663,9 +1960,6 @@
     <t>Philanthropy Officer</t>
   </si>
   <si>
-    <t>USD 85000.00 - 95000.00/year</t>
-  </si>
-  <si>
     <t>https://www.idealist.org/en/nonprofit-job/5fa7315ac87d40e7b3440c475a144034-philanthropy-officer-jewish-federation-of-greater-houston-houston</t>
   </si>
   <si>
@@ -1744,9 +2038,6 @@
     <t>USD 24.00 - 26.00/hour</t>
   </si>
   <si>
-    <t>Children Youth</t>
-  </si>
-  <si>
     <t>https://www.idealist.org/en/nonprofit-job/1b2ed7928df0453e967166f9da87e6b7-program-coordinator-baby2baby-culver-city</t>
   </si>
   <si>
@@ -1765,6 +2056,21 @@
     <t>https://www.idealist.org/en/nonprofit-job/c455c9ac89b94111b9c6ac866a274dc3-program-manager-mental-health-education-growth-mental-health-collaborative-inc-hopkinton</t>
   </si>
   <si>
+    <t>Program Officer, Member Experience and Relations</t>
+  </si>
+  <si>
+    <t>Inclusiv</t>
+  </si>
+  <si>
+    <t>USD 90000.00 - 105000.00/year</t>
+  </si>
+  <si>
+    <t>Community Development, Economic Development</t>
+  </si>
+  <si>
+    <t>https://www.idealist.org/en/nonprofit-job/25c721493f73407bbcc8feefaf258e44-program-officer-member-experience-and-relations-inclusiv-new-york</t>
+  </si>
+  <si>
     <t>Project Manager</t>
   </si>
   <si>
@@ -1792,6 +2098,12 @@
     <t>https://www.idealist.org/en/nonprofit-job/e56d9f7595ae4879a2fdbc1946c4147c-public-policy-and-advocacy-associate-ct-community-nonprofit-alliance-inc-rocky-hill</t>
   </si>
   <si>
+    <t>Recruitment Manager</t>
+  </si>
+  <si>
+    <t>https://www.idealist.org/en/nonprofit-job/64f48c99002c4f11a2b61cfa1a2a2571-recruitment-manager-parkinsons-foundation-miami</t>
+  </si>
+  <si>
     <t>Salt Watch Coordinator</t>
   </si>
   <si>
@@ -1825,6 +2137,27 @@
     <t>https://www.idealist.org/en/nonprofit-job/b792deed69b24e2ba16bac108848475f-senior-communications-manager-ten-strands-san-francisco</t>
   </si>
   <si>
+    <t>Senior Director of Individual Giving</t>
+  </si>
+  <si>
+    <t>LifeMoves</t>
+  </si>
+  <si>
+    <t>Santa Clara, California</t>
+  </si>
+  <si>
+    <t>USD 155000.00 - 190000.00/year</t>
+  </si>
+  <si>
+    <t>https://www.idealist.org/en/nonprofit-job/a7f2f26b7ff240f78ad1b652c318635a-senior-director-of-individual-giving-lifemoves-santa-clara</t>
+  </si>
+  <si>
+    <t>Senior Director of Institutional Giving</t>
+  </si>
+  <si>
+    <t>https://www.idealist.org/en/nonprofit-job/2f774d7671114abfba6e5ff5badb6742-senior-director-of-institutional-giving-lifemoves-santa-clara</t>
+  </si>
+  <si>
     <t>Senior Grants &amp; Contracts Analyst</t>
   </si>
   <si>
@@ -1840,6 +2173,21 @@
     <t>https://www.idealist.org/en/nonprofit-job/89231fa18c9f429d893460a3a81247d6-senior-grants-contracts-analyst-rural-community-assistance-partnershipinc-washington</t>
   </si>
   <si>
+    <t>Senior Industry Specialist, IICM</t>
+  </si>
+  <si>
+    <t>Great Plains Institute</t>
+  </si>
+  <si>
+    <t>Minneapolis, Minnesota</t>
+  </si>
+  <si>
+    <t>USD 74000.00 - 84000.00/year</t>
+  </si>
+  <si>
+    <t>https://www.idealist.org/en/nonprofit-job/d75ae997843f442c92f2426e5dda5a7e-senior-industry-specialist-iicm-great-plains-institute-minneapolis</t>
+  </si>
+  <si>
     <t>Senior Manager, Corporate Partnerships &amp; Communications</t>
   </si>
   <si>
@@ -1936,6 +2284,12 @@
     <t>https://www.idealist.org/en/nonprofit-job/fe60e60144554603aadc728f6b25d003-staff-attorney-wafa-house-inc-woodland-park</t>
   </si>
   <si>
+    <t>USD 76230.00 - 129600.00/year</t>
+  </si>
+  <si>
+    <t>https://www.idealist.org/en/nonprofit-job/e18a159e82db4952a05a3ff290072b31-staff-attorney-americans-for-immigrant-justice-miami</t>
+  </si>
+  <si>
     <t>Staff Attorney – Housing and Disability Advocacy Program (HDAP)</t>
   </si>
   <si>
@@ -2035,6 +2389,15 @@
     <t>https://www.idealist.org/en/nonprofit-job/c08dbdca552d444bb4f761bf5b3497b2-substitute-teacher-freedom-side-school-philadelphia</t>
   </si>
   <si>
+    <t>Supervising Attorney</t>
+  </si>
+  <si>
+    <t>USD 85430.00 - 129600.00/year</t>
+  </si>
+  <si>
+    <t>https://www.idealist.org/en/nonprofit-job/6498692c79e2450aa0d1e12c86353a33-supervising-attorney-americans-for-immigrant-justice-miami</t>
+  </si>
+  <si>
     <t>Supervisory Youth Development Representative</t>
   </si>
   <si>
@@ -2053,6 +2416,21 @@
     <t>https://www.idealist.org/en/government-job/7f4bfc93351e48de9529b11f60a0f435-supervisory-youth-development-representative-district-of-columbia-department-of-youth-rehabilitation-services-laurel</t>
   </si>
   <si>
+    <t>Sustainability and Nutrition Rep. (Community Enrollment) - Tucson, AZ</t>
+  </si>
+  <si>
+    <t>Farm Fresh To You</t>
+  </si>
+  <si>
+    <t>Tucson, Arizona</t>
+  </si>
+  <si>
+    <t>USD 35000.00 - 90000.00/year</t>
+  </si>
+  <si>
+    <t>https://www.idealist.org/en/nonprofit-job/2792f1a2077e4f13b3b145bf4b5dff00-sustainability-and-nutrition-rep-community-enrollment-tucson-az-farm-fresh-to-you-tucson</t>
+  </si>
+  <si>
     <t>Systems and Data Integrity Specialist</t>
   </si>
   <si>
@@ -2092,6 +2470,15 @@
     <t>https://www.idealist.org/en/nonprofit-job/1178265cc3484f97896a29e7558858b5-teaching-fellowteacher-city-teaching-alliance-washington</t>
   </si>
   <si>
+    <t>USD 48000.00 - 55000.00/year</t>
+  </si>
+  <si>
+    <t>Environment, Transportation</t>
+  </si>
+  <si>
+    <t>https://www.idealist.org/en/nonprofit-job/7acb98b42a87452c83e7e09aad01b0eb-trail-and-watershed-outreach-coordinator-clean-air-council-philadelphia</t>
+  </si>
+  <si>
     <t>Vice President</t>
   </si>
   <si>
@@ -2099,6 +2486,18 @@
   </si>
   <si>
     <t>https://www.idealist.org/en/consultant-job/6cf6edb7238c403e9702c5f657686935-vice-president-617mediagroup-boston</t>
+  </si>
+  <si>
+    <t>Vice President, Human Resources</t>
+  </si>
+  <si>
+    <t>National Parks Conservation Association</t>
+  </si>
+  <si>
+    <t>USD 175000.00 - 190000.00/year</t>
+  </si>
+  <si>
+    <t>https://www.idealist.org/en/nonprofit-job/a866d6521398454499b67edb17ecd083-vice-president-human-resources-national-parks-conservation-association-washington</t>
   </si>
   <si>
     <t>Vice President, Programs</t>
@@ -3752,7 +4151,7 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <dimension ref="A1:H3"/>
+  <dimension ref="A1:H5"/>
   <sheetFormatPr defaultRowHeight="15" outlineLevelRow="0" outlineLevelCol="0" x14ac:dyDescent="55"/>
   <cols>
     <col min="1" max="1" width="48" customWidth="1"/>
@@ -3802,39 +4201,91 @@
         <v>262</v>
       </c>
       <c r="D2" t="s">
-        <v>30</v>
+        <v>263</v>
       </c>
       <c r="E2" t="s">
-        <v>263</v>
+        <v>264</v>
       </c>
       <c r="F2" t="s">
-        <v>264</v>
+        <v>265</v>
+      </c>
+      <c r="G2" t="s">
+        <v>266</v>
       </c>
       <c r="H2" s="2" t="s">
-        <v>265</v>
+        <v>267</v>
       </c>
     </row>
     <row r="3" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A3" t="s">
-        <v>266</v>
+        <v>268</v>
       </c>
       <c r="B3" t="s">
-        <v>267</v>
+        <v>269</v>
       </c>
       <c r="C3" t="s">
-        <v>268</v>
+        <v>270</v>
       </c>
       <c r="D3" t="s">
-        <v>269</v>
+        <v>30</v>
       </c>
       <c r="E3" t="s">
-        <v>270</v>
+        <v>271</v>
       </c>
       <c r="F3" t="s">
-        <v>271</v>
+        <v>265</v>
       </c>
       <c r="H3" s="2" t="s">
         <v>272</v>
+      </c>
+    </row>
+    <row r="4" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A4" t="s">
+        <v>273</v>
+      </c>
+      <c r="B4" t="s">
+        <v>274</v>
+      </c>
+      <c r="C4" t="s">
+        <v>275</v>
+      </c>
+      <c r="D4" t="s">
+        <v>263</v>
+      </c>
+      <c r="E4" t="s">
+        <v>276</v>
+      </c>
+      <c r="F4" t="s">
+        <v>277</v>
+      </c>
+      <c r="H4" s="2" t="s">
+        <v>278</v>
+      </c>
+    </row>
+    <row r="5" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A5" t="s">
+        <v>279</v>
+      </c>
+      <c r="B5" t="s">
+        <v>280</v>
+      </c>
+      <c r="C5" t="s">
+        <v>281</v>
+      </c>
+      <c r="D5" t="s">
+        <v>263</v>
+      </c>
+      <c r="E5" t="s">
+        <v>282</v>
+      </c>
+      <c r="F5" t="s">
+        <v>283</v>
+      </c>
+      <c r="G5" t="s">
+        <v>266</v>
+      </c>
+      <c r="H5" s="2" t="s">
+        <v>284</v>
       </c>
     </row>
   </sheetData>
@@ -3842,6 +4293,8 @@
   <hyperlinks>
     <hyperlink ref="H2" r:id="rId1"/>
     <hyperlink ref="H3" r:id="rId2"/>
+    <hyperlink ref="H4" r:id="rId3"/>
+    <hyperlink ref="H5" r:id="rId4"/>
   </hyperlinks>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup orientation="portrait" horizontalDpi="4294967295" verticalDpi="4294967295" scale="100" fitToWidth="1" fitToHeight="1"/>
@@ -3850,7 +4303,7 @@
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <dimension ref="A1:H91"/>
+  <dimension ref="A1:H120"/>
   <sheetFormatPr defaultRowHeight="15" outlineLevelRow="0" outlineLevelCol="0" x14ac:dyDescent="55"/>
   <cols>
     <col min="1" max="1" width="48" customWidth="1"/>
@@ -3891,2072 +4344,2745 @@
     </row>
     <row r="2" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A2" t="s">
-        <v>273</v>
+        <v>285</v>
       </c>
       <c r="B2" t="s">
-        <v>274</v>
+        <v>286</v>
       </c>
       <c r="C2" t="s">
-        <v>275</v>
+        <v>287</v>
       </c>
       <c r="D2" t="s">
-        <v>276</v>
+        <v>288</v>
       </c>
       <c r="E2" t="s">
-        <v>277</v>
+        <v>289</v>
       </c>
       <c r="F2" t="s">
-        <v>278</v>
+        <v>290</v>
       </c>
       <c r="H2" s="2" t="s">
-        <v>279</v>
+        <v>291</v>
       </c>
     </row>
     <row r="3" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A3" t="s">
-        <v>280</v>
+        <v>292</v>
       </c>
       <c r="B3" t="s">
-        <v>281</v>
+        <v>293</v>
       </c>
       <c r="C3" t="s">
-        <v>282</v>
+        <v>294</v>
       </c>
       <c r="D3" t="s">
-        <v>276</v>
+        <v>288</v>
       </c>
       <c r="E3" t="s">
-        <v>283</v>
+        <v>295</v>
       </c>
       <c r="F3" t="s">
-        <v>284</v>
+        <v>296</v>
       </c>
       <c r="H3" s="2" t="s">
-        <v>285</v>
+        <v>297</v>
       </c>
     </row>
     <row r="4" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A4" t="s">
-        <v>286</v>
+        <v>298</v>
       </c>
       <c r="B4" t="s">
-        <v>287</v>
+        <v>299</v>
       </c>
       <c r="C4" t="s">
-        <v>288</v>
+        <v>262</v>
       </c>
       <c r="D4" t="s">
-        <v>276</v>
+        <v>288</v>
       </c>
       <c r="E4" t="s">
-        <v>289</v>
+        <v>300</v>
       </c>
       <c r="F4" t="s">
-        <v>290</v>
+        <v>301</v>
       </c>
       <c r="H4" s="2" t="s">
-        <v>291</v>
+        <v>302</v>
       </c>
     </row>
     <row r="5" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A5" t="s">
-        <v>292</v>
+        <v>303</v>
       </c>
       <c r="B5" t="s">
-        <v>293</v>
+        <v>304</v>
       </c>
       <c r="C5" t="s">
-        <v>237</v>
+        <v>305</v>
       </c>
       <c r="D5" t="s">
-        <v>276</v>
+        <v>288</v>
       </c>
       <c r="E5" t="s">
-        <v>294</v>
+        <v>306</v>
       </c>
       <c r="F5" t="s">
-        <v>295</v>
+        <v>307</v>
       </c>
       <c r="H5" s="2" t="s">
-        <v>296</v>
+        <v>308</v>
       </c>
     </row>
     <row r="6" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A6" t="s">
-        <v>297</v>
+        <v>309</v>
       </c>
       <c r="B6" t="s">
-        <v>298</v>
+        <v>310</v>
       </c>
       <c r="C6" t="s">
-        <v>282</v>
+        <v>237</v>
       </c>
       <c r="D6" t="s">
-        <v>276</v>
+        <v>288</v>
       </c>
       <c r="E6" t="s">
-        <v>299</v>
+        <v>311</v>
       </c>
       <c r="F6" t="s">
-        <v>300</v>
+        <v>312</v>
       </c>
       <c r="H6" s="2" t="s">
-        <v>301</v>
+        <v>313</v>
       </c>
     </row>
     <row r="7" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A7" t="s">
-        <v>302</v>
+        <v>314</v>
       </c>
       <c r="B7" t="s">
-        <v>303</v>
+        <v>315</v>
       </c>
       <c r="C7" t="s">
-        <v>304</v>
+        <v>262</v>
       </c>
       <c r="D7" t="s">
-        <v>276</v>
+        <v>288</v>
       </c>
       <c r="E7" t="s">
-        <v>305</v>
+        <v>316</v>
       </c>
       <c r="F7" t="s">
-        <v>306</v>
+        <v>317</v>
       </c>
       <c r="H7" s="2" t="s">
-        <v>307</v>
+        <v>318</v>
       </c>
     </row>
     <row r="8" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A8" t="s">
-        <v>308</v>
+        <v>319</v>
       </c>
       <c r="B8" t="s">
-        <v>309</v>
+        <v>320</v>
       </c>
       <c r="C8" t="s">
-        <v>310</v>
+        <v>321</v>
       </c>
       <c r="D8" t="s">
-        <v>276</v>
+        <v>288</v>
       </c>
       <c r="E8" t="s">
-        <v>311</v>
+        <v>322</v>
       </c>
       <c r="F8" t="s">
-        <v>312</v>
+        <v>323</v>
       </c>
       <c r="H8" s="2" t="s">
-        <v>313</v>
+        <v>324</v>
       </c>
     </row>
     <row r="9" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A9" t="s">
-        <v>314</v>
+        <v>325</v>
       </c>
       <c r="B9" t="s">
-        <v>315</v>
+        <v>326</v>
       </c>
       <c r="C9" t="s">
-        <v>310</v>
+        <v>327</v>
       </c>
       <c r="D9" t="s">
-        <v>276</v>
+        <v>288</v>
       </c>
       <c r="E9" t="s">
-        <v>316</v>
+        <v>328</v>
       </c>
       <c r="F9" t="s">
-        <v>317</v>
+        <v>329</v>
       </c>
       <c r="H9" s="2" t="s">
-        <v>318</v>
+        <v>330</v>
       </c>
     </row>
     <row r="10" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A10" t="s">
-        <v>319</v>
+        <v>331</v>
       </c>
       <c r="B10" t="s">
-        <v>320</v>
+        <v>332</v>
       </c>
       <c r="C10" t="s">
-        <v>321</v>
+        <v>327</v>
       </c>
       <c r="D10" t="s">
-        <v>276</v>
+        <v>288</v>
       </c>
       <c r="E10" t="s">
-        <v>270</v>
+        <v>333</v>
       </c>
       <c r="F10" t="s">
-        <v>322</v>
+        <v>334</v>
       </c>
       <c r="H10" s="2" t="s">
-        <v>323</v>
+        <v>335</v>
       </c>
     </row>
     <row r="11" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A11" t="s">
-        <v>324</v>
+        <v>336</v>
       </c>
       <c r="B11" t="s">
-        <v>325</v>
+        <v>337</v>
       </c>
       <c r="C11" t="s">
-        <v>326</v>
+        <v>338</v>
       </c>
       <c r="D11" t="s">
+        <v>288</v>
+      </c>
+      <c r="E11" t="s">
         <v>276</v>
       </c>
-      <c r="E11" t="s">
-        <v>327</v>
-      </c>
       <c r="F11" t="s">
-        <v>328</v>
+        <v>339</v>
       </c>
       <c r="H11" s="2" t="s">
-        <v>329</v>
+        <v>340</v>
       </c>
     </row>
     <row r="12" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A12" t="s">
-        <v>330</v>
+        <v>341</v>
       </c>
       <c r="B12" t="s">
-        <v>331</v>
+        <v>342</v>
       </c>
       <c r="C12" t="s">
-        <v>332</v>
+        <v>343</v>
       </c>
       <c r="D12" t="s">
-        <v>276</v>
+        <v>288</v>
       </c>
       <c r="E12" t="s">
-        <v>333</v>
+        <v>344</v>
       </c>
       <c r="F12" t="s">
-        <v>270</v>
+        <v>345</v>
       </c>
       <c r="H12" s="2" t="s">
-        <v>334</v>
+        <v>346</v>
       </c>
     </row>
     <row r="13" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A13" t="s">
-        <v>335</v>
+        <v>347</v>
       </c>
       <c r="B13" t="s">
-        <v>336</v>
+        <v>348</v>
       </c>
       <c r="C13" t="s">
-        <v>282</v>
+        <v>349</v>
       </c>
       <c r="D13" t="s">
+        <v>350</v>
+      </c>
+      <c r="E13" t="s">
         <v>276</v>
       </c>
-      <c r="E13" t="s">
-        <v>337</v>
-      </c>
       <c r="F13" t="s">
-        <v>338</v>
+        <v>351</v>
       </c>
       <c r="H13" s="2" t="s">
-        <v>339</v>
+        <v>352</v>
       </c>
     </row>
     <row r="14" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A14" t="s">
-        <v>340</v>
+        <v>353</v>
       </c>
       <c r="B14" t="s">
-        <v>341</v>
+        <v>354</v>
       </c>
       <c r="C14" t="s">
-        <v>342</v>
+        <v>355</v>
       </c>
       <c r="D14" t="s">
+        <v>288</v>
+      </c>
+      <c r="E14" t="s">
+        <v>356</v>
+      </c>
+      <c r="F14" t="s">
         <v>276</v>
       </c>
-      <c r="E14" t="s">
-        <v>343</v>
-      </c>
-      <c r="F14" t="s">
-        <v>270</v>
-      </c>
       <c r="H14" s="2" t="s">
-        <v>344</v>
+        <v>357</v>
       </c>
     </row>
     <row r="15" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A15" t="s">
-        <v>345</v>
+        <v>358</v>
       </c>
       <c r="B15" t="s">
-        <v>346</v>
+        <v>359</v>
       </c>
       <c r="C15" t="s">
-        <v>304</v>
+        <v>360</v>
       </c>
       <c r="D15" t="s">
+        <v>288</v>
+      </c>
+      <c r="E15" t="s">
         <v>276</v>
       </c>
-      <c r="E15" t="s">
-        <v>347</v>
-      </c>
       <c r="F15" t="s">
-        <v>348</v>
+        <v>276</v>
       </c>
       <c r="H15" s="2" t="s">
-        <v>349</v>
+        <v>361</v>
       </c>
     </row>
     <row r="16" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A16" t="s">
-        <v>350</v>
+        <v>362</v>
       </c>
       <c r="B16" t="s">
-        <v>351</v>
+        <v>363</v>
       </c>
       <c r="C16" t="s">
-        <v>352</v>
+        <v>262</v>
       </c>
       <c r="D16" t="s">
-        <v>276</v>
+        <v>288</v>
       </c>
       <c r="E16" t="s">
-        <v>353</v>
+        <v>364</v>
       </c>
       <c r="F16" t="s">
-        <v>354</v>
+        <v>365</v>
       </c>
       <c r="H16" s="2" t="s">
-        <v>355</v>
+        <v>366</v>
       </c>
     </row>
     <row r="17" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A17" t="s">
-        <v>356</v>
+        <v>367</v>
       </c>
       <c r="B17" t="s">
-        <v>357</v>
+        <v>368</v>
       </c>
       <c r="C17" t="s">
-        <v>332</v>
+        <v>369</v>
       </c>
       <c r="D17" t="s">
+        <v>288</v>
+      </c>
+      <c r="E17" t="s">
+        <v>370</v>
+      </c>
+      <c r="F17" t="s">
         <v>276</v>
       </c>
-      <c r="E17" t="s">
-        <v>358</v>
-      </c>
-      <c r="F17" t="s">
-        <v>359</v>
-      </c>
       <c r="H17" s="2" t="s">
-        <v>360</v>
+        <v>371</v>
       </c>
     </row>
     <row r="18" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A18" t="s">
-        <v>361</v>
+        <v>372</v>
       </c>
       <c r="B18" t="s">
-        <v>362</v>
+        <v>373</v>
       </c>
       <c r="C18" t="s">
-        <v>363</v>
+        <v>321</v>
       </c>
       <c r="D18" t="s">
-        <v>276</v>
+        <v>288</v>
       </c>
       <c r="E18" t="s">
-        <v>364</v>
+        <v>374</v>
       </c>
       <c r="F18" t="s">
-        <v>365</v>
+        <v>375</v>
       </c>
       <c r="H18" s="2" t="s">
-        <v>366</v>
+        <v>376</v>
       </c>
     </row>
     <row r="19" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A19" t="s">
-        <v>367</v>
+        <v>377</v>
       </c>
       <c r="B19" t="s">
-        <v>368</v>
+        <v>378</v>
       </c>
       <c r="C19" t="s">
-        <v>310</v>
+        <v>379</v>
       </c>
       <c r="D19" t="s">
-        <v>369</v>
+        <v>288</v>
       </c>
       <c r="E19" t="s">
-        <v>270</v>
+        <v>380</v>
       </c>
       <c r="F19" t="s">
-        <v>370</v>
+        <v>381</v>
       </c>
       <c r="H19" s="2" t="s">
-        <v>371</v>
+        <v>382</v>
       </c>
     </row>
     <row r="20" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A20" t="s">
-        <v>372</v>
+        <v>383</v>
       </c>
       <c r="B20" t="s">
-        <v>373</v>
+        <v>384</v>
       </c>
       <c r="C20" t="s">
-        <v>374</v>
+        <v>355</v>
       </c>
       <c r="D20" t="s">
-        <v>276</v>
+        <v>288</v>
       </c>
       <c r="E20" t="s">
-        <v>289</v>
+        <v>385</v>
       </c>
       <c r="F20" t="s">
-        <v>375</v>
+        <v>386</v>
       </c>
       <c r="H20" s="2" t="s">
-        <v>376</v>
+        <v>387</v>
       </c>
     </row>
     <row r="21" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A21" t="s">
-        <v>377</v>
+        <v>388</v>
       </c>
       <c r="B21" t="s">
-        <v>378</v>
+        <v>293</v>
       </c>
       <c r="C21" t="s">
-        <v>379</v>
+        <v>262</v>
       </c>
       <c r="D21" t="s">
-        <v>276</v>
+        <v>389</v>
       </c>
       <c r="E21" t="s">
-        <v>380</v>
+        <v>390</v>
       </c>
       <c r="F21" t="s">
-        <v>381</v>
+        <v>296</v>
       </c>
       <c r="H21" s="2" t="s">
-        <v>382</v>
+        <v>391</v>
       </c>
     </row>
     <row r="22" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A22" t="s">
-        <v>383</v>
+        <v>392</v>
       </c>
       <c r="B22" t="s">
-        <v>384</v>
+        <v>393</v>
       </c>
       <c r="C22" t="s">
-        <v>304</v>
+        <v>394</v>
       </c>
       <c r="D22" t="s">
-        <v>276</v>
+        <v>288</v>
       </c>
       <c r="E22" t="s">
-        <v>385</v>
+        <v>295</v>
       </c>
       <c r="F22" t="s">
-        <v>270</v>
+        <v>395</v>
       </c>
       <c r="H22" s="2" t="s">
-        <v>386</v>
+        <v>396</v>
       </c>
     </row>
     <row r="23" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A23" t="s">
-        <v>387</v>
+        <v>397</v>
       </c>
       <c r="B23" t="s">
-        <v>388</v>
+        <v>398</v>
       </c>
       <c r="C23" t="s">
-        <v>282</v>
+        <v>327</v>
       </c>
       <c r="D23" t="s">
-        <v>389</v>
+        <v>350</v>
       </c>
       <c r="E23" t="s">
-        <v>390</v>
+        <v>276</v>
       </c>
       <c r="F23" t="s">
-        <v>391</v>
+        <v>399</v>
       </c>
       <c r="H23" s="2" t="s">
-        <v>392</v>
+        <v>400</v>
       </c>
     </row>
     <row r="24" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A24" t="s">
-        <v>393</v>
+        <v>401</v>
       </c>
       <c r="B24" t="s">
-        <v>394</v>
+        <v>402</v>
       </c>
       <c r="C24" t="s">
-        <v>395</v>
+        <v>403</v>
       </c>
       <c r="D24" t="s">
-        <v>276</v>
+        <v>288</v>
       </c>
       <c r="E24" t="s">
-        <v>396</v>
+        <v>404</v>
       </c>
       <c r="F24" t="s">
-        <v>397</v>
+        <v>405</v>
       </c>
       <c r="H24" s="2" t="s">
-        <v>398</v>
+        <v>406</v>
       </c>
     </row>
     <row r="25" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A25" t="s">
-        <v>399</v>
+        <v>407</v>
       </c>
       <c r="B25" t="s">
-        <v>400</v>
+        <v>408</v>
       </c>
       <c r="C25" t="s">
-        <v>401</v>
+        <v>262</v>
       </c>
       <c r="D25" t="s">
-        <v>276</v>
+        <v>288</v>
       </c>
       <c r="E25" t="s">
-        <v>402</v>
+        <v>409</v>
       </c>
       <c r="F25" t="s">
-        <v>290</v>
+        <v>410</v>
       </c>
       <c r="H25" s="2" t="s">
-        <v>403</v>
+        <v>411</v>
       </c>
     </row>
     <row r="26" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A26" t="s">
-        <v>404</v>
+        <v>412</v>
       </c>
       <c r="B26" t="s">
-        <v>405</v>
+        <v>413</v>
       </c>
       <c r="C26" t="s">
-        <v>304</v>
+        <v>414</v>
       </c>
       <c r="D26" t="s">
-        <v>276</v>
+        <v>288</v>
       </c>
       <c r="E26" t="s">
-        <v>406</v>
+        <v>306</v>
       </c>
       <c r="F26" t="s">
-        <v>407</v>
+        <v>415</v>
       </c>
       <c r="H26" s="2" t="s">
-        <v>408</v>
+        <v>416</v>
       </c>
     </row>
     <row r="27" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A27" t="s">
-        <v>404</v>
+        <v>417</v>
       </c>
       <c r="B27" t="s">
-        <v>409</v>
+        <v>418</v>
       </c>
       <c r="C27" t="s">
-        <v>410</v>
+        <v>419</v>
       </c>
       <c r="D27" t="s">
-        <v>276</v>
+        <v>288</v>
       </c>
       <c r="E27" t="s">
-        <v>411</v>
+        <v>420</v>
       </c>
       <c r="F27" t="s">
-        <v>412</v>
+        <v>421</v>
       </c>
       <c r="H27" s="2" t="s">
-        <v>413</v>
+        <v>422</v>
       </c>
     </row>
     <row r="28" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A28" t="s">
-        <v>404</v>
+        <v>423</v>
       </c>
       <c r="B28" t="s">
-        <v>414</v>
+        <v>424</v>
       </c>
       <c r="C28" t="s">
-        <v>342</v>
+        <v>321</v>
       </c>
       <c r="D28" t="s">
-        <v>276</v>
+        <v>288</v>
       </c>
       <c r="E28" t="s">
-        <v>415</v>
+        <v>425</v>
       </c>
       <c r="F28" t="s">
-        <v>270</v>
+        <v>351</v>
       </c>
       <c r="H28" s="2" t="s">
-        <v>416</v>
+        <v>426</v>
       </c>
     </row>
     <row r="29" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A29" t="s">
-        <v>417</v>
+        <v>427</v>
       </c>
       <c r="B29" t="s">
-        <v>418</v>
+        <v>428</v>
       </c>
       <c r="C29" t="s">
-        <v>419</v>
+        <v>321</v>
       </c>
       <c r="D29" t="s">
+        <v>288</v>
+      </c>
+      <c r="E29" t="s">
+        <v>429</v>
+      </c>
+      <c r="F29" t="s">
         <v>276</v>
       </c>
-      <c r="E29" t="s">
-        <v>420</v>
-      </c>
-      <c r="F29" t="s">
-        <v>421</v>
-      </c>
       <c r="H29" s="2" t="s">
-        <v>422</v>
+        <v>430</v>
       </c>
     </row>
     <row r="30" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A30" t="s">
-        <v>423</v>
+        <v>431</v>
       </c>
       <c r="B30" t="s">
-        <v>424</v>
+        <v>432</v>
       </c>
       <c r="C30" t="s">
-        <v>342</v>
+        <v>321</v>
       </c>
       <c r="D30" t="s">
+        <v>288</v>
+      </c>
+      <c r="E30" t="s">
+        <v>433</v>
+      </c>
+      <c r="F30" t="s">
         <v>276</v>
       </c>
-      <c r="E30" t="s">
-        <v>425</v>
-      </c>
-      <c r="F30" t="s">
-        <v>426</v>
-      </c>
       <c r="H30" s="2" t="s">
-        <v>427</v>
+        <v>434</v>
       </c>
     </row>
     <row r="31" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A31" t="s">
-        <v>428</v>
+        <v>435</v>
       </c>
       <c r="B31" t="s">
-        <v>429</v>
+        <v>436</v>
       </c>
       <c r="C31" t="s">
-        <v>430</v>
+        <v>262</v>
       </c>
       <c r="D31" t="s">
-        <v>276</v>
+        <v>389</v>
       </c>
       <c r="E31" t="s">
-        <v>431</v>
+        <v>437</v>
       </c>
       <c r="F31" t="s">
-        <v>432</v>
+        <v>438</v>
       </c>
       <c r="H31" s="2" t="s">
-        <v>433</v>
+        <v>439</v>
       </c>
     </row>
     <row r="32" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A32" t="s">
-        <v>434</v>
+        <v>440</v>
       </c>
       <c r="B32" t="s">
-        <v>435</v>
+        <v>441</v>
       </c>
       <c r="C32" t="s">
-        <v>282</v>
+        <v>442</v>
       </c>
       <c r="D32" t="s">
-        <v>276</v>
+        <v>288</v>
       </c>
       <c r="E32" t="s">
-        <v>436</v>
+        <v>443</v>
       </c>
       <c r="F32" t="s">
-        <v>437</v>
+        <v>444</v>
       </c>
       <c r="H32" s="2" t="s">
-        <v>438</v>
+        <v>445</v>
       </c>
     </row>
     <row r="33" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A33" t="s">
-        <v>439</v>
+        <v>446</v>
       </c>
       <c r="B33" t="s">
-        <v>429</v>
+        <v>447</v>
       </c>
       <c r="C33" t="s">
-        <v>430</v>
+        <v>448</v>
       </c>
       <c r="D33" t="s">
-        <v>276</v>
+        <v>288</v>
       </c>
       <c r="E33" t="s">
-        <v>270</v>
+        <v>449</v>
       </c>
       <c r="F33" t="s">
-        <v>440</v>
+        <v>307</v>
       </c>
       <c r="H33" s="2" t="s">
-        <v>441</v>
+        <v>450</v>
       </c>
     </row>
     <row r="34" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A34" t="s">
-        <v>442</v>
+        <v>451</v>
       </c>
       <c r="B34" t="s">
-        <v>443</v>
+        <v>452</v>
       </c>
       <c r="C34" t="s">
-        <v>64</v>
+        <v>321</v>
       </c>
       <c r="D34" t="s">
-        <v>444</v>
+        <v>288</v>
       </c>
       <c r="E34" t="s">
-        <v>445</v>
+        <v>453</v>
       </c>
       <c r="F34" t="s">
-        <v>446</v>
+        <v>454</v>
       </c>
       <c r="H34" s="2" t="s">
-        <v>447</v>
+        <v>455</v>
       </c>
     </row>
     <row r="35" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A35" t="s">
-        <v>448</v>
+        <v>451</v>
       </c>
       <c r="B35" t="s">
-        <v>449</v>
+        <v>456</v>
       </c>
       <c r="C35" t="s">
-        <v>450</v>
+        <v>457</v>
       </c>
       <c r="D35" t="s">
-        <v>276</v>
+        <v>288</v>
       </c>
       <c r="E35" t="s">
-        <v>451</v>
+        <v>458</v>
       </c>
       <c r="F35" t="s">
-        <v>452</v>
+        <v>459</v>
       </c>
       <c r="H35" s="2" t="s">
-        <v>453</v>
+        <v>460</v>
       </c>
     </row>
     <row r="36" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A36" t="s">
-        <v>448</v>
+        <v>451</v>
       </c>
       <c r="B36" t="s">
-        <v>454</v>
+        <v>461</v>
       </c>
       <c r="C36" t="s">
-        <v>363</v>
+        <v>369</v>
       </c>
       <c r="D36" t="s">
+        <v>288</v>
+      </c>
+      <c r="E36" t="s">
+        <v>462</v>
+      </c>
+      <c r="F36" t="s">
         <v>276</v>
       </c>
-      <c r="E36" t="s">
-        <v>455</v>
-      </c>
-      <c r="F36" t="s">
-        <v>456</v>
-      </c>
       <c r="H36" s="2" t="s">
-        <v>457</v>
+        <v>463</v>
       </c>
     </row>
     <row r="37" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A37" t="s">
-        <v>448</v>
+        <v>464</v>
       </c>
       <c r="B37" t="s">
-        <v>458</v>
+        <v>465</v>
       </c>
       <c r="C37" t="s">
-        <v>459</v>
+        <v>466</v>
       </c>
       <c r="D37" t="s">
-        <v>276</v>
+        <v>288</v>
       </c>
       <c r="E37" t="s">
-        <v>460</v>
+        <v>467</v>
       </c>
       <c r="F37" t="s">
-        <v>270</v>
+        <v>468</v>
       </c>
       <c r="H37" s="2" t="s">
-        <v>461</v>
+        <v>469</v>
       </c>
     </row>
     <row r="38" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A38" t="s">
-        <v>462</v>
+        <v>470</v>
       </c>
       <c r="B38" t="s">
-        <v>463</v>
+        <v>465</v>
       </c>
       <c r="C38" t="s">
-        <v>282</v>
+        <v>466</v>
       </c>
       <c r="D38" t="s">
-        <v>276</v>
+        <v>288</v>
       </c>
       <c r="E38" t="s">
-        <v>464</v>
+        <v>471</v>
       </c>
       <c r="F38" t="s">
-        <v>465</v>
+        <v>468</v>
       </c>
       <c r="H38" s="2" t="s">
-        <v>466</v>
+        <v>472</v>
       </c>
     </row>
     <row r="39" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A39" t="s">
-        <v>467</v>
+        <v>473</v>
       </c>
       <c r="B39" t="s">
-        <v>468</v>
+        <v>474</v>
       </c>
       <c r="C39" t="s">
-        <v>379</v>
+        <v>475</v>
       </c>
       <c r="D39" t="s">
-        <v>276</v>
+        <v>288</v>
       </c>
       <c r="E39" t="s">
-        <v>469</v>
+        <v>425</v>
       </c>
       <c r="F39" t="s">
-        <v>470</v>
+        <v>476</v>
       </c>
       <c r="H39" s="2" t="s">
-        <v>471</v>
+        <v>477</v>
       </c>
     </row>
     <row r="40" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A40" t="s">
-        <v>472</v>
+        <v>478</v>
       </c>
       <c r="B40" t="s">
-        <v>473</v>
+        <v>479</v>
       </c>
       <c r="C40" t="s">
-        <v>474</v>
+        <v>480</v>
       </c>
       <c r="D40" t="s">
-        <v>369</v>
+        <v>288</v>
       </c>
       <c r="E40" t="s">
-        <v>270</v>
+        <v>481</v>
       </c>
       <c r="F40" t="s">
-        <v>475</v>
+        <v>482</v>
       </c>
       <c r="H40" s="2" t="s">
-        <v>476</v>
+        <v>483</v>
       </c>
     </row>
     <row r="41" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A41" t="s">
-        <v>477</v>
+        <v>484</v>
       </c>
       <c r="B41" t="s">
-        <v>478</v>
+        <v>485</v>
       </c>
       <c r="C41" t="s">
-        <v>401</v>
+        <v>369</v>
       </c>
       <c r="D41" t="s">
-        <v>276</v>
+        <v>288</v>
       </c>
       <c r="E41" t="s">
-        <v>479</v>
+        <v>486</v>
       </c>
       <c r="F41" t="s">
-        <v>480</v>
+        <v>487</v>
       </c>
       <c r="H41" s="2" t="s">
-        <v>481</v>
+        <v>488</v>
       </c>
     </row>
     <row r="42" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A42" t="s">
-        <v>482</v>
+        <v>489</v>
       </c>
       <c r="B42" t="s">
-        <v>325</v>
+        <v>490</v>
       </c>
       <c r="C42" t="s">
-        <v>326</v>
+        <v>491</v>
       </c>
       <c r="D42" t="s">
-        <v>276</v>
+        <v>288</v>
       </c>
       <c r="E42" t="s">
-        <v>483</v>
+        <v>492</v>
       </c>
       <c r="F42" t="s">
-        <v>328</v>
+        <v>493</v>
       </c>
       <c r="H42" s="2" t="s">
-        <v>484</v>
+        <v>494</v>
       </c>
     </row>
     <row r="43" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A43" t="s">
-        <v>485</v>
+        <v>495</v>
       </c>
       <c r="B43" t="s">
-        <v>486</v>
+        <v>496</v>
       </c>
       <c r="C43" t="s">
-        <v>487</v>
+        <v>262</v>
       </c>
       <c r="D43" t="s">
-        <v>276</v>
+        <v>288</v>
       </c>
       <c r="E43" t="s">
-        <v>488</v>
+        <v>497</v>
       </c>
       <c r="F43" t="s">
-        <v>489</v>
+        <v>498</v>
       </c>
       <c r="H43" s="2" t="s">
-        <v>490</v>
+        <v>499</v>
       </c>
     </row>
     <row r="44" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A44" t="s">
-        <v>491</v>
+        <v>500</v>
       </c>
       <c r="B44" t="s">
-        <v>492</v>
+        <v>501</v>
       </c>
       <c r="C44" t="s">
-        <v>304</v>
+        <v>262</v>
       </c>
       <c r="D44" t="s">
-        <v>276</v>
+        <v>288</v>
       </c>
       <c r="E44" t="s">
-        <v>493</v>
+        <v>502</v>
       </c>
       <c r="F44" t="s">
-        <v>494</v>
+        <v>503</v>
       </c>
       <c r="H44" s="2" t="s">
-        <v>495</v>
+        <v>504</v>
       </c>
     </row>
     <row r="45" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A45" t="s">
-        <v>496</v>
+        <v>505</v>
       </c>
       <c r="B45" t="s">
-        <v>497</v>
+        <v>490</v>
       </c>
       <c r="C45" t="s">
-        <v>379</v>
+        <v>491</v>
       </c>
       <c r="D45" t="s">
-        <v>498</v>
+        <v>288</v>
       </c>
       <c r="E45" t="s">
-        <v>499</v>
+        <v>276</v>
       </c>
       <c r="F45" t="s">
-        <v>270</v>
+        <v>506</v>
       </c>
       <c r="H45" s="2" t="s">
-        <v>500</v>
+        <v>507</v>
       </c>
     </row>
     <row r="46" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A46" t="s">
-        <v>501</v>
+        <v>508</v>
       </c>
       <c r="B46" t="s">
-        <v>303</v>
+        <v>509</v>
       </c>
       <c r="C46" t="s">
-        <v>304</v>
+        <v>64</v>
       </c>
       <c r="D46" t="s">
-        <v>276</v>
+        <v>510</v>
       </c>
       <c r="E46" t="s">
-        <v>502</v>
+        <v>511</v>
       </c>
       <c r="F46" t="s">
-        <v>503</v>
+        <v>512</v>
       </c>
       <c r="H46" s="2" t="s">
-        <v>504</v>
+        <v>513</v>
       </c>
     </row>
     <row r="47" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A47" t="s">
-        <v>505</v>
+        <v>260</v>
       </c>
       <c r="B47" t="s">
-        <v>506</v>
+        <v>261</v>
       </c>
       <c r="C47" t="s">
-        <v>282</v>
+        <v>262</v>
       </c>
       <c r="D47" t="s">
-        <v>276</v>
+        <v>288</v>
       </c>
       <c r="E47" t="s">
-        <v>507</v>
+        <v>514</v>
       </c>
       <c r="F47" t="s">
-        <v>508</v>
+        <v>515</v>
+      </c>
+      <c r="G47" t="s">
+        <v>516</v>
       </c>
       <c r="H47" s="2" t="s">
-        <v>509</v>
+        <v>517</v>
       </c>
     </row>
     <row r="48" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A48" t="s">
-        <v>510</v>
+        <v>518</v>
       </c>
       <c r="B48" t="s">
-        <v>511</v>
+        <v>519</v>
       </c>
       <c r="C48" t="s">
-        <v>342</v>
+        <v>520</v>
       </c>
       <c r="D48" t="s">
-        <v>444</v>
+        <v>350</v>
       </c>
       <c r="E48" t="s">
-        <v>512</v>
+        <v>521</v>
       </c>
       <c r="F48" t="s">
-        <v>513</v>
+        <v>522</v>
       </c>
       <c r="H48" s="2" t="s">
-        <v>514</v>
+        <v>523</v>
       </c>
     </row>
     <row r="49" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A49" t="s">
-        <v>515</v>
+        <v>524</v>
       </c>
       <c r="B49" t="s">
-        <v>516</v>
+        <v>525</v>
       </c>
       <c r="C49" t="s">
-        <v>517</v>
+        <v>526</v>
       </c>
       <c r="D49" t="s">
-        <v>276</v>
+        <v>288</v>
       </c>
       <c r="E49" t="s">
-        <v>299</v>
+        <v>527</v>
       </c>
       <c r="F49" t="s">
-        <v>518</v>
+        <v>528</v>
       </c>
       <c r="H49" s="2" t="s">
-        <v>519</v>
+        <v>529</v>
       </c>
     </row>
     <row r="50" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A50" t="s">
-        <v>520</v>
+        <v>524</v>
       </c>
       <c r="B50" t="s">
-        <v>521</v>
+        <v>530</v>
       </c>
       <c r="C50" t="s">
-        <v>282</v>
+        <v>394</v>
       </c>
       <c r="D50" t="s">
-        <v>276</v>
+        <v>288</v>
       </c>
       <c r="E50" t="s">
-        <v>522</v>
+        <v>531</v>
       </c>
       <c r="F50" t="s">
-        <v>523</v>
+        <v>532</v>
       </c>
       <c r="H50" s="2" t="s">
-        <v>524</v>
+        <v>533</v>
       </c>
     </row>
     <row r="51" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A51" t="s">
-        <v>525</v>
+        <v>524</v>
       </c>
       <c r="B51" t="s">
-        <v>429</v>
+        <v>534</v>
       </c>
       <c r="C51" t="s">
-        <v>430</v>
+        <v>535</v>
       </c>
       <c r="D51" t="s">
+        <v>288</v>
+      </c>
+      <c r="E51" t="s">
+        <v>536</v>
+      </c>
+      <c r="F51" t="s">
         <v>276</v>
       </c>
-      <c r="E51" t="s">
-        <v>526</v>
-      </c>
-      <c r="F51" t="s">
-        <v>440</v>
-      </c>
       <c r="H51" s="2" t="s">
-        <v>527</v>
+        <v>537</v>
       </c>
     </row>
     <row r="52" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A52" t="s">
-        <v>528</v>
+        <v>538</v>
       </c>
       <c r="B52" t="s">
-        <v>529</v>
+        <v>539</v>
       </c>
       <c r="C52" t="s">
-        <v>530</v>
+        <v>262</v>
       </c>
       <c r="D52" t="s">
-        <v>276</v>
+        <v>288</v>
       </c>
       <c r="E52" t="s">
-        <v>531</v>
+        <v>540</v>
       </c>
       <c r="F52" t="s">
-        <v>532</v>
+        <v>541</v>
       </c>
       <c r="H52" s="2" t="s">
-        <v>533</v>
+        <v>542</v>
       </c>
     </row>
     <row r="53" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A53" t="s">
-        <v>534</v>
+        <v>543</v>
       </c>
       <c r="B53" t="s">
-        <v>303</v>
+        <v>544</v>
       </c>
       <c r="C53" t="s">
-        <v>304</v>
+        <v>419</v>
       </c>
       <c r="D53" t="s">
-        <v>276</v>
+        <v>288</v>
       </c>
       <c r="E53" t="s">
-        <v>535</v>
+        <v>545</v>
       </c>
       <c r="F53" t="s">
-        <v>306</v>
+        <v>515</v>
       </c>
       <c r="H53" s="2" t="s">
-        <v>536</v>
+        <v>546</v>
       </c>
     </row>
     <row r="54" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A54" t="s">
-        <v>537</v>
+        <v>547</v>
       </c>
       <c r="B54" t="s">
-        <v>538</v>
+        <v>548</v>
       </c>
       <c r="C54" t="s">
-        <v>310</v>
+        <v>549</v>
       </c>
       <c r="D54" t="s">
+        <v>350</v>
+      </c>
+      <c r="E54" t="s">
         <v>276</v>
       </c>
-      <c r="E54" t="s">
-        <v>396</v>
-      </c>
       <c r="F54" t="s">
-        <v>539</v>
+        <v>550</v>
       </c>
       <c r="H54" s="2" t="s">
-        <v>540</v>
+        <v>551</v>
       </c>
     </row>
     <row r="55" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A55" t="s">
-        <v>541</v>
+        <v>552</v>
       </c>
       <c r="B55" t="s">
-        <v>542</v>
+        <v>553</v>
       </c>
       <c r="C55" t="s">
-        <v>304</v>
+        <v>448</v>
       </c>
       <c r="D55" t="s">
-        <v>276</v>
+        <v>288</v>
       </c>
       <c r="E55" t="s">
-        <v>543</v>
+        <v>554</v>
       </c>
       <c r="F55" t="s">
-        <v>270</v>
+        <v>555</v>
       </c>
       <c r="H55" s="2" t="s">
-        <v>544</v>
+        <v>556</v>
       </c>
     </row>
     <row r="56" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A56" t="s">
-        <v>545</v>
+        <v>557</v>
       </c>
       <c r="B56" t="s">
-        <v>429</v>
+        <v>342</v>
       </c>
       <c r="C56" t="s">
-        <v>430</v>
+        <v>343</v>
       </c>
       <c r="D56" t="s">
-        <v>276</v>
+        <v>288</v>
       </c>
       <c r="E56" t="s">
-        <v>546</v>
+        <v>558</v>
       </c>
       <c r="F56" t="s">
-        <v>440</v>
+        <v>345</v>
       </c>
       <c r="H56" s="2" t="s">
-        <v>547</v>
+        <v>559</v>
       </c>
     </row>
     <row r="57" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A57" t="s">
-        <v>548</v>
+        <v>560</v>
       </c>
       <c r="B57" t="s">
-        <v>429</v>
+        <v>561</v>
       </c>
       <c r="C57" t="s">
-        <v>430</v>
+        <v>562</v>
       </c>
       <c r="D57" t="s">
-        <v>276</v>
+        <v>288</v>
       </c>
       <c r="E57" t="s">
-        <v>549</v>
+        <v>563</v>
       </c>
       <c r="F57" t="s">
-        <v>440</v>
+        <v>564</v>
       </c>
       <c r="H57" s="2" t="s">
-        <v>550</v>
+        <v>565</v>
       </c>
     </row>
     <row r="58" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A58" t="s">
-        <v>551</v>
+        <v>566</v>
       </c>
       <c r="B58" t="s">
-        <v>552</v>
+        <v>567</v>
       </c>
       <c r="C58" t="s">
-        <v>553</v>
+        <v>321</v>
       </c>
       <c r="D58" t="s">
-        <v>276</v>
+        <v>288</v>
       </c>
       <c r="E58" t="s">
-        <v>554</v>
+        <v>568</v>
       </c>
       <c r="F58" t="s">
-        <v>270</v>
+        <v>569</v>
       </c>
       <c r="H58" s="2" t="s">
-        <v>555</v>
+        <v>570</v>
       </c>
     </row>
     <row r="59" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A59" t="s">
-        <v>556</v>
+        <v>571</v>
       </c>
       <c r="B59" t="s">
-        <v>557</v>
+        <v>572</v>
       </c>
       <c r="C59" t="s">
-        <v>282</v>
+        <v>369</v>
       </c>
       <c r="D59" t="s">
-        <v>276</v>
+        <v>510</v>
       </c>
       <c r="E59" t="s">
-        <v>558</v>
+        <v>573</v>
       </c>
       <c r="F59" t="s">
-        <v>559</v>
+        <v>574</v>
       </c>
       <c r="H59" s="2" t="s">
-        <v>560</v>
+        <v>575</v>
       </c>
     </row>
     <row r="60" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A60" t="s">
-        <v>561</v>
+        <v>576</v>
       </c>
       <c r="B60" t="s">
-        <v>562</v>
+        <v>577</v>
       </c>
       <c r="C60" t="s">
-        <v>563</v>
+        <v>419</v>
       </c>
       <c r="D60" t="s">
+        <v>578</v>
+      </c>
+      <c r="E60" t="s">
+        <v>579</v>
+      </c>
+      <c r="F60" t="s">
         <v>276</v>
       </c>
-      <c r="E60" t="s">
-        <v>564</v>
-      </c>
-      <c r="F60" t="s">
-        <v>565</v>
-      </c>
       <c r="H60" s="2" t="s">
-        <v>566</v>
+        <v>580</v>
       </c>
     </row>
     <row r="61" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A61" t="s">
-        <v>567</v>
+        <v>581</v>
       </c>
       <c r="B61" t="s">
-        <v>568</v>
+        <v>582</v>
       </c>
       <c r="C61" t="s">
-        <v>569</v>
+        <v>526</v>
       </c>
       <c r="D61" t="s">
-        <v>389</v>
+        <v>288</v>
       </c>
       <c r="E61" t="s">
-        <v>270</v>
+        <v>583</v>
       </c>
       <c r="F61" t="s">
-        <v>570</v>
+        <v>584</v>
       </c>
       <c r="H61" s="2" t="s">
-        <v>571</v>
+        <v>585</v>
       </c>
     </row>
     <row r="62" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A62" t="s">
-        <v>572</v>
+        <v>586</v>
       </c>
       <c r="B62" t="s">
-        <v>573</v>
+        <v>587</v>
       </c>
       <c r="C62" t="s">
-        <v>574</v>
+        <v>419</v>
       </c>
       <c r="D62" t="s">
-        <v>276</v>
+        <v>288</v>
       </c>
       <c r="E62" t="s">
-        <v>575</v>
+        <v>588</v>
       </c>
       <c r="F62" t="s">
-        <v>576</v>
+        <v>589</v>
       </c>
       <c r="H62" s="2" t="s">
-        <v>577</v>
+        <v>590</v>
       </c>
     </row>
     <row r="63" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A63" t="s">
-        <v>578</v>
+        <v>591</v>
       </c>
       <c r="B63" t="s">
-        <v>579</v>
+        <v>320</v>
       </c>
       <c r="C63" t="s">
-        <v>282</v>
+        <v>321</v>
       </c>
       <c r="D63" t="s">
-        <v>276</v>
+        <v>288</v>
       </c>
       <c r="E63" t="s">
-        <v>580</v>
+        <v>592</v>
       </c>
       <c r="F63" t="s">
-        <v>581</v>
+        <v>593</v>
       </c>
       <c r="H63" s="2" t="s">
-        <v>582</v>
+        <v>594</v>
       </c>
     </row>
     <row r="64" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A64" t="s">
-        <v>583</v>
+        <v>595</v>
       </c>
       <c r="B64" t="s">
-        <v>303</v>
+        <v>596</v>
       </c>
       <c r="C64" t="s">
-        <v>584</v>
+        <v>262</v>
       </c>
       <c r="D64" t="s">
-        <v>276</v>
+        <v>288</v>
       </c>
       <c r="E64" t="s">
-        <v>585</v>
+        <v>597</v>
       </c>
       <c r="F64" t="s">
-        <v>306</v>
+        <v>598</v>
       </c>
       <c r="H64" s="2" t="s">
-        <v>586</v>
+        <v>599</v>
       </c>
     </row>
     <row r="65" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A65" t="s">
-        <v>587</v>
+        <v>600</v>
       </c>
       <c r="B65" t="s">
-        <v>588</v>
+        <v>601</v>
       </c>
       <c r="C65" t="s">
-        <v>589</v>
+        <v>602</v>
       </c>
       <c r="D65" t="s">
-        <v>276</v>
+        <v>350</v>
       </c>
       <c r="E65" t="s">
-        <v>289</v>
+        <v>603</v>
       </c>
       <c r="F65" t="s">
-        <v>590</v>
+        <v>307</v>
       </c>
       <c r="H65" s="2" t="s">
-        <v>591</v>
+        <v>604</v>
       </c>
     </row>
     <row r="66" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A66" t="s">
-        <v>592</v>
+        <v>605</v>
       </c>
       <c r="B66" t="s">
-        <v>593</v>
+        <v>606</v>
       </c>
       <c r="C66" t="s">
-        <v>594</v>
+        <v>369</v>
       </c>
       <c r="D66" t="s">
-        <v>276</v>
+        <v>510</v>
       </c>
       <c r="E66" t="s">
-        <v>595</v>
+        <v>607</v>
       </c>
       <c r="F66" t="s">
-        <v>596</v>
+        <v>608</v>
       </c>
       <c r="H66" s="2" t="s">
-        <v>597</v>
+        <v>609</v>
       </c>
     </row>
     <row r="67" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A67" t="s">
-        <v>598</v>
+        <v>610</v>
       </c>
       <c r="B67" t="s">
-        <v>599</v>
+        <v>611</v>
       </c>
       <c r="C67" t="s">
-        <v>600</v>
+        <v>612</v>
       </c>
       <c r="D67" t="s">
-        <v>276</v>
+        <v>288</v>
       </c>
       <c r="E67" t="s">
-        <v>411</v>
+        <v>316</v>
       </c>
       <c r="F67" t="s">
-        <v>601</v>
+        <v>613</v>
       </c>
       <c r="H67" s="2" t="s">
-        <v>602</v>
+        <v>614</v>
       </c>
     </row>
     <row r="68" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A68" t="s">
-        <v>603</v>
+        <v>615</v>
       </c>
       <c r="B68" t="s">
-        <v>604</v>
+        <v>616</v>
       </c>
       <c r="C68" t="s">
-        <v>282</v>
+        <v>262</v>
       </c>
       <c r="D68" t="s">
-        <v>276</v>
+        <v>288</v>
       </c>
       <c r="E68" t="s">
-        <v>605</v>
+        <v>617</v>
       </c>
       <c r="F68" t="s">
-        <v>606</v>
+        <v>618</v>
       </c>
       <c r="H68" s="2" t="s">
-        <v>607</v>
+        <v>619</v>
       </c>
     </row>
     <row r="69" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A69" t="s">
-        <v>608</v>
+        <v>620</v>
       </c>
       <c r="B69" t="s">
-        <v>609</v>
+        <v>490</v>
       </c>
       <c r="C69" t="s">
-        <v>610</v>
+        <v>491</v>
       </c>
       <c r="D69" t="s">
-        <v>276</v>
+        <v>288</v>
       </c>
       <c r="E69" t="s">
-        <v>611</v>
+        <v>621</v>
       </c>
       <c r="F69" t="s">
-        <v>612</v>
+        <v>506</v>
       </c>
       <c r="H69" s="2" t="s">
-        <v>613</v>
+        <v>622</v>
       </c>
     </row>
     <row r="70" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A70" t="s">
-        <v>614</v>
+        <v>623</v>
       </c>
       <c r="B70" t="s">
-        <v>615</v>
+        <v>624</v>
       </c>
       <c r="C70" t="s">
-        <v>282</v>
+        <v>625</v>
       </c>
       <c r="D70" t="s">
-        <v>276</v>
+        <v>288</v>
       </c>
       <c r="E70" t="s">
-        <v>616</v>
+        <v>626</v>
       </c>
       <c r="F70" t="s">
-        <v>617</v>
+        <v>627</v>
       </c>
       <c r="H70" s="2" t="s">
-        <v>618</v>
+        <v>628</v>
       </c>
     </row>
     <row r="71" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A71" t="s">
-        <v>619</v>
+        <v>629</v>
       </c>
       <c r="B71" t="s">
-        <v>620</v>
+        <v>320</v>
       </c>
       <c r="C71" t="s">
-        <v>401</v>
+        <v>321</v>
       </c>
       <c r="D71" t="s">
-        <v>276</v>
+        <v>288</v>
       </c>
       <c r="E71" t="s">
-        <v>621</v>
+        <v>630</v>
       </c>
       <c r="F71" t="s">
-        <v>622</v>
+        <v>323</v>
       </c>
       <c r="H71" s="2" t="s">
-        <v>623</v>
+        <v>631</v>
       </c>
     </row>
     <row r="72" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A72" t="s">
-        <v>624</v>
+        <v>629</v>
       </c>
       <c r="B72" t="s">
-        <v>625</v>
+        <v>632</v>
       </c>
       <c r="C72" t="s">
-        <v>626</v>
+        <v>633</v>
       </c>
       <c r="D72" t="s">
-        <v>276</v>
+        <v>510</v>
       </c>
       <c r="E72" t="s">
-        <v>627</v>
+        <v>634</v>
       </c>
       <c r="F72" t="s">
-        <v>539</v>
+        <v>635</v>
       </c>
       <c r="H72" s="2" t="s">
-        <v>628</v>
+        <v>636</v>
       </c>
     </row>
     <row r="73" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A73" t="s">
-        <v>629</v>
+        <v>637</v>
       </c>
       <c r="B73" t="s">
-        <v>630</v>
+        <v>638</v>
       </c>
       <c r="C73" t="s">
-        <v>282</v>
+        <v>327</v>
       </c>
       <c r="D73" t="s">
-        <v>276</v>
+        <v>288</v>
       </c>
       <c r="E73" t="s">
-        <v>631</v>
+        <v>443</v>
       </c>
       <c r="F73" t="s">
-        <v>270</v>
+        <v>584</v>
       </c>
       <c r="H73" s="2" t="s">
-        <v>632</v>
+        <v>639</v>
       </c>
     </row>
     <row r="74" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A74" t="s">
-        <v>633</v>
+        <v>640</v>
       </c>
       <c r="B74" t="s">
-        <v>634</v>
+        <v>641</v>
       </c>
       <c r="C74" t="s">
-        <v>282</v>
+        <v>321</v>
       </c>
       <c r="D74" t="s">
+        <v>288</v>
+      </c>
+      <c r="E74" t="s">
+        <v>642</v>
+      </c>
+      <c r="F74" t="s">
         <v>276</v>
       </c>
-      <c r="E74" t="s">
-        <v>635</v>
-      </c>
-      <c r="F74" t="s">
-        <v>636</v>
-      </c>
       <c r="H74" s="2" t="s">
-        <v>637</v>
+        <v>643</v>
       </c>
     </row>
     <row r="75" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A75" t="s">
-        <v>212</v>
+        <v>644</v>
       </c>
       <c r="B75" t="s">
-        <v>516</v>
+        <v>490</v>
       </c>
       <c r="C75" t="s">
-        <v>517</v>
+        <v>491</v>
       </c>
       <c r="D75" t="s">
-        <v>276</v>
+        <v>288</v>
       </c>
       <c r="E75" t="s">
-        <v>347</v>
+        <v>645</v>
       </c>
       <c r="F75" t="s">
-        <v>638</v>
+        <v>506</v>
       </c>
       <c r="H75" s="2" t="s">
-        <v>639</v>
+        <v>646</v>
       </c>
     </row>
     <row r="76" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A76" t="s">
-        <v>640</v>
+        <v>647</v>
       </c>
       <c r="B76" t="s">
-        <v>641</v>
+        <v>490</v>
       </c>
       <c r="C76" t="s">
-        <v>642</v>
+        <v>491</v>
       </c>
       <c r="D76" t="s">
-        <v>276</v>
+        <v>288</v>
       </c>
       <c r="E76" t="s">
-        <v>643</v>
+        <v>404</v>
       </c>
       <c r="F76" t="s">
-        <v>270</v>
+        <v>506</v>
       </c>
       <c r="H76" s="2" t="s">
-        <v>644</v>
+        <v>648</v>
       </c>
     </row>
     <row r="77" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A77" t="s">
-        <v>645</v>
+        <v>649</v>
       </c>
       <c r="B77" t="s">
-        <v>641</v>
+        <v>650</v>
       </c>
       <c r="C77" t="s">
-        <v>642</v>
+        <v>651</v>
       </c>
       <c r="D77" t="s">
+        <v>288</v>
+      </c>
+      <c r="E77" t="s">
+        <v>652</v>
+      </c>
+      <c r="F77" t="s">
         <v>276</v>
       </c>
-      <c r="E77" t="s">
-        <v>646</v>
-      </c>
-      <c r="F77" t="s">
-        <v>270</v>
-      </c>
       <c r="H77" s="2" t="s">
-        <v>647</v>
+        <v>653</v>
       </c>
     </row>
     <row r="78" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A78" t="s">
-        <v>648</v>
+        <v>654</v>
       </c>
       <c r="B78" t="s">
-        <v>649</v>
+        <v>655</v>
       </c>
       <c r="C78" t="s">
-        <v>650</v>
+        <v>262</v>
       </c>
       <c r="D78" t="s">
-        <v>276</v>
+        <v>288</v>
       </c>
       <c r="E78" t="s">
-        <v>651</v>
+        <v>656</v>
       </c>
       <c r="F78" t="s">
-        <v>652</v>
+        <v>657</v>
       </c>
       <c r="H78" s="2" t="s">
-        <v>653</v>
+        <v>658</v>
       </c>
     </row>
     <row r="79" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A79" t="s">
-        <v>654</v>
+        <v>659</v>
       </c>
       <c r="B79" t="s">
-        <v>655</v>
+        <v>660</v>
       </c>
       <c r="C79" t="s">
-        <v>656</v>
+        <v>661</v>
       </c>
       <c r="D79" t="s">
-        <v>276</v>
+        <v>288</v>
       </c>
       <c r="E79" t="s">
-        <v>657</v>
+        <v>662</v>
       </c>
       <c r="F79" t="s">
-        <v>539</v>
+        <v>663</v>
       </c>
       <c r="H79" s="2" t="s">
-        <v>658</v>
+        <v>664</v>
       </c>
     </row>
     <row r="80" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A80" t="s">
-        <v>659</v>
+        <v>665</v>
       </c>
       <c r="B80" t="s">
-        <v>655</v>
+        <v>666</v>
       </c>
       <c r="C80" t="s">
-        <v>660</v>
+        <v>667</v>
       </c>
       <c r="D80" t="s">
+        <v>389</v>
+      </c>
+      <c r="E80" t="s">
         <v>276</v>
       </c>
-      <c r="E80" t="s">
-        <v>657</v>
-      </c>
       <c r="F80" t="s">
-        <v>539</v>
+        <v>668</v>
       </c>
       <c r="H80" s="2" t="s">
-        <v>661</v>
+        <v>669</v>
       </c>
     </row>
     <row r="81" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A81" t="s">
-        <v>662</v>
+        <v>670</v>
       </c>
       <c r="B81" t="s">
-        <v>521</v>
+        <v>671</v>
       </c>
       <c r="C81" t="s">
-        <v>282</v>
+        <v>672</v>
       </c>
       <c r="D81" t="s">
-        <v>276</v>
+        <v>288</v>
       </c>
       <c r="E81" t="s">
-        <v>522</v>
+        <v>673</v>
       </c>
       <c r="F81" t="s">
-        <v>663</v>
+        <v>410</v>
       </c>
       <c r="H81" s="2" t="s">
-        <v>664</v>
+        <v>674</v>
       </c>
     </row>
     <row r="82" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A82" t="s">
-        <v>665</v>
+        <v>675</v>
       </c>
       <c r="B82" t="s">
-        <v>666</v>
+        <v>676</v>
       </c>
       <c r="C82" t="s">
-        <v>667</v>
+        <v>262</v>
       </c>
       <c r="D82" t="s">
-        <v>276</v>
+        <v>288</v>
       </c>
       <c r="E82" t="s">
-        <v>668</v>
+        <v>677</v>
       </c>
       <c r="F82" t="s">
-        <v>669</v>
+        <v>678</v>
       </c>
       <c r="H82" s="2" t="s">
-        <v>670</v>
+        <v>679</v>
       </c>
     </row>
     <row r="83" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A83" t="s">
-        <v>671</v>
+        <v>680</v>
       </c>
       <c r="B83" t="s">
-        <v>309</v>
+        <v>681</v>
       </c>
       <c r="C83" t="s">
-        <v>310</v>
+        <v>321</v>
       </c>
       <c r="D83" t="s">
-        <v>389</v>
+        <v>288</v>
       </c>
       <c r="E83" t="s">
-        <v>270</v>
+        <v>682</v>
       </c>
       <c r="F83" t="s">
-        <v>312</v>
+        <v>683</v>
       </c>
       <c r="H83" s="2" t="s">
-        <v>672</v>
+        <v>684</v>
       </c>
     </row>
     <row r="84" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A84" t="s">
-        <v>673</v>
+        <v>685</v>
       </c>
       <c r="B84" t="s">
-        <v>674</v>
+        <v>320</v>
       </c>
       <c r="C84" t="s">
-        <v>675</v>
+        <v>686</v>
       </c>
       <c r="D84" t="s">
-        <v>276</v>
+        <v>288</v>
       </c>
       <c r="E84" t="s">
-        <v>676</v>
+        <v>687</v>
       </c>
       <c r="F84" t="s">
-        <v>677</v>
+        <v>323</v>
       </c>
       <c r="H84" s="2" t="s">
-        <v>678</v>
+        <v>688</v>
       </c>
     </row>
     <row r="85" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A85" t="s">
-        <v>679</v>
+        <v>689</v>
       </c>
       <c r="B85" t="s">
-        <v>680</v>
+        <v>690</v>
       </c>
       <c r="C85" t="s">
-        <v>681</v>
+        <v>691</v>
       </c>
       <c r="D85" t="s">
-        <v>276</v>
+        <v>288</v>
       </c>
       <c r="E85" t="s">
-        <v>643</v>
+        <v>306</v>
       </c>
       <c r="F85" t="s">
-        <v>565</v>
+        <v>692</v>
       </c>
       <c r="H85" s="2" t="s">
-        <v>682</v>
+        <v>693</v>
       </c>
     </row>
     <row r="86" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A86" t="s">
-        <v>683</v>
+        <v>694</v>
       </c>
       <c r="B86" t="s">
-        <v>684</v>
+        <v>293</v>
       </c>
       <c r="C86" t="s">
-        <v>310</v>
+        <v>262</v>
       </c>
       <c r="D86" t="s">
-        <v>276</v>
+        <v>288</v>
       </c>
       <c r="E86" t="s">
-        <v>685</v>
+        <v>645</v>
       </c>
       <c r="F86" t="s">
-        <v>290</v>
+        <v>296</v>
       </c>
       <c r="H86" s="2" t="s">
-        <v>686</v>
+        <v>695</v>
       </c>
     </row>
     <row r="87" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A87" t="s">
-        <v>683</v>
+        <v>696</v>
       </c>
       <c r="B87" t="s">
-        <v>684</v>
+        <v>697</v>
       </c>
       <c r="C87" t="s">
-        <v>687</v>
+        <v>698</v>
       </c>
       <c r="D87" t="s">
-        <v>276</v>
+        <v>288</v>
       </c>
       <c r="E87" t="s">
-        <v>685</v>
+        <v>699</v>
       </c>
       <c r="F87" t="s">
-        <v>290</v>
+        <v>700</v>
       </c>
       <c r="H87" s="2" t="s">
-        <v>688</v>
+        <v>701</v>
       </c>
     </row>
     <row r="88" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A88" t="s">
-        <v>683</v>
+        <v>702</v>
       </c>
       <c r="B88" t="s">
-        <v>684</v>
+        <v>703</v>
       </c>
       <c r="C88" t="s">
-        <v>689</v>
+        <v>704</v>
       </c>
       <c r="D88" t="s">
-        <v>276</v>
+        <v>288</v>
       </c>
       <c r="E88" t="s">
-        <v>685</v>
+        <v>458</v>
       </c>
       <c r="F88" t="s">
-        <v>290</v>
+        <v>705</v>
       </c>
       <c r="H88" s="2" t="s">
-        <v>690</v>
+        <v>706</v>
       </c>
     </row>
     <row r="89" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A89" t="s">
-        <v>683</v>
+        <v>707</v>
       </c>
       <c r="B89" t="s">
-        <v>684</v>
+        <v>708</v>
       </c>
       <c r="C89" t="s">
-        <v>342</v>
+        <v>709</v>
       </c>
       <c r="D89" t="s">
-        <v>276</v>
+        <v>288</v>
       </c>
       <c r="E89" t="s">
-        <v>685</v>
+        <v>710</v>
       </c>
       <c r="F89" t="s">
-        <v>290</v>
+        <v>399</v>
       </c>
       <c r="H89" s="2" t="s">
-        <v>691</v>
+        <v>711</v>
       </c>
     </row>
     <row r="90" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A90" t="s">
-        <v>692</v>
+        <v>712</v>
       </c>
       <c r="B90" t="s">
-        <v>630</v>
+        <v>708</v>
       </c>
       <c r="C90" t="s">
-        <v>282</v>
+        <v>709</v>
       </c>
       <c r="D90" t="s">
-        <v>276</v>
+        <v>288</v>
       </c>
       <c r="E90" t="s">
-        <v>693</v>
+        <v>710</v>
       </c>
       <c r="F90" t="s">
-        <v>270</v>
+        <v>399</v>
       </c>
       <c r="H90" s="2" t="s">
-        <v>694</v>
+        <v>713</v>
       </c>
     </row>
     <row r="91" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A91" t="s">
-        <v>695</v>
+        <v>714</v>
       </c>
       <c r="B91" t="s">
-        <v>696</v>
+        <v>715</v>
       </c>
       <c r="C91" t="s">
-        <v>697</v>
+        <v>262</v>
       </c>
       <c r="D91" t="s">
+        <v>288</v>
+      </c>
+      <c r="E91" t="s">
+        <v>716</v>
+      </c>
+      <c r="F91" t="s">
+        <v>717</v>
+      </c>
+      <c r="H91" s="2" t="s">
+        <v>718</v>
+      </c>
+    </row>
+    <row r="92" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A92" t="s">
+        <v>719</v>
+      </c>
+      <c r="B92" t="s">
+        <v>720</v>
+      </c>
+      <c r="C92" t="s">
+        <v>721</v>
+      </c>
+      <c r="D92" t="s">
+        <v>288</v>
+      </c>
+      <c r="E92" t="s">
+        <v>722</v>
+      </c>
+      <c r="F92" t="s">
+        <v>515</v>
+      </c>
+      <c r="H92" s="2" t="s">
+        <v>723</v>
+      </c>
+    </row>
+    <row r="93" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A93" t="s">
+        <v>724</v>
+      </c>
+      <c r="B93" t="s">
+        <v>725</v>
+      </c>
+      <c r="C93" t="s">
+        <v>726</v>
+      </c>
+      <c r="D93" t="s">
+        <v>288</v>
+      </c>
+      <c r="E93" t="s">
+        <v>727</v>
+      </c>
+      <c r="F93" t="s">
+        <v>728</v>
+      </c>
+      <c r="H93" s="2" t="s">
+        <v>729</v>
+      </c>
+    </row>
+    <row r="94" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A94" t="s">
+        <v>730</v>
+      </c>
+      <c r="B94" t="s">
+        <v>731</v>
+      </c>
+      <c r="C94" t="s">
+        <v>262</v>
+      </c>
+      <c r="D94" t="s">
+        <v>288</v>
+      </c>
+      <c r="E94" t="s">
+        <v>732</v>
+      </c>
+      <c r="F94" t="s">
+        <v>733</v>
+      </c>
+      <c r="H94" s="2" t="s">
+        <v>734</v>
+      </c>
+    </row>
+    <row r="95" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A95" t="s">
+        <v>735</v>
+      </c>
+      <c r="B95" t="s">
+        <v>736</v>
+      </c>
+      <c r="C95" t="s">
+        <v>448</v>
+      </c>
+      <c r="D95" t="s">
+        <v>288</v>
+      </c>
+      <c r="E95" t="s">
+        <v>737</v>
+      </c>
+      <c r="F95" t="s">
+        <v>738</v>
+      </c>
+      <c r="H95" s="2" t="s">
+        <v>739</v>
+      </c>
+    </row>
+    <row r="96" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A96" t="s">
+        <v>740</v>
+      </c>
+      <c r="B96" t="s">
+        <v>741</v>
+      </c>
+      <c r="C96" t="s">
+        <v>742</v>
+      </c>
+      <c r="D96" t="s">
+        <v>288</v>
+      </c>
+      <c r="E96" t="s">
+        <v>743</v>
+      </c>
+      <c r="F96" t="s">
+        <v>584</v>
+      </c>
+      <c r="H96" s="2" t="s">
+        <v>744</v>
+      </c>
+    </row>
+    <row r="97" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A97" t="s">
+        <v>745</v>
+      </c>
+      <c r="B97" t="s">
+        <v>746</v>
+      </c>
+      <c r="C97" t="s">
+        <v>262</v>
+      </c>
+      <c r="D97" t="s">
+        <v>288</v>
+      </c>
+      <c r="E97" t="s">
+        <v>747</v>
+      </c>
+      <c r="F97" t="s">
         <v>276</v>
       </c>
-      <c r="E91" t="s">
-        <v>698</v>
-      </c>
-      <c r="F91" t="s">
-        <v>699</v>
-      </c>
-      <c r="H91" s="2" t="s">
-        <v>700</v>
+      <c r="H97" s="2" t="s">
+        <v>748</v>
+      </c>
+    </row>
+    <row r="98" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A98" t="s">
+        <v>749</v>
+      </c>
+      <c r="B98" t="s">
+        <v>750</v>
+      </c>
+      <c r="C98" t="s">
+        <v>262</v>
+      </c>
+      <c r="D98" t="s">
+        <v>288</v>
+      </c>
+      <c r="E98" t="s">
+        <v>751</v>
+      </c>
+      <c r="F98" t="s">
+        <v>752</v>
+      </c>
+      <c r="H98" s="2" t="s">
+        <v>753</v>
+      </c>
+    </row>
+    <row r="99" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A99" t="s">
+        <v>212</v>
+      </c>
+      <c r="B99" t="s">
+        <v>611</v>
+      </c>
+      <c r="C99" t="s">
+        <v>612</v>
+      </c>
+      <c r="D99" t="s">
+        <v>288</v>
+      </c>
+      <c r="E99" t="s">
+        <v>374</v>
+      </c>
+      <c r="F99" t="s">
+        <v>754</v>
+      </c>
+      <c r="H99" s="2" t="s">
+        <v>755</v>
+      </c>
+    </row>
+    <row r="100" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A100" t="s">
+        <v>212</v>
+      </c>
+      <c r="B100" t="s">
+        <v>632</v>
+      </c>
+      <c r="C100" t="s">
+        <v>633</v>
+      </c>
+      <c r="D100" t="s">
+        <v>510</v>
+      </c>
+      <c r="E100" t="s">
+        <v>756</v>
+      </c>
+      <c r="F100" t="s">
+        <v>635</v>
+      </c>
+      <c r="H100" s="2" t="s">
+        <v>757</v>
+      </c>
+    </row>
+    <row r="101" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A101" t="s">
+        <v>758</v>
+      </c>
+      <c r="B101" t="s">
+        <v>759</v>
+      </c>
+      <c r="C101" t="s">
+        <v>760</v>
+      </c>
+      <c r="D101" t="s">
+        <v>288</v>
+      </c>
+      <c r="E101" t="s">
+        <v>761</v>
+      </c>
+      <c r="F101" t="s">
+        <v>276</v>
+      </c>
+      <c r="H101" s="2" t="s">
+        <v>762</v>
+      </c>
+    </row>
+    <row r="102" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A102" t="s">
+        <v>763</v>
+      </c>
+      <c r="B102" t="s">
+        <v>759</v>
+      </c>
+      <c r="C102" t="s">
+        <v>760</v>
+      </c>
+      <c r="D102" t="s">
+        <v>288</v>
+      </c>
+      <c r="E102" t="s">
+        <v>764</v>
+      </c>
+      <c r="F102" t="s">
+        <v>276</v>
+      </c>
+      <c r="H102" s="2" t="s">
+        <v>765</v>
+      </c>
+    </row>
+    <row r="103" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A103" t="s">
+        <v>766</v>
+      </c>
+      <c r="B103" t="s">
+        <v>767</v>
+      </c>
+      <c r="C103" t="s">
+        <v>768</v>
+      </c>
+      <c r="D103" t="s">
+        <v>288</v>
+      </c>
+      <c r="E103" t="s">
+        <v>769</v>
+      </c>
+      <c r="F103" t="s">
+        <v>770</v>
+      </c>
+      <c r="H103" s="2" t="s">
+        <v>771</v>
+      </c>
+    </row>
+    <row r="104" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A104" t="s">
+        <v>772</v>
+      </c>
+      <c r="B104" t="s">
+        <v>773</v>
+      </c>
+      <c r="C104" t="s">
+        <v>774</v>
+      </c>
+      <c r="D104" t="s">
+        <v>288</v>
+      </c>
+      <c r="E104" t="s">
+        <v>775</v>
+      </c>
+      <c r="F104" t="s">
+        <v>584</v>
+      </c>
+      <c r="H104" s="2" t="s">
+        <v>776</v>
+      </c>
+    </row>
+    <row r="105" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A105" t="s">
+        <v>777</v>
+      </c>
+      <c r="B105" t="s">
+        <v>773</v>
+      </c>
+      <c r="C105" t="s">
+        <v>778</v>
+      </c>
+      <c r="D105" t="s">
+        <v>288</v>
+      </c>
+      <c r="E105" t="s">
+        <v>775</v>
+      </c>
+      <c r="F105" t="s">
+        <v>584</v>
+      </c>
+      <c r="H105" s="2" t="s">
+        <v>779</v>
+      </c>
+    </row>
+    <row r="106" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A106" t="s">
+        <v>780</v>
+      </c>
+      <c r="B106" t="s">
+        <v>616</v>
+      </c>
+      <c r="C106" t="s">
+        <v>262</v>
+      </c>
+      <c r="D106" t="s">
+        <v>288</v>
+      </c>
+      <c r="E106" t="s">
+        <v>617</v>
+      </c>
+      <c r="F106" t="s">
+        <v>781</v>
+      </c>
+      <c r="H106" s="2" t="s">
+        <v>782</v>
+      </c>
+    </row>
+    <row r="107" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A107" t="s">
+        <v>783</v>
+      </c>
+      <c r="B107" t="s">
+        <v>784</v>
+      </c>
+      <c r="C107" t="s">
+        <v>785</v>
+      </c>
+      <c r="D107" t="s">
+        <v>288</v>
+      </c>
+      <c r="E107" t="s">
+        <v>786</v>
+      </c>
+      <c r="F107" t="s">
+        <v>787</v>
+      </c>
+      <c r="H107" s="2" t="s">
+        <v>788</v>
+      </c>
+    </row>
+    <row r="108" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A108" t="s">
+        <v>789</v>
+      </c>
+      <c r="B108" t="s">
+        <v>326</v>
+      </c>
+      <c r="C108" t="s">
+        <v>327</v>
+      </c>
+      <c r="D108" t="s">
+        <v>389</v>
+      </c>
+      <c r="E108" t="s">
+        <v>276</v>
+      </c>
+      <c r="F108" t="s">
+        <v>329</v>
+      </c>
+      <c r="H108" s="2" t="s">
+        <v>790</v>
+      </c>
+    </row>
+    <row r="109" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A109" t="s">
+        <v>791</v>
+      </c>
+      <c r="B109" t="s">
+        <v>632</v>
+      </c>
+      <c r="C109" t="s">
+        <v>633</v>
+      </c>
+      <c r="D109" t="s">
+        <v>510</v>
+      </c>
+      <c r="E109" t="s">
+        <v>792</v>
+      </c>
+      <c r="F109" t="s">
+        <v>635</v>
+      </c>
+      <c r="H109" s="2" t="s">
+        <v>793</v>
+      </c>
+    </row>
+    <row r="110" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A110" t="s">
+        <v>794</v>
+      </c>
+      <c r="B110" t="s">
+        <v>795</v>
+      </c>
+      <c r="C110" t="s">
+        <v>796</v>
+      </c>
+      <c r="D110" t="s">
+        <v>288</v>
+      </c>
+      <c r="E110" t="s">
+        <v>797</v>
+      </c>
+      <c r="F110" t="s">
+        <v>798</v>
+      </c>
+      <c r="H110" s="2" t="s">
+        <v>799</v>
+      </c>
+    </row>
+    <row r="111" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A111" t="s">
+        <v>800</v>
+      </c>
+      <c r="B111" t="s">
+        <v>801</v>
+      </c>
+      <c r="C111" t="s">
+        <v>802</v>
+      </c>
+      <c r="D111" t="s">
+        <v>288</v>
+      </c>
+      <c r="E111" t="s">
+        <v>803</v>
+      </c>
+      <c r="F111" t="s">
+        <v>339</v>
+      </c>
+      <c r="H111" s="2" t="s">
+        <v>804</v>
+      </c>
+    </row>
+    <row r="112" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A112" t="s">
+        <v>805</v>
+      </c>
+      <c r="B112" t="s">
+        <v>806</v>
+      </c>
+      <c r="C112" t="s">
+        <v>807</v>
+      </c>
+      <c r="D112" t="s">
+        <v>288</v>
+      </c>
+      <c r="E112" t="s">
+        <v>761</v>
+      </c>
+      <c r="F112" t="s">
+        <v>663</v>
+      </c>
+      <c r="H112" s="2" t="s">
+        <v>808</v>
+      </c>
+    </row>
+    <row r="113" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A113" t="s">
+        <v>809</v>
+      </c>
+      <c r="B113" t="s">
+        <v>810</v>
+      </c>
+      <c r="C113" t="s">
+        <v>327</v>
+      </c>
+      <c r="D113" t="s">
+        <v>288</v>
+      </c>
+      <c r="E113" t="s">
+        <v>811</v>
+      </c>
+      <c r="F113" t="s">
+        <v>307</v>
+      </c>
+      <c r="H113" s="2" t="s">
+        <v>812</v>
+      </c>
+    </row>
+    <row r="114" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A114" t="s">
+        <v>809</v>
+      </c>
+      <c r="B114" t="s">
+        <v>810</v>
+      </c>
+      <c r="C114" t="s">
+        <v>813</v>
+      </c>
+      <c r="D114" t="s">
+        <v>288</v>
+      </c>
+      <c r="E114" t="s">
+        <v>811</v>
+      </c>
+      <c r="F114" t="s">
+        <v>307</v>
+      </c>
+      <c r="H114" s="2" t="s">
+        <v>814</v>
+      </c>
+    </row>
+    <row r="115" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A115" t="s">
+        <v>809</v>
+      </c>
+      <c r="B115" t="s">
+        <v>810</v>
+      </c>
+      <c r="C115" t="s">
+        <v>815</v>
+      </c>
+      <c r="D115" t="s">
+        <v>288</v>
+      </c>
+      <c r="E115" t="s">
+        <v>811</v>
+      </c>
+      <c r="F115" t="s">
+        <v>307</v>
+      </c>
+      <c r="H115" s="2" t="s">
+        <v>816</v>
+      </c>
+    </row>
+    <row r="116" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A116" t="s">
+        <v>809</v>
+      </c>
+      <c r="B116" t="s">
+        <v>810</v>
+      </c>
+      <c r="C116" t="s">
+        <v>369</v>
+      </c>
+      <c r="D116" t="s">
+        <v>288</v>
+      </c>
+      <c r="E116" t="s">
+        <v>811</v>
+      </c>
+      <c r="F116" t="s">
+        <v>307</v>
+      </c>
+      <c r="H116" s="2" t="s">
+        <v>817</v>
+      </c>
+    </row>
+    <row r="117" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A117" t="s">
+        <v>279</v>
+      </c>
+      <c r="B117" t="s">
+        <v>280</v>
+      </c>
+      <c r="C117" t="s">
+        <v>327</v>
+      </c>
+      <c r="D117" t="s">
+        <v>288</v>
+      </c>
+      <c r="E117" t="s">
+        <v>818</v>
+      </c>
+      <c r="F117" t="s">
+        <v>819</v>
+      </c>
+      <c r="G117" t="s">
+        <v>516</v>
+      </c>
+      <c r="H117" s="2" t="s">
+        <v>820</v>
+      </c>
+    </row>
+    <row r="118" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A118" t="s">
+        <v>821</v>
+      </c>
+      <c r="B118" t="s">
+        <v>746</v>
+      </c>
+      <c r="C118" t="s">
+        <v>262</v>
+      </c>
+      <c r="D118" t="s">
+        <v>288</v>
+      </c>
+      <c r="E118" t="s">
+        <v>822</v>
+      </c>
+      <c r="F118" t="s">
+        <v>276</v>
+      </c>
+      <c r="H118" s="2" t="s">
+        <v>823</v>
+      </c>
+    </row>
+    <row r="119" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A119" t="s">
+        <v>824</v>
+      </c>
+      <c r="B119" t="s">
+        <v>825</v>
+      </c>
+      <c r="C119" t="s">
+        <v>369</v>
+      </c>
+      <c r="D119" t="s">
+        <v>288</v>
+      </c>
+      <c r="E119" t="s">
+        <v>826</v>
+      </c>
+      <c r="F119" t="s">
+        <v>515</v>
+      </c>
+      <c r="H119" s="2" t="s">
+        <v>827</v>
+      </c>
+    </row>
+    <row r="120" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A120" t="s">
+        <v>828</v>
+      </c>
+      <c r="B120" t="s">
+        <v>829</v>
+      </c>
+      <c r="C120" t="s">
+        <v>830</v>
+      </c>
+      <c r="D120" t="s">
+        <v>288</v>
+      </c>
+      <c r="E120" t="s">
+        <v>831</v>
+      </c>
+      <c r="F120" t="s">
+        <v>832</v>
+      </c>
+      <c r="H120" s="2" t="s">
+        <v>833</v>
       </c>
     </row>
   </sheetData>
@@ -6052,6 +7178,35 @@
     <hyperlink ref="H89" r:id="rId88"/>
     <hyperlink ref="H90" r:id="rId89"/>
     <hyperlink ref="H91" r:id="rId90"/>
+    <hyperlink ref="H92" r:id="rId91"/>
+    <hyperlink ref="H93" r:id="rId92"/>
+    <hyperlink ref="H94" r:id="rId93"/>
+    <hyperlink ref="H95" r:id="rId94"/>
+    <hyperlink ref="H96" r:id="rId95"/>
+    <hyperlink ref="H97" r:id="rId96"/>
+    <hyperlink ref="H98" r:id="rId97"/>
+    <hyperlink ref="H99" r:id="rId98"/>
+    <hyperlink ref="H100" r:id="rId99"/>
+    <hyperlink ref="H101" r:id="rId100"/>
+    <hyperlink ref="H102" r:id="rId101"/>
+    <hyperlink ref="H103" r:id="rId102"/>
+    <hyperlink ref="H104" r:id="rId103"/>
+    <hyperlink ref="H105" r:id="rId104"/>
+    <hyperlink ref="H106" r:id="rId105"/>
+    <hyperlink ref="H107" r:id="rId106"/>
+    <hyperlink ref="H108" r:id="rId107"/>
+    <hyperlink ref="H109" r:id="rId108"/>
+    <hyperlink ref="H110" r:id="rId109"/>
+    <hyperlink ref="H111" r:id="rId110"/>
+    <hyperlink ref="H112" r:id="rId111"/>
+    <hyperlink ref="H113" r:id="rId112"/>
+    <hyperlink ref="H114" r:id="rId113"/>
+    <hyperlink ref="H115" r:id="rId114"/>
+    <hyperlink ref="H116" r:id="rId115"/>
+    <hyperlink ref="H117" r:id="rId116"/>
+    <hyperlink ref="H118" r:id="rId117"/>
+    <hyperlink ref="H119" r:id="rId118"/>
+    <hyperlink ref="H120" r:id="rId119"/>
   </hyperlinks>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup orientation="portrait" horizontalDpi="4294967295" verticalDpi="4294967295" scale="100" fitToWidth="1" fitToHeight="1"/>
